--- a/results/scraped_Cape_Town_Women_and_Family_Support.xlsx
+++ b/results/scraped_Cape_Town_Women_and_Family_Support.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="197">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -43,31 +43,31 @@
     <t>Woman-Wikipedia</t>
   </si>
   <si>
+    <t>Woman- Simple EnglishWikipedia, the free encyclopedia</t>
+  </si>
+  <si>
     <t>WOMANDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>Female-Wikipedia</t>
+  </si>
+  <si>
     <t>Women| News, Celebrity, Lifestyle, and Expert Opinions</t>
   </si>
   <si>
-    <t>Woman- Simple EnglishWikipedia, the free encyclopedia</t>
-  </si>
-  <si>
     <t>51 FamousWomenin History Who Have Changed the World</t>
   </si>
   <si>
-    <t>Women's Clothing &amp; Apparel |Dillard's</t>
-  </si>
-  <si>
-    <t>Woman vs.Women: What’s the Difference? - Thesaurus.com</t>
+    <t>Women| Britannica</t>
   </si>
   <si>
     <t>Women's History| NationalWomen's HistoryMuseum</t>
   </si>
   <si>
-    <t>Women's Clothing, Shoes, Jewelry, Watches &amp; Handbags | Amazon.com</t>
-  </si>
-  <si>
-    <t>Women in the United States-Wikipedia</t>
+    <t>Women|The Guardian</t>
+  </si>
+  <si>
+    <t>Women's Clothing, Shoes, &amp; Accessories |Nordstrom</t>
   </si>
   <si>
     <t>Gender-Wikipedia</t>
@@ -88,16 +88,16 @@
     <t>How Many Genders Are There? All 72 Genders List -MedicineNet</t>
   </si>
   <si>
+    <t>List ofgenderidentities -Wikipedia</t>
+  </si>
+  <si>
     <t>Sex and gender: Meanings, definition, identity, and expression</t>
   </si>
   <si>
-    <t>List ofgenderidentities -Wikipedia</t>
-  </si>
-  <si>
     <t>Gender- LGBTQIA+ Wiki</t>
   </si>
   <si>
-    <t>Gender- Simple EnglishWikipedia, the free encyclopedia</t>
+    <t>Gender– Stanford Med Education</t>
   </si>
   <si>
     <t>Family- Wikipedia</t>
@@ -109,25 +109,25 @@
     <t>FAMILYDefinition &amp; Meaning - Merriam-Webster</t>
   </si>
   <si>
+    <t>Family- Simple English Wikipedia, the free encyclopedia</t>
+  </si>
+  <si>
     <t>Find yourfamily. Free Genealogy Archives - FamilySearch</t>
   </si>
   <si>
     <t>12 Types ofFamilyStructures &amp; Their Characteristics - wikiHow</t>
   </si>
   <si>
-    <t>Family- Simple English Wikipedia, the free encyclopedia</t>
+    <t>What IsFamily? A Closer Look AtFamilyStructure ... -FamilyOriented</t>
+  </si>
+  <si>
+    <t>What IsFamily? (14 Key Points) - Simplicable</t>
   </si>
   <si>
     <t>Familyin the United States - Wikipedia</t>
   </si>
   <si>
-    <t>FAMILY| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>What IsFamily? A Closer Look AtFamilyStructure ... -FamilyOriented</t>
-  </si>
-  <si>
-    <t>What IsFamily? (14 Key Points) - Simplicable</t>
+    <t>The Meaning ofFamily- LoveToKnow</t>
   </si>
   <si>
     <t>SINGLEDefinition &amp; Meaning - Merriam-Webster</t>
@@ -139,85 +139,175 @@
     <t>SINGLE| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
-    <t>Single(music) - Wikipedia</t>
+    <t>Single- Wikipedia</t>
   </si>
   <si>
     <t>Match® | The leading dating app for singles. Find better matches.</t>
   </si>
   <si>
-    <t>Single- YouTube</t>
-  </si>
-  <si>
     <t>Why Some People Really Love BeingSingle- Psychology Today</t>
   </si>
   <si>
-    <t>Single person- Simple English Wikipedia, the free encyclopedia</t>
+    <t>Lil Wayne- Single (Official Video) - YouTube</t>
   </si>
   <si>
     <t>SINGLEDefinition &amp; Meaning |Dictionary.com</t>
   </si>
   <si>
+    <t>eharmony - Dating site to meet singles &amp; find real love!</t>
+  </si>
+  <si>
     <t>Single- definition ofsingleby The Free Dictionary</t>
   </si>
   <si>
-    <t>ABUSEDDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>ABUSED| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>ABUSEDSynonyms: 157 Similar and Opposite Words -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>ABUSE| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>Abused- definition ofabusedby The Free Dictionary</t>
-  </si>
-  <si>
-    <t>Abused - Definition, Meaning &amp; Synonyms| Vocabulary.com</t>
-  </si>
-  <si>
-    <t>ABUSEDefinition &amp; Meaning |Dictionary.com</t>
-  </si>
-  <si>
-    <t>ABUSEDDefinition &amp; Meaning | Dictionary.com</t>
-  </si>
-  <si>
-    <t>abused- Wiktionary, the free dictionary</t>
-  </si>
-  <si>
-    <t>What doesabusedmean? -Definitions.net</t>
-  </si>
-  <si>
-    <t>Framework - Scaled Agile Framework</t>
-  </si>
-  <si>
-    <t>Safes- The Home Depot</t>
-  </si>
-  <si>
-    <t>Amazon.com: Home Safes &amp;SafeAccessories - Home Safes &amp;Safe...</t>
-  </si>
-  <si>
-    <t>What isSAFe- Framework For Business Agility |Scaled Agile</t>
-  </si>
-  <si>
-    <t>Scaled Agile | Achieving Business Agility and Agile Planning</t>
-  </si>
-  <si>
-    <t>HOME SAFES- The Home Depot</t>
-  </si>
-  <si>
-    <t>Safes| Costco</t>
-  </si>
-  <si>
-    <t>Scaled agile framework- Wikipedia</t>
-  </si>
-  <si>
-    <t>Safesfor Secure Storage Solutions | Lowe's</t>
-  </si>
-  <si>
-    <t>SentrySafe® Official Site | Pistol Safes &amp; Fire Safes</t>
+    <t>Contact Us - Microsoft Support</t>
+  </si>
+  <si>
+    <t>Anmelden bei Hotmail | Microsoft Support</t>
+  </si>
+  <si>
+    <t>Microsoft Copilot Blog | Microsoft Community Hub</t>
+  </si>
+  <si>
+    <t>Exchange Online EWS, Your Time is Almost Up | Microsoft …</t>
+  </si>
+  <si>
+    <t>Getting ready for the Windows 11 upgrade | Microsoft Support</t>
+  </si>
+  <si>
+    <t>Mettre à jour les pilotes via Gestionnaire de périphériques dans ...</t>
+  </si>
+  <si>
+    <t>Aktualisieren von Treibern über Geräte-Manager in Windows</t>
+  </si>
+  <si>
+    <t>Getting the latest Microsoft Edge update just got easier</t>
+  </si>
+  <si>
+    <t>Share your calendar in Outlook | Microsoft Support</t>
+  </si>
+  <si>
+    <t>Sign in to Microsoft Forms</t>
+  </si>
+  <si>
+    <t>Microsoft– AI, Cloud, Productivity, Computing, Gaming &amp; Apps</t>
+  </si>
+  <si>
+    <t>Microsoftaccount | Sign In or Create Your Account Today –Microsoft</t>
+  </si>
+  <si>
+    <t>Sign in to your account</t>
+  </si>
+  <si>
+    <t>Microsoft- Wikipedia</t>
+  </si>
+  <si>
+    <t>Microsoft365 for Individuals: Subscription for Productivity Apps</t>
+  </si>
+  <si>
+    <t>Sign in to your account - myaccount.microsoft.com</t>
+  </si>
+  <si>
+    <t>Outlook</t>
+  </si>
+  <si>
+    <t>Home |MicrosoftCareers</t>
+  </si>
+  <si>
+    <t>Create yourMicrosoftaccount</t>
+  </si>
+  <si>
+    <t>Microsoft365 - Sign into Copilot</t>
+  </si>
+  <si>
+    <t>TOP 10BEST Used Tires in Sacramento, CA- (2026 Guide) -Yelp</t>
+  </si>
+  <si>
+    <t>TOP 10 BESTUsed Tiresand Rimsin Sacramento, CA - (2026 Guide ... -Yelp</t>
+  </si>
+  <si>
+    <t>Best 30Used Tire Dealers in Sacramento, CA | superpages.com</t>
+  </si>
+  <si>
+    <t>Used Tire Dealers in Sacramento, CA- The RealYellow Pages</t>
+  </si>
+  <si>
+    <t>Best 30Tire Dealers in Sacramento, CA | superpages.com</t>
+  </si>
+  <si>
+    <t>Frank'sUsed Tires in Sacramento, CA 95820 - 916-452...</t>
+  </si>
+  <si>
+    <t>Top 30Used Tire Dealers in Sacramento, CA |DexKnows.com</t>
+  </si>
+  <si>
+    <t>Used Tires Sacramento in Sacramento, CA - The Real Yellow Pages</t>
+  </si>
+  <si>
+    <t>Auto Wheels &amp;TiresFor Sale By Owner "used tires"in Sacramento</t>
+  </si>
+  <si>
+    <t>CarTires&amp; Wheels for salein Sacramento, California - Facebook</t>
+  </si>
+  <si>
+    <t>The Home Depot</t>
+  </si>
+  <si>
+    <t>Hiring - Careers at Home Depot</t>
+  </si>
+  <si>
+    <t>Mulch - The Home Depot</t>
+  </si>
+  <si>
+    <t>Log-in To Your Profile - Careers at Home Depot</t>
+  </si>
+  <si>
+    <t>Annual Reports Recent | The Home Depot</t>
+  </si>
+  <si>
+    <t>Grants | The Home Depot</t>
+  </si>
+  <si>
+    <t>Tax Exempt | The Home Depot</t>
+  </si>
+  <si>
+    <t>SSO - Employee Sign On - The Home Depot</t>
+  </si>
+  <si>
+    <t>Path to Pro Scholarship Programs - The Home Depot</t>
+  </si>
+  <si>
+    <t>UW Homepage</t>
+  </si>
+  <si>
+    <t>Applyto the University of Washington</t>
+  </si>
+  <si>
+    <t>University of Washington-Wikipedia</t>
+  </si>
+  <si>
+    <t>UW Medicine| Nationally ranked patient care inWashingtonstate</t>
+  </si>
+  <si>
+    <t>Apply– Office of Admissions</t>
+  </si>
+  <si>
+    <t>Cost of attendance– Office of Admissions</t>
+  </si>
+  <si>
+    <t>University ofWashingtonAthletics - Official Athletics Website</t>
+  </si>
+  <si>
+    <t>MyChart- Login Page -UWMedicine</t>
+  </si>
+  <si>
+    <t>University of Washington- Profile, Rankings and Data | US News Best ...</t>
+  </si>
+  <si>
+    <t>UWLibraries</t>
+  </si>
+  <si>
+    <t>Sign in - account.microsoft.com</t>
   </si>
   <si>
     <t>Women &amp; Family Support</t>
@@ -226,187 +316,292 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a71394ab676c43ebf5dae6c5b70f15e60009e7a9b17b96e01fb697866c10df2aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c58bcbb-af98-65e1-02bc-ab5aae1964f4&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Xb21hbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fdb2f694d1ce1506461ae352ca928f08de9cbee9ec1c097415e0a676d3a857e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c58bcbb-af98-65e1-02bc-ab5aae1964f4&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3dvbWFu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8acc7c8e1aefc946e5036facc9566b9f457915d6ac3533263438f447f94a500aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c58bcbb-af98-65e1-02bc-ab5aae1964f4&amp;u=a1aHR0cHM6Ly93d3cud29tZW4uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e2db50cfd50969b8dc41635dbfb3926c5d5e3a57c6d0693f4c99302ce5f399d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c58bcbb-af98-65e1-02bc-ab5aae1964f4&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvV29tYW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fbd8d814a0fb1a51b75d94b774e9c0d1adbb3cb21981412190d9c5a58b66d0c6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c58bcbb-af98-65e1-02bc-ab5aae1964f4&amp;u=a1aHR0cHM6Ly93d3cuYmlvZ3JhcGh5LmNvbS9oaXN0b3J5LWN1bHR1cmUvZzQzMzM2MjUyL2ZhbW91cy13b21lbi1pbi1oaXN0b3J5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a92608f85f931a6edde78870651ccf181f638378db5eb5694d24559c7fb373f8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c58bcbb-af98-65e1-02bc-ab5aae1964f4&amp;u=a1aHR0cHM6Ly93d3cuZGlsbGFyZHMuY29tL2Mvd29tZW4_bXNvY2tpZD0yYzU4YmNiYmFmOTg2NWUxMDJiY2FiNWFhZTE5NjRmNA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97c358015cd82e6ed5dfbfd17d5565dd9787001f4e877cb9c3ddbc394d7b41d2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c58bcbb-af98-65e1-02bc-ab5aae1964f4&amp;u=a1aHR0cHM6Ly93d3cudGhlc2F1cnVzLmNvbS9hcnRpY2xlcy93b21hbi12cy13b21lbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d181aa8db44d717ac403a1ee1cff12c5167478ffd8f8fb4dba91f4acd6f747cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c58bcbb-af98-65e1-02bc-ab5aae1964f4&amp;u=a1aHR0cHM6Ly93d3cud29tZW5zaGlzdG9yeS5vcmcvd29tZW5zLWhpc3Rvcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=639c66bb8b292626499a3628f0349320d18f168cbab21dfef2b19876cd3dfbe4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c58bcbb-af98-65e1-02bc-ab5aae1964f4&amp;u=a1aHR0cHM6Ly93d3cuYW1hem9uLmNvbS9Xb21lbnMtRmFzaGlvbi9iP25vZGU9NzE0NzQ0MDAxMQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=216a4f9142cb207d5bb36e75b67d4043afe68b7c9beb83d4fdc2d1faf04efe58JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2c58bcbb-af98-65e1-02bc-ab5aae1964f4&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Xb21lbl9pbl90aGVfVW5pdGVkX1N0YXRlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c83e0d20f09641f40aa10305cb7caa3c4b4237fac81d45f8c93b06656419c4aeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=375a7795-7975-64a1-06dc-607478c46553&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvR2VuZGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=954c31372d0d39170f99d0573afa7f51164b03bdc94f9b22b2d80cfc3dedc3bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=375a7795-7975-64a1-06dc-607478c46553&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2dlbmRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80a4dadd39db91bc2df2e6a5083d8d77b1652ed1fe5081ff52d6ebc7c00fba25JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=375a7795-7975-64a1-06dc-607478c46553&amp;u=a1aHR0cHM6Ly93d3cuc2ltcGx5cHN5Y2hvbG9neS5vcmcvc2V4LWdlbmRlci5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4606a96351f2f2c87d20a70257dc8b01bfd715a9d26592de269d1ac1db5398e1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=375a7795-7975-64a1-06dc-607478c46553&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9oZWFsdGgtdG9waWNzL2dlbmRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dde8296981d3d0588ba537ef7c04856d4437ae93182bdf9434fdc718610faa5dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=375a7795-7975-64a1-06dc-607478c46553&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9iYXNpY3MvZ2VuZGVyP21zb2NraWQ9Mzc1YTc3OTU3OTc1NjRhMTA2ZGM2MDc0NzhjNDY1NTM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d1caf2bc344437efdb5f7e4e0b221bb7fc33f039597276cd2995e1dfe39ab32JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=375a7795-7975-64a1-06dc-607478c46553&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNpbmVuZXQuY29tL3doYXRfYXJlX3RoZV83Ml9vdGhlcl9nZW5kZXJzL2FydGljbGUuaHRt&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b72f813b15902408c9fd2f7159d928e533abe7db91e59e571459815365ecb7ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=375a7795-7975-64a1-06dc-607478c46553&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMjMyMzYz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96af94e5c34b8958730257bd172ba044ebd1a7db18e20c9ff37d77f9d950334aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=375a7795-7975-64a1-06dc-607478c46553&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGlzdF9vZl9nZW5kZXJfaWRlbnRpdGllcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f7f2007b7a7f9a4ee221851b60a6739714b63e87b6e3db9c3aaae76be285d7bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=375a7795-7975-64a1-06dc-607478c46553&amp;u=a1aHR0cHM6Ly9sZ2J0cWlhLndpa2kvd2lraS9HZW5kZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e1b0552ee31ed084219f5ccb0d183ff40dc2fbe959d5bfacb73976b3b1239587JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=375a7795-7975-64a1-06dc-607478c46553&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL0dlbmRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4fd11004ac88c03f93b48f053c0a32e5c4f19548eb7fd0ac358a3eba22a4923fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f97933c-9a7a-665a-0b09-84dd9be867ed&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GYW1pbHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c24e0a34f51db9d8adbb40bf8c335ac03887c1a141007d9ca936c32bf55053efJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f97933c-9a7a-665a-0b09-84dd9be867ed&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvZmFtaWx5LWtpbnNoaXA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f860481ec976175278e3975da396f8511f4db785f34ffc0ed3ac10ee5123dbcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f97933c-9a7a-665a-0b09-84dd9be867ed&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZhbWlseQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7c692d50f1c58187c261450b70cf66140b671894671397eb141ddd9736fdbf1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f97933c-9a7a-665a-0b09-84dd9be867ed&amp;u=a1aHR0cHM6Ly93d3cuZmFtaWx5c2VhcmNoLm9yZy9lbi91bml0ZWQtc3RhdGVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=830f953d8ae1e9accabcefc9f9d0df1a432b35257cb8aebfafe4e0346578879eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f97933c-9a7a-665a-0b09-84dd9be867ed&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vVHlwZXMtb2YtRmFtaWx5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=536e9d2d8ab7ec7a9a4b817619cc586827c4adb6a6cb4c2358f9242e5c31f1caJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f97933c-9a7a-665a-0b09-84dd9be867ed&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvRmFtaWx5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=252fa52e955ebbfac83e43a5a9e93d366d891bb00ea016ba3180f82db2b0beefJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f97933c-9a7a-665a-0b09-84dd9be867ed&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GYW1pbHlfaW5fdGhlX1VuaXRlZF9TdGF0ZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=82d841f563309ab0657e9ab583e40ed4355fe89d160ef79cfdb4ebd5b6f72b5bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f97933c-9a7a-665a-0b09-84dd9be867ed&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZhbWlseQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87cc3668924415d65e5e3bb22708d3c9006b5140372c638697f37df17021e75dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f97933c-9a7a-665a-0b09-84dd9be867ed&amp;u=a1aHR0cHM6Ly9mYW1pbHlvcmllbnRlZC5uZXQvd2hhdC1pcy1mYW1pbHkv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a6e605bce1b046c3494115208976eaf1bed5ea204ff6fcb2c6140e386c5af756JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f97933c-9a7a-665a-0b09-84dd9be867ed&amp;u=a1aHR0cHM6Ly9zaW1wbGljYWJsZS5jb20vc29jaWV0eS93aGF0LWlzLWZhbWlseQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5797bf4279e94f30d2820794a3b300e7a75045954c5870e8bbe8154af3d96518JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d9ae80e-df36-6d59-2925-ffefdece6c14&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5d6b7f15ea8eea3d41b2e1655137c106216b1168cc1824f4486903bd1803ba40JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d9ae80e-df36-6d59-2925-ffefdece6c14&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9TaW5nbGVfJTI4ZmlsbSUyOQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2ea6e7ee61d40699419d50a9b971486bedadbf629a3ec7a10624e69cb026c9ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d9ae80e-df36-6d59-2925-ffefdece6c14&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b1e9daed2673a2bd98da9b8df058c5a87ed8ee4d57bd55d74d414b071c49e9bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d9ae80e-df36-6d59-2925-ffefdece6c14&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9TaW5nbGVfKG11c2ljKQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dfa7b6e1285d079af9da2a401f13deec1bf621616a1759c5173bd546534e87d2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d9ae80e-df36-6d59-2925-ffefdece6c14&amp;u=a1aHR0cHM6Ly93d3cubWF0Y2guY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2bf448e19775c1c2a326e332f23d976b5f3dce95feb49defebe4b9cda60cd5eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d9ae80e-df36-6d59-2925-ffefdece6c14&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9ZHhSOXRDdThIX1U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=61f85854b6cdf0c6ec8ad7f43b9c6eba8452afa0e53bd9a5a797467eabac419dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d9ae80e-df36-6d59-2925-ffefdece6c14&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9ibG9nL2xpdmluZy1zaW5nbGUvMjAyMTA5L3doeS1zb21lLXBlb3BsZS1yZWFsbHktbG92ZS1iZWluZy1zaW5nbGU_bXNvY2tpZD0wZDlhZTgwZWRmMzY2ZDU5MjkyNWZmZWZkZWNlNmMxNA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91ac64bf7495165f2fde5e9708067af2fec4d24f6d953082ed6878318ad511e9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d9ae80e-df36-6d59-2925-ffefdece6c14&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvU2luZ2xlX3BlcnNvbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4aa0d01f5cc6ee6ac481b4fd45a62e9ea0e661410f2f9ccbba6e7822dd70d65fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d9ae80e-df36-6d59-2925-ffefdece6c14&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ffa58bb1b0a86f772adb76597ed0e35d6313bcb70f61d15a5e208107b3aee187JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d9ae80e-df36-6d59-2925-ffefdece6c14&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=92943bd6b332e8f3d8ef69d5dd39698d685a6b9f88778f0413b2efb1b3558a5dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=385b3097-24be-6acf-2db4-277625536baf&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=da26000c09ed06b924398ba188da0b58058f109ec5056bd134bdbdeb41f4888aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=385b3097-24be-6acf-2db4-277625536baf&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7baf404eee2d2d76aa0a22bb96f4fd8f5c579d7724b0ac5ab2a5f324fcb9ce9aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=385b3097-24be-6acf-2db4-277625536baf&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvYWJ1c2Vk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a24c16530ea09670b6a872691a8c8fb41ffff2ff1575ac12a8840186853377b8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=385b3097-24be-6acf-2db4-277625536baf&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7176bea86fbca338358028046fa395a88b93ee4e3aaec0d614a30ff287b25603JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=385b3097-24be-6acf-2db4-277625536baf&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=db7bb26d39fbf8e6c55fe6c92e98992bf7c6d07ccc2e5afb8ef1890e2326c159JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=385b3097-24be-6acf-2db4-277625536baf&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9hYnVzZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f8d1063daa8f90171331750b5d68269fa0d201097667a5ab0070215db56cf7f9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=385b3097-24be-6acf-2db4-277625536baf&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=58e1e2377de596948d729003af42efa8ab89126e0ea9bcd1d85807f137622fb5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=385b3097-24be-6acf-2db4-277625536baf&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0867d7de9afba79051e57b52d5f18d122a682871fabd638cf2c2b4dfdb2d3747JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=385b3097-24be-6acf-2db4-277625536baf&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6053dfb0b20483063bc8e8749f93bfc106794268ed30c43d8ebd2420ad83d1c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=385b3097-24be-6acf-2db4-277625536baf&amp;u=a1aHR0cHM6Ly93d3cuZGVmaW5pdGlvbnMubmV0L2RlZmluaXRpb24vYWJ1c2Vk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0fde41b99948a291256c066b9549f77b8196d11bf3268af6415b38a588d1506fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3543fc6a-d89a-6736-36e4-eb8bd943665c&amp;u=a1aHR0cHM6Ly9mcmFtZXdvcmsuc2NhbGVkYWdpbGUuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=36338b49e34fa53181fc381820174d3405d0fc0487c04f9af5dd1b06e393c713JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3543fc6a-d89a-6736-36e4-eb8bd943665c&amp;u=a1aHR0cHM6Ly93d3cuaG9tZWRlcG90LmNvbS9iL1Rvb2xzLVNhZmV0eS1TZWN1cml0eS1TYWZlcy9OLTV5YzF2WmMyYjE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d064a1b97d6026e7329dbca18c7ff7d09e2aac7658117e4651e48ce4edbdebb6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3543fc6a-d89a-6736-36e4-eb8bd943665c&amp;u=a1aHR0cHM6Ly93d3cuYW1hem9uLmNvbS9TYWZlcy9iP25vZGU9MzE4MDM3MQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=915421cd85f8954ee8760e599adfaee6cf1b0653fd531cd8a112ecf459df0727JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3543fc6a-d89a-6736-36e4-eb8bd943665c&amp;u=a1aHR0cHM6Ly9zY2FsZWRhZ2lsZS5jb20vd2hhdC1pcy1zYWZlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=56053e8acea9ec45324dbaf74c0571ed93ccafc4b1a129739bab4ec9c004e34bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3543fc6a-d89a-6736-36e4-eb8bd943665c&amp;u=a1aHR0cHM6Ly9zY2FsZWRhZ2lsZS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24e20c12ed6f5cee398ede8189ddff939fcd0e1ddf39ce30c0b9df88349da282JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3543fc6a-d89a-6736-36e4-eb8bd943665c&amp;u=a1aHR0cHM6Ly93d3cuaG9tZWRlcG90LmNvbS9iL1Rvb2xzLVNhZmV0eS1TZWN1cml0eS1TYWZlcy1Ib21lLVNhZmVzL04tNXljMXZaYzI5bg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=610ac5fef7d82a86db311f330d9df4175254b1c91ac0c8fb0b7f4960ff91f4f3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3543fc6a-d89a-6736-36e4-eb8bd943665c&amp;u=a1aHR0cHM6Ly93d3cuY29zdGNvLmNvbS9oYXJkd2FyZS1zYWZlcy5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ad0521b99dc8b2348de666ad7d5cc68a1076b10ebc2a35286958b416932fa90eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3543fc6a-d89a-6736-36e4-eb8bd943665c&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2NhbGVkX2FnaWxlX2ZyYW1ld29yaw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ab5ea10e8d9f0735970fafa1577692c8c72b4e8f97a6b15de21e5d41ab97ea4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3543fc6a-d89a-6736-36e4-eb8bd943665c&amp;u=a1aHR0cHM6Ly93d3cubG93ZXMuY29tL3BsL3NhZmVzLzQyOTQ4MDYzNTM_bXNvY2tpZD0zNTQzZmM2YWQ4OWE2NzM2MzZlNGViOGJkOTQzNjY1Yw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4572c42275684c805f6457424e96807dad0b15ec6754aa5f7192b17577b827e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3543fc6a-d89a-6736-36e4-eb8bd943665c&amp;u=a1aHR0cHM6Ly93d3cuc2VudHJ5c2FmZS5jb20v&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=98b6e5904bad4a86eaafbf9c4f1e26ef8c2bf4cafe324e383ce6dfc56384b38fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=189df1a9-b6ff-60ec-0287-e648b76361f6&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV29tYW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2472556867a840ca3fa63199017f2b1b6ae2ff16a2ada05f95fa71ef67de692cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=189df1a9-b6ff-60ec-0287-e648b76361f6&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL1dvbWFu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9c224201dff2091061ac8f9f696fbee82f19054ca936b36ad0619d5cf640d489JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=189df1a9-b6ff-60ec-0287-e648b76361f6&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3dvbWFu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3fba2d20a74d9f87a0f6730f4d2f7d041a40ae7f9c8dc473ec7df770c97946e5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=189df1a9-b6ff-60ec-0287-e648b76361f6&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmVtYWxl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e7c1b4a217d368f79ff37bd218e35e1cf6d72501c8d4a7850ee54f7aff4985d4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=189df1a9-b6ff-60ec-0287-e648b76361f6&amp;u=a1aHR0cHM6Ly93d3cud29tZW4uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6078e8da363e75c8ebf959b8fd36d61fdb91d9c81bf04834dfaf51656161f0aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=189df1a9-b6ff-60ec-0287-e648b76361f6&amp;u=a1aHR0cHM6Ly93d3cuYmlvZ3JhcGh5LmNvbS9oaXN0b3J5LWN1bHR1cmUvZzQzMzM2MjUyL2ZhbW91cy13b21lbi1pbi1oaXN0b3J5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=af284bfb455380e26504b6b00d46abfa6d9a2b730434418318d9917610ee18b8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=189df1a9-b6ff-60ec-0287-e648b76361f6&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvd29tZW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=567a27d05e22bc36ac2f97e38ddc5036210824fe47ccf98f5efdd5afb7fee7e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=189df1a9-b6ff-60ec-0287-e648b76361f6&amp;u=a1aHR0cHM6Ly93d3cud29tZW5zaGlzdG9yeS5vcmcvd29tZW5zLWhpc3Rvcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=86d02d701b5f81f198edbfeab6c8b92f88dacf89d2931e4a23c85b6dc2bb7bbeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=189df1a9-b6ff-60ec-0287-e648b76361f6&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL2xpZmVhbmRzdHlsZS93b21lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=858271376fb719af64eb9413954ea18f29bdb4d4d051aa0fe419bf023186d2f7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=189df1a9-b6ff-60ec-0287-e648b76361f6&amp;u=a1aHR0cHM6Ly93d3cubm9yZHN0cm9tLmNvbS9icm93c2Uvd29tZW4_bXNvY2tpZD0xODlkZjFhOWI2ZmY2MGVjMDI4N2U2NDhiNzYzNjFmNg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07269579b9aaaca58be4897e418e081bb45ccf4422542802f8a0c11f8789ca73JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f509332-d24d-6049-1461-84d3d3c961ff&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9HZW5kZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fed68d0cd8bdcb6932d0e9551901683552c625b42bdea32dabd30ff222377239JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f509332-d24d-6049-1461-84d3d3c961ff&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2dlbmRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72de0c1c6c50df0b02953df65d5b620f3b11b9735090c898d0506a0eac338bc2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f509332-d24d-6049-1461-84d3d3c961ff&amp;u=a1aHR0cHM6Ly93d3cuc2ltcGx5cHN5Y2hvbG9neS5vcmcvc2V4LWdlbmRlci5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=08cd0362fa40d36b12f5c95d02d3915996a60cbe2a396495d8970c4a8f7b59efJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f509332-d24d-6049-1461-84d3d3c961ff&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9oZWFsdGgtdG9waWNzL2dlbmRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71c8a459be548305ab11cddb881cd5311132f972b0d12c5b8622de16e6d63daeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f509332-d24d-6049-1461-84d3d3c961ff&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9iYXNpY3MvZ2VuZGVyP21zb2NraWQ9MWY1MDkzMzJkMjRkNjA0OTE0NjE4NGQzZDNjOTYxZmY&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=67b5fb914ce89fb5cd8264aea96e2627a2aded874577d0c67f479ba421267d39JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f509332-d24d-6049-1461-84d3d3c961ff&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNpbmVuZXQuY29tL3doYXRfYXJlX3RoZV83Ml9vdGhlcl9nZW5kZXJzL2FydGljbGUuaHRt&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=676c60f388aa285bc29254a6628ec2d885738ec8eb361097487e2936d0c977e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f509332-d24d-6049-1461-84d3d3c961ff&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9MaXN0X29mX2dlbmRlcl9pZGVudGl0aWVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f87eee2209078ed94b3ec3f2978a7b8ffeb3f73103cd4f67014601428ab8f999JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f509332-d24d-6049-1461-84d3d3c961ff&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMjMyMzYz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=084e89e69c96d771cd523000f09a1500dad45d0624f99bb5fc8ed4a27573bc7aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f509332-d24d-6049-1461-84d3d3c961ff&amp;u=a1aHR0cHM6Ly9sZ2J0cWlhLndpa2kvd2lraS9HZW5kZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fdf3051801d865fedbc46527c6bc2007357e4ba161241eab1d288f1ee77287dbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1f509332-d24d-6049-1461-84d3d3c961ff&amp;u=a1aHR0cHM6Ly9tZWRlZHVjYXRpb24uc3RhbmZvcmQuZWR1L2dsb3NzYXJ5L2dlbmRlci8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a694d75448236c427aaf51462f6694d474687b41c5a917cfb66a27ac1bd7f98JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=004fce77-af68-6d42-2cb6-d996ae1c6caf&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GYW1pbHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f98499ae830c7f56d608645887bd19cdda2271931403fdc9b2ca6192586d5c6aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=004fce77-af68-6d42-2cb6-d996ae1c6caf&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvZmFtaWx5LWtpbnNoaXA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5ab2395601225c40865d0c2a13390ba05c525480ccbf15550eeb3a2bb8b50565JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=004fce77-af68-6d42-2cb6-d996ae1c6caf&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZhbWlseQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3c51ecddf12606b880ba7e2ae8ec231309746f1466e8eff50cb27ded6355e5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=004fce77-af68-6d42-2cb6-d996ae1c6caf&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvRmFtaWx5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c992c27268408a57ed87f561f8b879d544e1387a7790c9e4e82b10c07c77172JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=004fce77-af68-6d42-2cb6-d996ae1c6caf&amp;u=a1aHR0cHM6Ly93d3cuZmFtaWx5c2VhcmNoLm9yZy9lbi91bml0ZWQtc3RhdGVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b5e8e11f0b47c43045bc15c90b9a269fe04cfd94781c146617af42aa9625e59dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=004fce77-af68-6d42-2cb6-d996ae1c6caf&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vVHlwZXMtb2YtRmFtaWx5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=625c41212f6ca0c8c22e2408836def1852f555fa893f540c3c8bda070ad7d882JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=004fce77-af68-6d42-2cb6-d996ae1c6caf&amp;u=a1aHR0cHM6Ly9mYW1pbHlvcmllbnRlZC5uZXQvd2hhdC1pcy1mYW1pbHkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=29227bb27a17236b9252e9accc0d086bc97d0f47f82774919c619da2e8a9548fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=004fce77-af68-6d42-2cb6-d996ae1c6caf&amp;u=a1aHR0cHM6Ly9zaW1wbGljYWJsZS5jb20vc29jaWV0eS93aGF0LWlzLWZhbWlseQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=644b20f4d56fd29e69de87e84a88ec07d3b9885facee7e1ad8c826ab8afac716JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=004fce77-af68-6d42-2cb6-d996ae1c6caf&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GYW1pbHlfaW5fdGhlX1VuaXRlZF9TdGF0ZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=03046a2b907f44533312a0a7f86e7f49afe9609c9bb16b0c8a79f66e217994f5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=004fce77-af68-6d42-2cb6-d996ae1c6caf&amp;u=a1aHR0cHM6Ly93d3cubG92ZXRva25vdy5jb20vbGlmZS9yZWxhdGlvbnNoaXBzL21lYW5pbmctZmFtaWx5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2bcade84ee35ce717c238e057320fbc918d28250c49117cb9492e7fe3bf9032eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133aff4f-fe26-61ef-1ae6-e8aeff3860e3&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aae245980ce1fbbe4d02070ecf906e26569418e873c079e287804f7fb6a3aa6aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133aff4f-fe26-61ef-1ae6-e8aeff3860e3&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2luZ2xlXyhmaWxtKQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ad4000e6e7043d3f46d8326a70a0e3f4c6fd405a96b5d03beb174455400f592bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133aff4f-fe26-61ef-1ae6-e8aeff3860e3&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24cdc4ab24595c78168a775aeaf4d4854bbbf590773eff9db21f510515928f41JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133aff4f-fe26-61ef-1ae6-e8aeff3860e3&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2luZ2xl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=53658a6c0508b690243bfa2931a5af55b6c0c4736534d5902b011a841d4f2b0fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133aff4f-fe26-61ef-1ae6-e8aeff3860e3&amp;u=a1aHR0cHM6Ly93d3cubWF0Y2guY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9196bb8cd666c6c25c3b7dd422a5a45457e01b6b6debe1b65f20d997027aaf5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133aff4f-fe26-61ef-1ae6-e8aeff3860e3&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9ibG9nL2xpdmluZy1zaW5nbGUvMjAyMTA5L3doeS1zb21lLXBlb3BsZS1yZWFsbHktbG92ZS1iZWluZy1zaW5nbGU_bXNvY2tpZD0xMzNhZmY0ZmZlMjY2MWVmMWFlNmU4YWVmZjM4NjBlMw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=853217da5b4a57be759c4dace73a253d47da9502563dde3b4541072ba8951773JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133aff4f-fe26-61ef-1ae6-e8aeff3860e3&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1malY3a3JtWW9iSQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a40a71c662fa8baec210bf3da1da4a30d23384d0a258f99f0aa154515414401JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133aff4f-fe26-61ef-1ae6-e8aeff3860e3&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5231e62436a3709ab36f99b7a8a1d8debe970104365098529d461012dfe889a8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133aff4f-fe26-61ef-1ae6-e8aeff3860e3&amp;u=a1aHR0cHM6Ly93d3cuZWhhcm1vbnkuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dbf912c1ffb14004c35339880cab5166331a5cd649a6a3d0da50b07c93b09b67JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133aff4f-fe26-61ef-1ae6-e8aeff3860e3&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80548a9fee233080b83f29fc77f7f9afd941761d553bbef5f3b72c218db0dd6fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2befa160-3fc1-6959-05f4-b6813e1d68a5&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tZ2IvY29udGFjdHVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d884817882d36f4c6d50d1c9550d08d2142c93420f5a8ac6877d76df9825f537JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2befa160-3fc1-6959-05f4-b6813e1d68a5&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZGUtZGUvYWNjb3VudHMtYmlsbGluZy9tYW5hZ2UvaG93LXRvLXNpZ24taW4tdG8taG90bWFpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=668d23d6ccde09cdaf2519e82c9287774af91efd3591a9c72001d1519ea5a08bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2befa160-3fc1-6959-05f4-b6813e1d68a5&amp;u=a1aHR0cHM6Ly90ZWNoY29tbXVuaXR5Lm1pY3Jvc29mdC5jb20vY2F0ZWdvcnkvbWljcm9zb2Z0LWNvcGlsb3QvYmxvZy9taWNyb3NvZnQtY29waWxvdC1ibG9n&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4398190f469871b98fb6a0ab86f5d2db710f5d7a0c1662401c5f75b8952d538fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2befa160-3fc1-6959-05f4-b6813e1d68a5&amp;u=a1aHR0cHM6Ly90ZWNoY29tbXVuaXR5Lm1pY3Jvc29mdC5jb20vYmxvZy9leGNoYW5nZS9leGNoYW5nZS1vbmxpbmUtZXdzLXlvdXItdGltZS1pcy1hbG1vc3QtdXAvNDQ5MjM2MQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b82461b81280f6b1a6b76163680ecb9b033fe1305d266529cf319563f538a4ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2befa160-3fc1-6959-05f4-b6813e1d68a5&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvd2luZG93cy9kZXBsb3ltZW50L2luc3RhbGwtdXBncmFkZS9nZXR0aW5nLXJlYWR5LWZvci10aGUtd2luZG93cy0xMS11cGdyYWRl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=31632b9fbf12e62fa3f1bf368ef1c317a97f5a2e134b2e655619d83263003e1dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2befa160-3fc1-6959-05f4-b6813e1d68a5&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZnItZnIvd2luZG93cy9tZXR0cmUtJUMzJUEwLWpvdXItbGVzLXBpbG90ZXMtdmlhLWdlc3Rpb25uYWlyZS1kZS1wJUMzJUE5cmlwaCVDMyVBOXJpcXVlcy1kYW5zLXdpbmRvd3MtZWM2MmY0NmMtZmYxNC1jOTFkLWVlYWQtZDcxMjZkYzFmN2I2&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=28001734850e0fc93c7e530e63d2cdd81ad5602c85e65ac1d8021dd6fbe77887JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2befa160-3fc1-6959-05f4-b6813e1d68a5&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZGUtZGUvd2luZG93cy9ha3R1YWxpc2llcmVuLXZvbi10cmVpYmVybi0lQzMlQkNiZXItZ2VyJUMzJUE0dGUtbWFuYWdlci1pbi13aW5kb3dzLWVjNjJmNDZjLWZmMTQtYzkxZC1lZWFkLWQ3MTI2ZGMxZjdiNg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=05217b16c7211936a0c1a0c30ee4497c284975ab97b074caa55d490ad38d93e9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2befa160-3fc1-6959-05f4-b6813e1d68a5&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvZWRnZS9nZXR0aW5nLXRoZS1sYXRlc3QtbWljcm9zb2Z0LWVkZ2UtdXBkYXRlLWp1c3QtZ290LWVhc2llcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f4e1347ad04e2bbdeefa3365b8ba21776b2d5781bdee978cc5ac48393d8c17abJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2befa160-3fc1-6959-05f4-b6813e1d68a5&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvb3V0bG9vay90cmFpbmluZy9zaGFyZS15b3VyLWNhbGVuZGFyLWluLW91dGxvb2s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f40263793900a3c488a46c026fb9b765ab74bd866320d90adac63bd6eeca2199JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2befa160-3fc1-6959-05f4-b6813e1d68a5&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvZm9ybXMvc2lnbi1pbi10by1taWNyb3NvZnQtZm9ybXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45e3dca16f6f28a942c067055b6ff63fc748fe168486e674da0ec8cb855ce0acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a398c24-7418-6e8d-3dae-9bc575966f5d&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cz9tc29ja2lkPTBhMzk4YzI0NzQxODZlOGQzZGFlOWJjNTc1OTY2ZjVk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11d187d98003fdd7950f48ea9216a7302d5cd5f8ac93a9abb23fbd57350ffd71JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a398c24-7418-6e8d-3dae-9bc575966f5d&amp;u=a1aHR0cHM6Ly9hY2NvdW50Lm1pY3Jvc29mdC5jb20vYWNjb3VudA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de59cfc72482a4518630ca8a95d15458bbe21b8ad91c2144f42d221fb631ce25JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a398c24-7418-6e8d-3dae-9bc575966f5d&amp;u=a1aHR0cHM6Ly9teWFjY291bnQubWljcm9zb2Z0LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be75f4f5d233676925cf97bf747fb27401a52efade019889d39796a516421791JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a398c24-7418-6e8d-3dae-9bc575966f5d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWljcm9zb2Z0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b97da115e430c13484ba34b9ea395fa84d327d002e140d66ff597880772dffcfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a398c24-7418-6e8d-3dae-9bc575966f5d&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cy9taWNyb3NvZnQtMzY1P21zb2NraWQ9MGEzOThjMjQ3NDE4NmU4ZDNkYWU5YmM1NzU5NjZmNWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=da75634802bd2a399d2376d05e999fa2f3703020a7fd5f3fcc0880675581bcc5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a398c24-7418-6e8d-3dae-9bc575966f5d&amp;u=a1aHR0cHM6Ly9teWFjY291bnQubWljcm9zb2Z0LmNvbS9sb2dpbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dac9728f2b3902d8b2e4797af55a082e0ba2c4dfab62c2730e8dbbfa0cedb69dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a398c24-7418-6e8d-3dae-9bc575966f5d&amp;u=a1aHR0cHM6Ly9vdXRsb29rLm9mZmljZS5jb20vbWFpbC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=558314c1d7bd6c70262fbdc6a51681753998f77184441ee9dbbfff60ad654c03JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a398c24-7418-6e8d-3dae-9bc575966f5d&amp;u=a1aHR0cHM6Ly9jYXJlZXJzLm1pY3Jvc29mdC5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1414032a73caf0e00fbb1fc534156885a3d4aa88098e2b295e6dd5d8b40e6807JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a398c24-7418-6e8d-3dae-9bc575966f5d&amp;u=a1aHR0cHM6Ly9zaWdudXAubGl2ZS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e6d5ad565a010b9504279c82b47bdd1d56b18f444e0cafde9b731590c28e5336JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0a398c24-7418-6e8d-3dae-9bc575966f5d&amp;u=a1aHR0cHM6Ly9tMzY1LmNsb3VkLm1pY3Jvc29mdC8_b3JpZ2luZG9tYWluPW1pY3Jvc29mdDM2NQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0b3a9afaaf3d72f0e198c06cce52fb0a1a3dfa4de3e312ce79c8b738b9ba79b3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09624590-deef-6317-22d7-5271df0b6252&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1Vc2VkK1RpcmVzJmZpbmRfbG9jPVNhY3JhbWVudG8lMkMrQ0EmbXNvY2tpZD0wOTYyNDU5MGRlZWY2MzE3MjJkNzUyNzFkZjBiNjI1Mg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d5ca9e67e2360f69e00e9e33b310621f3aadf1cf12c1045d861ebba0a6fa6b3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09624590-deef-6317-22d7-5271df0b6252&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz11c2VkK3RpcmVzK2FuZCtyaW1zJmZpbmRfbG9jPVNhY3JhbWVudG8lMkMrQ0EmbXNvY2tpZD0wOTYyNDU5MGRlZWY2MzE3MjJkNzUyNzFkZjBiNjI1Mg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f7e9cc81424798f8a3a2b76db476cf3fb875f858371eef4d6f8eb288c4496fc8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09624590-deef-6317-22d7-5271df0b6252&amp;u=a1aHR0cHM6Ly93d3cuc3VwZXJwYWdlcy5jb20vc2FjcmFtZW50by1jYS91c2VkLXRpcmVzLWFuZC1yaW1z&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=104c8fc44ddfbca3f64e19b260c11659d7e231008599ed9238c4751243868af1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09624590-deef-6317-22d7-5271df0b6252&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL3NhY3JhbWVudG8tY2EvdXNlZC10aXJlLWRlYWxlcnM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8accb007d7fd3d4c42d18a974595b26a65ecce2c4eaa4a927b97369fb16efcf5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09624590-deef-6317-22d7-5271df0b6252&amp;u=a1aHR0cHM6Ly93d3cuc3VwZXJwYWdlcy5jb20vc2FjcmFtZW50by1jYS91c2VkLWF1dG8tdGlyZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=962bb3e62875b6606fbc087638e47feb89a9616ea2e36cf5207067e3acc3b5a4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09624590-deef-6317-22d7-5271df0b6252&amp;u=a1aHR0cHM6Ly93d3cuY2hhbWJlcm9mY29tbWVyY2UuY29tL2J1c2luZXNzLWRpcmVjdG9yeS9jYWxpZm9ybmlhL3NhY3JhbWVudG8vdXNlZC10aXJlLXNob3AvMjAwMDUxNTQ3MS1mcmFuay1zLXVzZWQtdGlyZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=989ec59f9a3033065900f1a520659189dbba82401501ffddecd6b036bb2644a3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09624590-deef-6317-22d7-5271df0b6252&amp;u=a1aHR0cHM6Ly93d3cuZGV4a25vd3MuY29tL3NhY3JhbWVudG8tY2EvdXNlZC10aXJlLWRlYWxlcnM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a04c93baac4e44871ed08dc5b8b749611542eb7281e7fc60685d69e2258d48c3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09624590-deef-6317-22d7-5271df0b6252&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL3NhY3JhbWVudG8tY2EvdXNlZC10aXJlcy1zYWNyYW1lbnRv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c820bb7555bb29fd3ab00e4470e87c1b368b65739ce60b92896778b7e03cacd8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09624590-deef-6317-22d7-5271df0b6252&amp;u=a1aHR0cHM6Ly93d3cuY3JhaWdzbGlzdC5vcmcvc2VhcmNoL2FyZWEvc2FjcmFtZW50bz9jYXQ9d3RhJnB1cnZleW9yPW93bmVyJnF1ZXJ5PXVzZWQlMjB0aXJlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fa62bdd702b65b191cfd4da06f93a32591d2a7f6c283d1b309101054063b27ddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09624590-deef-6317-22d7-5271df0b6252&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL21hcmtldHBsYWNlL3NhYy9jYXItdGlyZXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7b12d892266bc4715d6bf7af09271b3853d0cc14dc2941da6d38cdc9f989a7a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172e4e8d-06f6-6a40-3263-596c07bc6b3c&amp;u=a1aHR0cHM6Ly93d3cuaG9tZWRlcG90LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d84fa550be3342f383e3580a8126529fa40cbe5595e104c32b4d753082e9699JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172e4e8d-06f6-6a40-3263-596c07bc6b3c&amp;u=a1aHR0cHM6Ly9jYXJlZXJzLmhvbWVkZXBvdC5jb20vaGlyaW5nLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=26635681fcc57ee56819f0052900f5cfb7b68226fe11dac95508c06e27c075a9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172e4e8d-06f6-6a40-3263-596c07bc6b3c&amp;u=a1aHR0cHM6Ly93d3cuaG9tZWRlcG90LmNvbS9iL091dGRvb3JzLUdhcmRlbi1DZW50ZXItTGFuZHNjYXBpbmctU3VwcGxpZXMtTXVsY2gvTi01eWMxdlpieDRh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6f61ab699c29326dfeb92b724b2acd3d26c88e07ff9415d7bb56dc8f5ea61c37JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172e4e8d-06f6-6a40-3263-596c07bc6b3c&amp;u=a1aHR0cHM6Ly9jYXJlZXJzLmhvbWVkZXBvdC5jb20vcHJvZmlsZS9sb2dpbi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2d367eca821ccfa534f27ee520ce2d21a2f895f648046f07cb87f859b848a94JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172e4e8d-06f6-6a40-3263-596c07bc6b3c&amp;u=a1aHR0cHM6Ly9pci5ob21lZGVwb3QuY29tL2ZpbmFuY2lhbC1yZXBvcnRzL2FubnVhbC1yZXBvcnRzL3JlY2VudA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eacfa768983be461d83920f7cc7039dc20e07cc43ab880b28a39c9c55e9996cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172e4e8d-06f6-6a40-3263-596c07bc6b3c&amp;u=a1aHR0cHM6Ly9jb3Jwb3JhdGUuaG9tZWRlcG90LmNvbS9wYWdlL2dyYW50cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eb59de4e7fb292616c4c7c1930e54010739ca01e0056b11a24e670a3cf9dd685JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172e4e8d-06f6-6a40-3263-596c07bc6b3c&amp;u=a1aHR0cHM6Ly90YXgtZXhlbXB0LmhvbWVkZXBvdC5jb20vbG9naW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=26671dca2032cb6fa905139644aeda48a69fb08fa9ae37d19ed208dc09d97f1cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172e4e8d-06f6-6a40-3263-596c07bc6b3c&amp;u=a1aHR0cHM6Ly90aGRzYW1sLmhvbWVkZXBvdC5jb20vdGhkc3NvL2xvZ29uLmpzcA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0326cbbc5d276568734155208433630556bdc89124210ea4b32c036a1290db5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172e4e8d-06f6-6a40-3263-596c07bc6b3c&amp;u=a1aHR0cHM6Ly9jb3Jwb3JhdGUuaG9tZWRlcG90LmNvbS9wYWdlL3BhdGgtcHJvLXNjaG9sYXJzaGlwLXByb2dyYW1z&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87a443126902aaf67d930606b8fb70eb227f353cb1a55d1cddb0f2f95b0d7ee9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f8b7117-bc05-692d-197e-66f6bd826868&amp;u=a1aHR0cHM6Ly93d3cud2FzaGluZ3Rvbi5lZHUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=48dedaa5a8e4d97d30bef2bfb73ad3eb1b290fd5184208fa2e82132c7b71a49cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f8b7117-bc05-692d-197e-66f6bd826868&amp;u=a1aHR0cHM6Ly93d3cud2FzaGluZ3Rvbi5lZHUvYWRtaXNzaW9ucy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a5c4331b18dc966f31cf799cd3c2b7713b620f031e8b8eaf01e5ebb9f7b41c1cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f8b7117-bc05-692d-197e-66f6bd826868&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Vbml2ZXJzaXR5X29mX1dhc2hpbmd0b24&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fcd3ec30d2c5f5b11b2684b0982219df151115b027b55f05881c384a6ff25888JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f8b7117-bc05-692d-197e-66f6bd826868&amp;u=a1aHR0cHM6Ly93d3cudXdtZWRpY2luZS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bfd0a4adefbc9ea9d21e2458852689cd11adc4297413d780abb07cf7570a65a8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f8b7117-bc05-692d-197e-66f6bd826868&amp;u=a1aHR0cHM6Ly9hZG1pdC53YXNoaW5ndG9uLmVkdS9BcHBseS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4408972ec07daa2bde0662fa056dee8743938163340f98d84a4bb19f0f051c2aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f8b7117-bc05-692d-197e-66f6bd826868&amp;u=a1aHR0cHM6Ly9hZG1pdC53YXNoaW5ndG9uLmVkdS9jb3N0cy9jb2Ev&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=06d8e6dbbfde581ecfba338d010337ceaaff8398ee59ab826cffba98f281480eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f8b7117-bc05-692d-197e-66f6bd826868&amp;u=a1aHR0cHM6Ly9nb2h1c2tpZXMuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f82a36704a2f730bdccaa1c497387f3d9c394bf0c30e8526c94bc3076f59b4acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f8b7117-bc05-692d-197e-66f6bd826868&amp;u=a1aHR0cHM6Ly9teWNoYXJ0LnV3bWVkaWNpbmUub3JnL1BST0QwMS9BdXRoZW50aWNhdGlvbi9Mb2dpbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c517f3f9de34578806061ab968c96c6b28fbd50396ab6611f005acfb1d2df165JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f8b7117-bc05-692d-197e-66f6bd826868&amp;u=a1aHR0cHM6Ly93d3cudXNuZXdzLmNvbS9iZXN0LWNvbGxlZ2VzL3VuaXZlcnNpdHktb2Ytd2FzaGluZ3Rvbi0zNzk4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a2d0a1d49298fec10e7024cea1af1f6dc11abb28a2db2d20bea040891ef1d34JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f8b7117-bc05-692d-197e-66f6bd826868&amp;u=a1aHR0cHM6Ly9saWIudXcuZWR1Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9513071eac419dd0dea425003e5399ce6a6dbdd20bfb0fea1141c7add4e8ca7bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1890a9fb-8faf-67ed-2e9c-be1a8e9866bc&amp;u=a1aHR0cHM6Ly9hY2NvdW50Lm1pY3Jvc29mdC5jb20vYWNjb3VudC1jaGVja3Vw&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
+  </si>
+  <si>
+    <t>Sea Point</t>
+  </si>
+  <si>
+    <t>Green Point</t>
+  </si>
+  <si>
+    <t>Woodstock</t>
+  </si>
+  <si>
+    <t>Observatory</t>
+  </si>
+  <si>
+    <t>Salt River</t>
   </si>
   <si>
     <t>Bing</t>
@@ -754,7 +949,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -788,19 +983,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G2" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H2" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -808,19 +1003,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="G3" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H3" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -828,19 +1023,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H4" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -848,19 +1043,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H5" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -868,19 +1063,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H6" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -888,19 +1083,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="G7" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H7" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -908,19 +1103,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="G8" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H8" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -928,19 +1123,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="G9" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H9" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -948,19 +1143,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="G10" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H10" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -968,19 +1163,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="G11" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H11" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -988,19 +1183,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="G12" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H12" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1008,19 +1203,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="G13" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H13" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1028,19 +1223,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="G14" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H14" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1048,19 +1243,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="G15" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H15" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1068,19 +1263,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="G16" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H16" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1088,19 +1283,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="G17" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H17" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1108,19 +1303,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="G18" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H18" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1128,19 +1323,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="G19" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H19" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1148,19 +1343,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="G20" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H20" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1168,19 +1363,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="G21" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H21" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1188,19 +1383,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G22" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H22" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1208,19 +1403,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="G23" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H23" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1228,19 +1423,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="G24" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H24" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1248,19 +1443,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G25" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H25" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1268,19 +1463,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="G26" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H26" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1288,19 +1483,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="G27" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H27" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1308,19 +1503,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="G28" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H28" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1328,19 +1523,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="G29" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H29" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1348,19 +1543,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="G30" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H30" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1368,19 +1563,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="G31" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H31" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1388,19 +1583,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="G32" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H32" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1408,19 +1603,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="G33" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H33" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1428,19 +1623,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="G34" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H34" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1448,19 +1643,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="G35" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H35" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1468,19 +1663,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="G36" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H36" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1488,19 +1683,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C37" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="G37" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H37" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1508,19 +1703,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C38" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="G38" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H38" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1528,19 +1723,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C39" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="G39" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H39" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1548,19 +1743,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C40" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="G40" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H40" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1568,19 +1763,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C41" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="G41" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H41" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1588,19 +1783,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C42" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="G42" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H42" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1608,19 +1803,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C43" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G43" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H43" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1628,19 +1823,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C44" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="G44" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H44" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1648,19 +1843,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C45" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="G45" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H45" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1668,19 +1863,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C46" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="G46" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H46" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1688,19 +1883,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="G47" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H47" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1708,19 +1903,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C48" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="G48" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H48" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1728,19 +1923,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C49" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="G49" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H49" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1748,19 +1943,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C50" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="G50" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H50" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1768,19 +1963,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C51" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="G51" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H51" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1788,19 +1983,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C52" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G52" t="s">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="H52" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1808,19 +2003,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C53" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="G53" t="s">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="H53" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1828,19 +2023,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C54" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="G54" t="s">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="H54" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -1848,19 +2043,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C55" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="G55" t="s">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="H55" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -1868,19 +2063,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C56" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="G56" t="s">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="H56" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -1888,19 +2083,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C57" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="G57" t="s">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="H57" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -1908,19 +2103,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C58" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="G58" t="s">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="H58" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -1928,19 +2123,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C59" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="G59" t="s">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="H59" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -1948,19 +2143,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C60" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="G60" t="s">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="H60" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -1968,19 +2163,619 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
+        <v>98</v>
+      </c>
+      <c r="C61" t="s">
+        <v>99</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G61" t="s">
+        <v>191</v>
+      </c>
+      <c r="H61" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
         <v>68</v>
       </c>
-      <c r="C61" t="s">
+      <c r="B62" t="s">
+        <v>98</v>
+      </c>
+      <c r="C62" t="s">
+        <v>99</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G62" t="s">
+        <v>192</v>
+      </c>
+      <c r="H62" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
         <v>69</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G61" t="s">
-        <v>130</v>
-      </c>
-      <c r="H61" t="s">
-        <v>131</v>
+      <c r="B63" t="s">
+        <v>98</v>
+      </c>
+      <c r="C63" t="s">
+        <v>99</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G63" t="s">
+        <v>192</v>
+      </c>
+      <c r="H63" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" t="s">
+        <v>98</v>
+      </c>
+      <c r="C64" t="s">
+        <v>99</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G64" t="s">
+        <v>192</v>
+      </c>
+      <c r="H64" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" t="s">
+        <v>98</v>
+      </c>
+      <c r="C65" t="s">
+        <v>99</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G65" t="s">
+        <v>192</v>
+      </c>
+      <c r="H65" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" t="s">
+        <v>98</v>
+      </c>
+      <c r="C66" t="s">
+        <v>99</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G66" t="s">
+        <v>192</v>
+      </c>
+      <c r="H66" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" t="s">
+        <v>98</v>
+      </c>
+      <c r="C67" t="s">
+        <v>99</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G67" t="s">
+        <v>192</v>
+      </c>
+      <c r="H67" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" t="s">
+        <v>98</v>
+      </c>
+      <c r="C68" t="s">
+        <v>99</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G68" t="s">
+        <v>192</v>
+      </c>
+      <c r="H68" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" t="s">
+        <v>98</v>
+      </c>
+      <c r="C69" t="s">
+        <v>99</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G69" t="s">
+        <v>192</v>
+      </c>
+      <c r="H69" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" t="s">
+        <v>98</v>
+      </c>
+      <c r="C70" t="s">
+        <v>99</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G70" t="s">
+        <v>192</v>
+      </c>
+      <c r="H70" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" t="s">
+        <v>98</v>
+      </c>
+      <c r="C71" t="s">
+        <v>99</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G71" t="s">
+        <v>192</v>
+      </c>
+      <c r="H71" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" t="s">
+        <v>98</v>
+      </c>
+      <c r="C72" t="s">
+        <v>99</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G72" t="s">
+        <v>193</v>
+      </c>
+      <c r="H72" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" t="s">
+        <v>98</v>
+      </c>
+      <c r="C73" t="s">
+        <v>99</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G73" t="s">
+        <v>193</v>
+      </c>
+      <c r="H73" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" t="s">
+        <v>98</v>
+      </c>
+      <c r="C74" t="s">
+        <v>99</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G74" t="s">
+        <v>193</v>
+      </c>
+      <c r="H74" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" t="s">
+        <v>98</v>
+      </c>
+      <c r="C75" t="s">
+        <v>99</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G75" t="s">
+        <v>193</v>
+      </c>
+      <c r="H75" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" t="s">
+        <v>98</v>
+      </c>
+      <c r="C76" t="s">
+        <v>99</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G76" t="s">
+        <v>193</v>
+      </c>
+      <c r="H76" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" t="s">
+        <v>98</v>
+      </c>
+      <c r="C77" t="s">
+        <v>99</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
+        <v>193</v>
+      </c>
+      <c r="H77" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" t="s">
+        <v>98</v>
+      </c>
+      <c r="C78" t="s">
+        <v>99</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G78" t="s">
+        <v>193</v>
+      </c>
+      <c r="H78" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" t="s">
+        <v>98</v>
+      </c>
+      <c r="C79" t="s">
+        <v>99</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G79" t="s">
+        <v>193</v>
+      </c>
+      <c r="H79" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" t="s">
+        <v>98</v>
+      </c>
+      <c r="C80" t="s">
+        <v>99</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G80" t="s">
+        <v>193</v>
+      </c>
+      <c r="H80" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" t="s">
+        <v>98</v>
+      </c>
+      <c r="C81" t="s">
+        <v>99</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G81" t="s">
+        <v>194</v>
+      </c>
+      <c r="H81" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" t="s">
+        <v>98</v>
+      </c>
+      <c r="C82" t="s">
+        <v>99</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G82" t="s">
+        <v>194</v>
+      </c>
+      <c r="H82" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" t="s">
+        <v>98</v>
+      </c>
+      <c r="C83" t="s">
+        <v>99</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G83" t="s">
+        <v>194</v>
+      </c>
+      <c r="H83" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" t="s">
+        <v>98</v>
+      </c>
+      <c r="C84" t="s">
+        <v>99</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G84" t="s">
+        <v>194</v>
+      </c>
+      <c r="H84" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" t="s">
+        <v>98</v>
+      </c>
+      <c r="C85" t="s">
+        <v>99</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G85" t="s">
+        <v>194</v>
+      </c>
+      <c r="H85" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" t="s">
+        <v>92</v>
+      </c>
+      <c r="B86" t="s">
+        <v>98</v>
+      </c>
+      <c r="C86" t="s">
+        <v>99</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G86" t="s">
+        <v>194</v>
+      </c>
+      <c r="H86" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" t="s">
+        <v>98</v>
+      </c>
+      <c r="C87" t="s">
+        <v>99</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G87" t="s">
+        <v>194</v>
+      </c>
+      <c r="H87" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" t="s">
+        <v>98</v>
+      </c>
+      <c r="C88" t="s">
+        <v>99</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G88" t="s">
+        <v>194</v>
+      </c>
+      <c r="H88" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89" t="s">
+        <v>98</v>
+      </c>
+      <c r="C89" t="s">
+        <v>99</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G89" t="s">
+        <v>194</v>
+      </c>
+      <c r="H89" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" t="s">
+        <v>98</v>
+      </c>
+      <c r="C90" t="s">
+        <v>99</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G90" t="s">
+        <v>194</v>
+      </c>
+      <c r="H90" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B91" t="s">
+        <v>98</v>
+      </c>
+      <c r="C91" t="s">
+        <v>99</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G91" t="s">
+        <v>195</v>
+      </c>
+      <c r="H91" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -2045,6 +2840,36 @@
     <hyperlink ref="F59" r:id="rId58"/>
     <hyperlink ref="F60" r:id="rId59"/>
     <hyperlink ref="F61" r:id="rId60"/>
+    <hyperlink ref="F62" r:id="rId61"/>
+    <hyperlink ref="F63" r:id="rId62"/>
+    <hyperlink ref="F64" r:id="rId63"/>
+    <hyperlink ref="F65" r:id="rId64"/>
+    <hyperlink ref="F66" r:id="rId65"/>
+    <hyperlink ref="F67" r:id="rId66"/>
+    <hyperlink ref="F68" r:id="rId67"/>
+    <hyperlink ref="F69" r:id="rId68"/>
+    <hyperlink ref="F70" r:id="rId69"/>
+    <hyperlink ref="F71" r:id="rId70"/>
+    <hyperlink ref="F72" r:id="rId71"/>
+    <hyperlink ref="F73" r:id="rId72"/>
+    <hyperlink ref="F74" r:id="rId73"/>
+    <hyperlink ref="F75" r:id="rId74"/>
+    <hyperlink ref="F76" r:id="rId75"/>
+    <hyperlink ref="F77" r:id="rId76"/>
+    <hyperlink ref="F78" r:id="rId77"/>
+    <hyperlink ref="F79" r:id="rId78"/>
+    <hyperlink ref="F80" r:id="rId79"/>
+    <hyperlink ref="F81" r:id="rId80"/>
+    <hyperlink ref="F82" r:id="rId81"/>
+    <hyperlink ref="F83" r:id="rId82"/>
+    <hyperlink ref="F84" r:id="rId83"/>
+    <hyperlink ref="F85" r:id="rId84"/>
+    <hyperlink ref="F86" r:id="rId85"/>
+    <hyperlink ref="F87" r:id="rId86"/>
+    <hyperlink ref="F88" r:id="rId87"/>
+    <hyperlink ref="F89" r:id="rId88"/>
+    <hyperlink ref="F90" r:id="rId89"/>
+    <hyperlink ref="F91" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Women_and_Family_Support.xlsx
+++ b/results/scraped_Cape_Town_Women_and_Family_Support.xlsx
@@ -43,25 +43,25 @@
     <t>Woman-Wikipedia</t>
   </si>
   <si>
+    <t>Woman- Simple EnglishWikipedia, the free encyclopedia</t>
+  </si>
+  <si>
     <t>WOMANDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
     <t>Female-Wikipedia</t>
   </si>
   <si>
-    <t>Woman- Simple EnglishWikipedia, the free encyclopedia</t>
+    <t>Women| News, Celebrity, Lifestyle, and Expert Opinions</t>
   </si>
   <si>
     <t>51 FamousWomenin History Who Have Changed the World</t>
   </si>
   <si>
-    <t>Women| News, Celebrity, Lifestyle, and Expert Opinions</t>
-  </si>
-  <si>
     <t>Women| Britannica</t>
   </si>
   <si>
-    <t>Welcome |UN Women– Headquarters</t>
+    <t>28,394,802WomenImages and Stock Photos - Getty Images</t>
   </si>
   <si>
     <t>Women's History| NationalWomen's HistoryMuseum</t>
@@ -79,12 +79,12 @@
     <t>What Is The Difference Between Sex andGender-Simply Psychology</t>
   </si>
   <si>
+    <t>Gender-World Health Organization(WHO)</t>
+  </si>
+  <si>
     <t>Gender-Psychology Today</t>
   </si>
   <si>
-    <t>Gender-World Health Organization(WHO)</t>
-  </si>
-  <si>
     <t>How Many Genders Are There? All 72 Genders List -MedicineNet</t>
   </si>
   <si>
@@ -103,90 +103,90 @@
     <t>Family- Wikipedia</t>
   </si>
   <si>
+    <t>Home |Familyand Medical Leave Insurance (FAMLI)</t>
+  </si>
+  <si>
     <t>Family| Definition, Meaning, Members, Types, &amp; Facts | Britannica</t>
   </si>
   <si>
+    <t>Find yourfamily. Free Genealogy Archives - FamilySearch</t>
+  </si>
+  <si>
+    <t>12 Types ofFamilyStructures &amp; Their Characteristics - wikiHow</t>
+  </si>
+  <si>
     <t>FAMILYDefinition &amp; Meaning - Merriam-Webster</t>
   </si>
   <si>
-    <t>12 Types ofFamilyStructures &amp; Their Characteristics - wikiHow</t>
-  </si>
-  <si>
-    <t>Find yourfamily. Free Genealogy Archives - FamilySearch</t>
-  </si>
-  <si>
     <t>Family- Simple English Wikipedia, the free encyclopedia</t>
   </si>
   <si>
+    <t>What IsFamily? (14 Key Points) - Simplicable</t>
+  </si>
+  <si>
     <t>FamilyMembers in English: Complete List with Examples</t>
   </si>
   <si>
     <t>Familyin the United States - Wikipedia</t>
   </si>
   <si>
-    <t>What IsFamily? (14 Key Points) - Simplicable</t>
-  </si>
-  <si>
-    <t>What IsFamily? A Closer Look AtFamilyStructure ... -FamilyOriented</t>
-  </si>
-  <si>
-    <t>SINGLEDefinition &amp; Meaning - Merriam-Webster</t>
-  </si>
-  <si>
-    <t>Match® | The leading dating app for singles. Find better matches.</t>
-  </si>
-  <si>
-    <t>Single- Wikipedia</t>
-  </si>
-  <si>
-    <t>Single(music) - Wikipedia</t>
+    <t>single, adj. meanings, etymology and more | Oxford English Dictionary</t>
+  </si>
+  <si>
+    <t>SINGLEDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
+    <t>single, singling, singled, singles- WordWeb dictionary definition</t>
+  </si>
+  <si>
+    <t>Examples of 'SINGLE' in a Sentence |Merriam-Webster</t>
+  </si>
+  <si>
+    <t>SINGLEDefinition &amp; Meaning |Dictionary.com</t>
+  </si>
+  <si>
+    <t>SINGLE| definition in the Cambridge English Dictionary</t>
   </si>
   <si>
     <t>SINGLE| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
-    <t>SINGLEDefinition &amp; Meaning |Dictionary.com</t>
-  </si>
-  <si>
-    <t>Single- definition ofsingleby The Free Dictionary</t>
-  </si>
-  <si>
-    <t>Single- YouTube</t>
-  </si>
-  <si>
-    <t>Single- Apps on Google Play</t>
-  </si>
-  <si>
-    <t>Welcome toSinglePoint- U.S. Bank Commercial Internet Banking</t>
+    <t>What is the abbreviation for Single?</t>
+  </si>
+  <si>
+    <t>SINGLE definitionin American English | Collins English Dictionary</t>
+  </si>
+  <si>
+    <t>#Single(2025) - IMDb</t>
   </si>
   <si>
     <t>ABUSEDDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>ABUSED| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
     <t>ABUSEDSynonyms: 157 Similar and Opposite Words -Merriam-Webster</t>
   </si>
   <si>
-    <t>ABUSED| English meaning - Cambridge Dictionary</t>
+    <t>Abused- IMDb</t>
   </si>
   <si>
     <t>ABUSE| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
-    <t>Abused- IMDb</t>
+    <t>ABUSEDefinition &amp; Meaning |Dictionary.com</t>
+  </si>
+  <si>
+    <t>abused- Wiktionary, the free dictionary</t>
+  </si>
+  <si>
+    <t>Abused - Definition, Meaning &amp; Synonyms| Vocabulary.com</t>
   </si>
   <si>
     <t>Abused- definition ofabusedby The Free Dictionary</t>
   </si>
   <si>
-    <t>Abused - Definition, Meaning &amp; Synonyms| Vocabulary.com</t>
-  </si>
-  <si>
-    <t>What doesabusedmean? -Definitions.net</t>
-  </si>
-  <si>
-    <t>ABUSEDefinition &amp; Meaning |Dictionary.com</t>
-  </si>
-  <si>
     <t>ABUSEDDefinition &amp; Meaning | Dictionary.com</t>
   </si>
   <si>
@@ -196,154 +196,154 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2df8283d07ca197be5bdca8cda14f4cb5524d1ec7a578c15b3841cba7b86e749JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=232302b0-13f9-6ff7-2bd7-155112ea6e84&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV29tYW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a747c5fea5647558cff910787e67fb3db7cf07dd47e7376260f73dc41a764752JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=232302b0-13f9-6ff7-2bd7-155112ea6e84&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3dvbWFu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=101b400593133321d0bf02f3d1792449328e57e9a8ea12b6a351c0ae574fd6a0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=232302b0-13f9-6ff7-2bd7-155112ea6e84&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmVtYWxl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7e8f69f8ca0a0fdd9be5a3356440feeb307a64438d8b8b3686e232924bbe219JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=232302b0-13f9-6ff7-2bd7-155112ea6e84&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL1dvbWFu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1b8b24b45acc8c7d1b06a6d730a2fdadcb3ac8fb3b4176886a25ca7b2c983719JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=232302b0-13f9-6ff7-2bd7-155112ea6e84&amp;u=a1aHR0cHM6Ly93d3cuYmlvZ3JhcGh5LmNvbS9oaXN0b3J5LWN1bHR1cmUvZzQzMzM2MjUyL2ZhbW91cy13b21lbi1pbi1oaXN0b3J5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=41e455e2105d5c1ff0e79905a97c7df0561ca052bdc557f50f2ddde8043c3498JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=232302b0-13f9-6ff7-2bd7-155112ea6e84&amp;u=a1aHR0cHM6Ly93d3cud29tZW4uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=854cab3f21138186a194ca448b6585f87b6d1cb869d1f7128ed04787b842fdd6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=232302b0-13f9-6ff7-2bd7-155112ea6e84&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvd29tZW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=63661e0a6962b29f93dad48b4db373dc6c2a4fd61b8924a4afa568241f041538JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=232302b0-13f9-6ff7-2bd7-155112ea6e84&amp;u=a1aHR0cHM6Ly93d3cudW53b21lbi5vcmcvZW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=38896ba21bbc70e36142a656fe32ec97dc47a1977275045118bf780c9a2ac02dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=232302b0-13f9-6ff7-2bd7-155112ea6e84&amp;u=a1aHR0cHM6Ly93d3cud29tZW5zaGlzdG9yeS5vcmcvd29tZW5zLWhpc3Rvcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ea2f64c135a327d5935bbc8ab8481d4c1051b4dfda346ef1fb34b861c747251JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=232302b0-13f9-6ff7-2bd7-155112ea6e84&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL2xpZmVhbmRzdHlsZS93b21lbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fbc1c9526cb4f72d436d44c5e209ef7b65b2ded66c3dd29797b00247c08e452bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b723e7e-52c0-6f40-3260-299f53d66e15&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9HZW5kZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e7f702c1d02cc08457092efe54d74435b17492eefd900298b1e50b82efee2fc2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b723e7e-52c0-6f40-3260-299f53d66e15&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2dlbmRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=931c39d450aed0b3dc9972898db622537f5aabbf8594408cb2592135cbba53b9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b723e7e-52c0-6f40-3260-299f53d66e15&amp;u=a1aHR0cHM6Ly93d3cuc2ltcGx5cHN5Y2hvbG9neS5vcmcvc2V4LWdlbmRlci5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0da57f61375d890b5ef220b8b17328ea8b660d27b6efa13467fe5b17fb9fc30cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b723e7e-52c0-6f40-3260-299f53d66e15&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9iYXNpY3MvZ2VuZGVyP21zb2NraWQ9MmI3MjNlN2U1MmMwNmY0MDMyNjAyOTlmNTNkNjZlMTU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7d8cc5a0ec3713f48d3b2bb8f683cca0d9791d30305b83d6a644fb482615aa7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b723e7e-52c0-6f40-3260-299f53d66e15&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9oZWFsdGgtdG9waWNzL2dlbmRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=053f269eaa4fafa0404fdc0ac072182d392585dc33ce93bdaf5299814c779b46JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b723e7e-52c0-6f40-3260-299f53d66e15&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNpbmVuZXQuY29tL3doYXRfYXJlX3RoZV83Ml9vdGhlcl9nZW5kZXJzL2FydGljbGUuaHRt&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1dba8693a6843c87631f1fc4c2fc8a4f14c2f0615f1cbd66037a8462e5aa771aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b723e7e-52c0-6f40-3260-299f53d66e15&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMjMyMzYz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b704c3d693866a56b79c9ee3e3f49353f00b8feff1f31f14caf1474441fa4ebbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b723e7e-52c0-6f40-3260-299f53d66e15&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9MaXN0X29mX2dlbmRlcl9pZGVudGl0aWVz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6667f12f4275919d6afa2b7d1a5abdf85e980bac02d1fb8524aeab62ca5d8bedJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b723e7e-52c0-6f40-3260-299f53d66e15&amp;u=a1aHR0cHM6Ly9sZ2J0cWlhLndpa2kvd2lraS9HZW5kZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fb13dd0a5cf2cda86867393796e0d6898bac2528b2c2f55030fbb0d907f064a7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2b723e7e-52c0-6f40-3260-299f53d66e15&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvR2VuZGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b47da7f09f321c6baaff92cad9069275cc400263fc0df342fc8688c30971049JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cdcc491-8d11-69ca-2d76-d3708c83684f&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmFtaWx5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=65e4323ef9b4839a432b19da260d28e252cb4953084d2d9fec737322c99ebdacJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cdcc491-8d11-69ca-2d76-d3708c83684f&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvZmFtaWx5LWtpbnNoaXA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=196fd89b8c0dd61f25a47110063cc47fe7a97da30f85e1325dc75360f9435437JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cdcc491-8d11-69ca-2d76-d3708c83684f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZhbWlseQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cbfa85bc12b317a5794a07fa7bc998ddb99b4f1e4b2f8115613677659cb62cf6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cdcc491-8d11-69ca-2d76-d3708c83684f&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vVHlwZXMtb2YtRmFtaWx5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fcf0f6f2dbb1f268a967277e6a190ba2e84c5e26d1c7d62f23e9a72f7c43bcd7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cdcc491-8d11-69ca-2d76-d3708c83684f&amp;u=a1aHR0cHM6Ly93d3cuZmFtaWx5c2VhcmNoLm9yZy9lbi91bml0ZWQtc3RhdGVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9eff70884ec85c8c80c47cfce7078e34bebe87c0cd645901a7e0c6f0ee472d83JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cdcc491-8d11-69ca-2d76-d3708c83684f&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL0ZhbWlseQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4702ec3c8a3ade9eccff3a36e1fe888db762d836990bb8b5736e5bd9e1926b38JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cdcc491-8d11-69ca-2d76-d3708c83684f&amp;u=a1aHR0cHM6Ly92b2NhYmVycnkuY29tL3ZvY2FidWxhcnkvZmFtaWx5LW1lbWJlcnMtaW4tZW5nbGlzaC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=43fe99e96006c401416daa7ff2a2029bf03f3d17990d65e2d4c578a810ae7e03JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cdcc491-8d11-69ca-2d76-d3708c83684f&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmFtaWx5X2luX3RoZV9Vbml0ZWRfU3RhdGVz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f6f83149decd47c151995b70d97f45193f4629d6081fb983f39aace679f78a2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cdcc491-8d11-69ca-2d76-d3708c83684f&amp;u=a1aHR0cHM6Ly9zaW1wbGljYWJsZS5jb20vc29jaWV0eS93aGF0LWlzLWZhbWlseQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b9dba7026370ab4234cd94033e4b62b76db5380f50752127116cb814874b9d76JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cdcc491-8d11-69ca-2d76-d3708c83684f&amp;u=a1aHR0cHM6Ly9mYW1pbHlvcmllbnRlZC5uZXQvd2hhdC1pcy1mYW1pbHkv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a34ba3ce859a6bfa94e9332f16d77a0bd1da39db13e1e16506df7ab856d93c07JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ba6d751-b488-65fc-2d92-c0b0b52b6491&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5ea4f64d293a25a0bb2e6a26e62139b9cb03aa201568071eafb1749369b7692cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ba6d751-b488-65fc-2d92-c0b0b52b6491&amp;u=a1aHR0cHM6Ly93d3cubWF0Y2guY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=238cf6f9cb073c6b4c698747fa0f1141c564aba39f3e5f59e5112107ab202b7fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ba6d751-b488-65fc-2d92-c0b0b52b6491&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2luZ2xl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ca04f4f79f7ab9c18b79eb61d6fc3a04df163f414123774583f12bed8b60fd7dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ba6d751-b488-65fc-2d92-c0b0b52b6491&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2luZ2xlXyhtdXNpYyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8000f2d9e2b99b11d5230e6eede72244379d0d0314865e3f91ac090901e2d630JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ba6d751-b488-65fc-2d92-c0b0b52b6491&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9b1d4ea4a500875b898cbcf9b80bb3e5217d1ed63a194b1c51789859858f794JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ba6d751-b488-65fc-2d92-c0b0b52b6491&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dee1724e99d0a28612a654bbabb7541fc66ba4b8807801d11d79d41d62e61976JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ba6d751-b488-65fc-2d92-c0b0b52b6491&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3ea71f8c6377f8d4a29e1f93a5622245d8e206726b6ecc1aac8d21dc8f78ce4fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ba6d751-b488-65fc-2d92-c0b0b52b6491&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1keFI5dEN1OEhfVQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e7200ac9cbf5fbda8268a99d504802c68dc9ba7fd8819a903f262fbf3279ebb8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ba6d751-b488-65fc-2d92-c0b0b52b6491&amp;u=a1aHR0cHM6Ly9wbGF5Lmdvb2dsZS5jb20vc3RvcmUvYXBwcy9kZXRhaWxzP2lkPWNvbS5zaW5nbGUuZGF0aW5nJmhsPWVuLVVT&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f4a7e75491998ea7d6c924cdf111f0a85a177e8ff9e27533ca42c12db241b37JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ba6d751-b488-65fc-2d92-c0b0b52b6491&amp;u=a1aHR0cHM6Ly9zaW5nbGVwb2ludC51c2JhbmsuY29tL2NzNzBfYmFua2luZy9sb2dvbi9zYnVzZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5faa6059710999bfdea010c4dab71bc0eed5e7340e84f5bb69ec7d568b8e82b5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a07f859-2b2e-6ba8-1e20-efb82af16a4a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7ccc6118c7700b285094f71ccfcf7f23446e6b8ad24053ab3c1a0151069cdc77JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a07f859-2b2e-6ba8-1e20-efb82af16a4a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvYWJ1c2Vk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4dfda085787b5fc0cd955d3c0f31b6509a6298fa50a1f94a9448454da6efdd07JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a07f859-2b2e-6ba8-1e20-efb82af16a4a&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b6ba5d0ebb2a6f109022c2ccd023ab2853378d739a29e330b7e197bc108e997bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a07f859-2b2e-6ba8-1e20-efb82af16a4a&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b45764f3f0bb378f91f9a34f7ee0f121950eb6b4d979f20500f5b7f6928f530JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a07f859-2b2e-6ba8-1e20-efb82af16a4a&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNjk2ODUwMC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c27ecfeaa77deabfe21314b28154982b5c7600d35eb45996219543c3f0ece93JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a07f859-2b2e-6ba8-1e20-efb82af16a4a&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1fb20b4dafc842a37922dd1b5c6a9de4684407724b3c73ab631af263b8796094JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a07f859-2b2e-6ba8-1e20-efb82af16a4a&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9hYnVzZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=79550b0422acdac572e54a5df8b9424d217980be4a67227d20462242498b4b26JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a07f859-2b2e-6ba8-1e20-efb82af16a4a&amp;u=a1aHR0cHM6Ly93d3cuZGVmaW5pdGlvbnMubmV0L2RlZmluaXRpb24vYWJ1c2Vk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6b9b234649bd9bc0c244b7ca209cc3efe51eedeedefd56d9a60f9ca2ce246097JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a07f859-2b2e-6ba8-1e20-efb82af16a4a&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1e8f452fbea88b9d419c371ea8f010b21b3a2ade9a77eb43149c28f1d0d67309JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a07f859-2b2e-6ba8-1e20-efb82af16a4a&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNlZA&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=402ba6566a69e51136612c002fae725832b4e6ab8e7196466d2726b6fd90255cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV29tYW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dcc2284eaf8321956ad7c768a6b7fe6fe3275150ec3ac2a8a14ebc59161d3c73JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL1dvbWFu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3b6db8563d85deb3ace78c38c922d8475ce7b943010f1d5be3b19ba522ed1939JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3dvbWFu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cebf3c34b096147a7d5230f7bb330d51f873dcc7d3fac50b2873116e93718cedJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmVtYWxl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8072a6a2d69b75fc6d7095dfd1ce257f418e73202078a917487f8b15ea4d5464JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly93d3cud29tZW4uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=388fccc8d2690c5b75eb32761fc1ba5fab3ebed82dbf9209ea58f5e505b7bf2fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly93d3cuYmlvZ3JhcGh5LmNvbS9oaXN0b3J5LWN1bHR1cmUvZzQzMzM2MjUyL2ZhbW91cy13b21lbi1pbi1oaXN0b3J5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60b1f871d2a5d8f1495f3e78a69acfcd512b364094d1efe341527783d8859a97JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvd29tZW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2e4bb4d47070635c996293f605643278cb8ed2e505040c5d83c593ecd31533fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly93d3cuZ2V0dHlpbWFnZXMuY29tL3Bob3Rvcy93b21lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=62fe60ab34f79d52f2e3e54990ec3dd60ccbc0c61a3133fee2782983d4ee79ffJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly93d3cud29tZW5zaGlzdG9yeS5vcmcvd29tZW5zLWhpc3Rvcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80c9c5200317f49f5fa905c8352971cce5ae9e49b307d19eab223ffbae4fd848JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL2xpZmVhbmRzdHlsZS93b21lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=73f28fb10dcbea9573d90819294bb421ab78da003a36fe1cd9526e9ea78122ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvR2VuZGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7b3cd9488b27375203baef9f2413e4c76bc2dbadbb427b17af451bc868ec6a21JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2dlbmRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=467c30a20593c36ea4c0a9f9a977bbf491d8316c9ebfd3a51464d8629187e183JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly93d3cuc2ltcGx5cHN5Y2hvbG9neS5vcmcvc2V4LWdlbmRlci5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fb7781fc7ee2c8a8aef90af335dbc24cd48caf41aac6f6b3d0684441fca6e2d3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9oZWFsdGgtdG9waWNzL2dlbmRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eb0624601959fbe9c97a61241996490831056da45f8733959536db3053cffea2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9iYXNpY3MvZ2VuZGVyP21zb2NraWQ9MDdkZDdiNjc4NGY2NmFlNzM5MTk2Yzg2ODU2ZjZiYzE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be8bb6027f1ca0af5dcad1d0b54c4c1c4475627b3ce621b6a856020b32aae363JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNpbmVuZXQuY29tL3doYXRfYXJlX3RoZV83Ml9vdGhlcl9nZW5kZXJzL2FydGljbGUuaHRt&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b99cc08fc772e4559c6c6aa1882efa9ec9b19063d2360fe523cfc3b1d60f03abJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMjMyMzYz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d37d9d7761ee03462c84b6ba923ac694f52532a783017212f8b838d703eb876JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGlzdF9vZl9nZW5kZXJfaWRlbnRpdGllcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d6d8429ac157f675e2495f7e3e66743eb7b51b539309c0be71ceb993e30c69e3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly9sZ2J0cWlhLndpa2kvd2lraS9HZW5kZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f601c5bd1aaf28a4f90338e3ae783a6357bab0d5ca6aadafb6d823866e2c915JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL0dlbmRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=609ceced94f1be51669718481599aa650982f933075b275dd301679149e20d05JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GYW1pbHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=793687a2f8cdb3a82e452847dee53f79b2429de5eae9f612532e89bb3e93950fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly9mYW1saS5jb2xvcmFkby5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e97dba4630ed12f625b7d1ee1ace507ae9338da16fa7c676609ec953ec1db85bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvZmFtaWx5LWtpbnNoaXA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4fc20c00a445c3325f6f2d8a9f1154c7e2ba1a643f2e1b0c22a2dc7db185e262JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly93d3cuZmFtaWx5c2VhcmNoLm9yZy9lbi91bml0ZWQtc3RhdGVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=34d4ab22a9e23ef45bc5e215cca191e19251d0551ca79192aa47de24d0a73cc4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vVHlwZXMtb2YtRmFtaWx5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ecca0a02cb319a22b9814a1e86efa8e2c0acb927f0f10df9c361029295629e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZhbWlseQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=43db6e935341a1df20e41865692b83239727cba027a7139179055a566e7e17aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvRmFtaWx5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0283fae4477be5e9517cb2c970e6de694f4a05b6b59168f999fb585426d4b8b5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly9zaW1wbGljYWJsZS5jb20vc29jaWV0eS93aGF0LWlzLWZhbWlseQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=29cdb178ea7422ef009251a85881bd06e6141b85eec00a888633c47655262e89JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly92b2NhYmVycnkuY29tL3ZvY2FidWxhcnkvZmFtaWx5LW1lbWJlcnMtaW4tZW5nbGlzaC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=83827caf6fb56897dd0f0cc5ebff45da68a766e0982c44728cc1a9b79ae6b844JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GYW1pbHlfaW5fdGhlX1VuaXRlZF9TdGF0ZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a6229b5331765b6c37c4961d06889c6be29878ff695a5e573c30db141c0aeb6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly93d3cub2VkLmNvbS9kaWN0aW9uYXJ5L3NpbmdsZV9hZGo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c1f94f19eb80c49b5f588103eca80e8791833e4df0a035e8492032b24431676JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c3011bcaedb7978df77da9d28530d5b16e8d6504c6075cfb16cd552e051e5c03JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly93d3cud29yZHdlYm9ubGluZS5jb20vZW4vU0lOR0xF&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=12dc8a2ebad7423ae907f059060e025778905c37289e491ade6b1be6e45ac4e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9zZW50ZW5jZXMvc2luZ2xl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a5c1268dc412f570177b9e5502aefc36bd867846d46c53a7203f597f45e8de9fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=736794dc703e05318599987594d8eaec4f67f96535e3a9ad48a4c17fa5580d84JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5061bc637f7bc3cf06455a720d0e631aad8f260733d8f3b9e6226d046e607bd8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ab3686636ecdd46fcbfc011d1398b9e07bcd3ae161aac098547ba1e61fb32560JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly93d3cuYWJicmV2aWF0aW9ucy5jb20vYWJicmV2aWF0aW9uL1NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9f5cb679795f60e5aaa547201471029fb08f3f768bc2112a29d55325b08cc310JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL3VzL2RpY3Rpb25hcnkvZW5nbGlzaC9zaW5nbGU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=00db2ab7f04c7dffe9249c5c35d3f85567e922a05a504fae7847f6d3000bdb64JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzNTY5NDU2NS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a06119dd4ea14b64d8e6bbcadbf7a46f10c8409d6aaf26efcf6618dfa9d37e9cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FidXNlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f204ae5b662734505c392b345abb83a688bb33ec44e0351ba7793bed396b1baJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c657dd34528084b3fc859dc188485103d75d576ff546c40ecc477708e86db1ddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvYWJ1c2Vk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d548cfb5c1d076ac2a4420decfd3bb4ee350bff9775ea12aa79fe71f0fe1a1c5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNjk2ODUwMC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d49aab6a0a501fd763f892fa7e5a35304a63456865f7411e591e21e4b9d52524JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4bc77dc8e01f15c7f0a21319a4688f91f2f4b5ba3bbc72f8a2ff9d0aca6aeb99JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=351ce1d0cbee68a3ea186f600a9fd30e0c993c1585d36eb30eaef59531abfd86JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2FidXNlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f796132d1f7c7fa5bcf897cf983c9b6ceeb478e31b4aea0133713edf9b778ceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9hYnVzZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e320f60ade73c680fe43c99902876f153e3fb717969197887d8712982b5b9a78JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2FidXNlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f1fe5548020cfecce0bd73151c28076898142f38f2d581bcf3ab98b66a05f0bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNlZA&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>

--- a/results/scraped_Cape_Town_Women_and_Family_Support.xlsx
+++ b/results/scraped_Cape_Town_Women_and_Family_Support.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="133">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -190,163 +190,226 @@
     <t>ABUSEDDefinition &amp; Meaning | Dictionary.com</t>
   </si>
   <si>
+    <t>10-DayWeatherForecast forSeattle, Washington -The Weather Channel...</t>
+  </si>
+  <si>
+    <t>Seattle, WAWeatherForecast |AccuWeather</t>
+  </si>
+  <si>
+    <t>7-Day Forecast 47.44N 122.27W -National Weather Service</t>
+  </si>
+  <si>
+    <t>Seattle, WAHourly Weather|AccuWeather</t>
+  </si>
+  <si>
+    <t>Weather|Seattle, Washington -king5.com</t>
+  </si>
+  <si>
+    <t>Seattle, WA 10-DayWeatherForecast |Weather Underground</t>
+  </si>
+  <si>
+    <t>Seattle-BBC Weather</t>
+  </si>
+  <si>
+    <t>Seattle/Tacoma, WA -National Weather Service</t>
+  </si>
+  <si>
+    <t>Weather-KOMO</t>
+  </si>
+  <si>
+    <t>National Weather Service</t>
+  </si>
+  <si>
     <t>Women &amp; Family Support</t>
   </si>
   <si>
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=402ba6566a69e51136612c002fae725832b4e6ab8e7196466d2726b6fd90255cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV29tYW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dcc2284eaf8321956ad7c768a6b7fe6fe3275150ec3ac2a8a14ebc59161d3c73JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL1dvbWFu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3b6db8563d85deb3ace78c38c922d8475ce7b943010f1d5be3b19ba522ed1939JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3dvbWFu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cebf3c34b096147a7d5230f7bb330d51f873dcc7d3fac50b2873116e93718cedJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmVtYWxl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8072a6a2d69b75fc6d7095dfd1ce257f418e73202078a917487f8b15ea4d5464JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly93d3cud29tZW4uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=388fccc8d2690c5b75eb32761fc1ba5fab3ebed82dbf9209ea58f5e505b7bf2fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly93d3cuYmlvZ3JhcGh5LmNvbS9oaXN0b3J5LWN1bHR1cmUvZzQzMzM2MjUyL2ZhbW91cy13b21lbi1pbi1oaXN0b3J5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60b1f871d2a5d8f1495f3e78a69acfcd512b364094d1efe341527783d8859a97JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvd29tZW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2e4bb4d47070635c996293f605643278cb8ed2e505040c5d83c593ecd31533fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly93d3cuZ2V0dHlpbWFnZXMuY29tL3Bob3Rvcy93b21lbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=62fe60ab34f79d52f2e3e54990ec3dd60ccbc0c61a3133fee2782983d4ee79ffJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly93d3cud29tZW5zaGlzdG9yeS5vcmcvd29tZW5zLWhpc3Rvcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80c9c5200317f49f5fa905c8352971cce5ae9e49b307d19eab223ffbae4fd848JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=345cdb57-0960-663a-1662-ccb608bd6738&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL2xpZmVhbmRzdHlsZS93b21lbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=73f28fb10dcbea9573d90819294bb421ab78da003a36fe1cd9526e9ea78122ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvR2VuZGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7b3cd9488b27375203baef9f2413e4c76bc2dbadbb427b17af451bc868ec6a21JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2dlbmRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=467c30a20593c36ea4c0a9f9a977bbf491d8316c9ebfd3a51464d8629187e183JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly93d3cuc2ltcGx5cHN5Y2hvbG9neS5vcmcvc2V4LWdlbmRlci5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fb7781fc7ee2c8a8aef90af335dbc24cd48caf41aac6f6b3d0684441fca6e2d3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9oZWFsdGgtdG9waWNzL2dlbmRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eb0624601959fbe9c97a61241996490831056da45f8733959536db3053cffea2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9iYXNpY3MvZ2VuZGVyP21zb2NraWQ9MDdkZDdiNjc4NGY2NmFlNzM5MTk2Yzg2ODU2ZjZiYzE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be8bb6027f1ca0af5dcad1d0b54c4c1c4475627b3ce621b6a856020b32aae363JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNpbmVuZXQuY29tL3doYXRfYXJlX3RoZV83Ml9vdGhlcl9nZW5kZXJzL2FydGljbGUuaHRt&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b99cc08fc772e4559c6c6aa1882efa9ec9b19063d2360fe523cfc3b1d60f03abJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMjMyMzYz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d37d9d7761ee03462c84b6ba923ac694f52532a783017212f8b838d703eb876JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGlzdF9vZl9nZW5kZXJfaWRlbnRpdGllcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d6d8429ac157f675e2495f7e3e66743eb7b51b539309c0be71ceb993e30c69e3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly9sZ2J0cWlhLndpa2kvd2lraS9HZW5kZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f601c5bd1aaf28a4f90338e3ae783a6357bab0d5ca6aadafb6d823866e2c915JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=07dd7b67-84f6-6ae7-3919-6c86856f6bc1&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL0dlbmRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=609ceced94f1be51669718481599aa650982f933075b275dd301679149e20d05JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GYW1pbHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=793687a2f8cdb3a82e452847dee53f79b2429de5eae9f612532e89bb3e93950fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly9mYW1saS5jb2xvcmFkby5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e97dba4630ed12f625b7d1ee1ace507ae9338da16fa7c676609ec953ec1db85bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvZmFtaWx5LWtpbnNoaXA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4fc20c00a445c3325f6f2d8a9f1154c7e2ba1a643f2e1b0c22a2dc7db185e262JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly93d3cuZmFtaWx5c2VhcmNoLm9yZy9lbi91bml0ZWQtc3RhdGVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=34d4ab22a9e23ef45bc5e215cca191e19251d0551ca79192aa47de24d0a73cc4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vVHlwZXMtb2YtRmFtaWx5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ecca0a02cb319a22b9814a1e86efa8e2c0acb927f0f10df9c361029295629e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZhbWlseQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=43db6e935341a1df20e41865692b83239727cba027a7139179055a566e7e17aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvRmFtaWx5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0283fae4477be5e9517cb2c970e6de694f4a05b6b59168f999fb585426d4b8b5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly9zaW1wbGljYWJsZS5jb20vc29jaWV0eS93aGF0LWlzLWZhbWlseQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=29cdb178ea7422ef009251a85881bd06e6141b85eec00a888633c47655262e89JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly92b2NhYmVycnkuY29tL3ZvY2FidWxhcnkvZmFtaWx5LW1lbWJlcnMtaW4tZW5nbGlzaC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=83827caf6fb56897dd0f0cc5ebff45da68a766e0982c44728cc1a9b79ae6b844JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23b15c35-98f0-6e55-2add-4bd499f86f72&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GYW1pbHlfaW5fdGhlX1VuaXRlZF9TdGF0ZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a6229b5331765b6c37c4961d06889c6be29878ff695a5e573c30db141c0aeb6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly93d3cub2VkLmNvbS9kaWN0aW9uYXJ5L3NpbmdsZV9hZGo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c1f94f19eb80c49b5f588103eca80e8791833e4df0a035e8492032b24431676JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c3011bcaedb7978df77da9d28530d5b16e8d6504c6075cfb16cd552e051e5c03JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly93d3cud29yZHdlYm9ubGluZS5jb20vZW4vU0lOR0xF&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=12dc8a2ebad7423ae907f059060e025778905c37289e491ade6b1be6e45ac4e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9zZW50ZW5jZXMvc2luZ2xl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a5c1268dc412f570177b9e5502aefc36bd867846d46c53a7203f597f45e8de9fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=736794dc703e05318599987594d8eaec4f67f96535e3a9ad48a4c17fa5580d84JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5061bc637f7bc3cf06455a720d0e631aad8f260733d8f3b9e6226d046e607bd8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ab3686636ecdd46fcbfc011d1398b9e07bcd3ae161aac098547ba1e61fb32560JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly93d3cuYWJicmV2aWF0aW9ucy5jb20vYWJicmV2aWF0aW9uL1NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9f5cb679795f60e5aaa547201471029fb08f3f768bc2112a29d55325b08cc310JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL3VzL2RpY3Rpb25hcnkvZW5nbGlzaC9zaW5nbGU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=00db2ab7f04c7dffe9249c5c35d3f85567e922a05a504fae7847f6d3000bdb64JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3fccb91d-4960-6c49-2c19-aefc48666d6e&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzNTY5NDU2NS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a06119dd4ea14b64d8e6bbcadbf7a46f10c8409d6aaf26efcf6618dfa9d37e9cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f204ae5b662734505c392b345abb83a688bb33ec44e0351ba7793bed396b1baJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c657dd34528084b3fc859dc188485103d75d576ff546c40ecc477708e86db1ddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvYWJ1c2Vk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d548cfb5c1d076ac2a4420decfd3bb4ee350bff9775ea12aa79fe71f0fe1a1c5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNjk2ODUwMC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d49aab6a0a501fd763f892fa7e5a35304a63456865f7411e591e21e4b9d52524JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4bc77dc8e01f15c7f0a21319a4688f91f2f4b5ba3bbc72f8a2ff9d0aca6aeb99JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=351ce1d0cbee68a3ea186f600a9fd30e0c993c1585d36eb30eaef59531abfd86JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f796132d1f7c7fa5bcf897cf983c9b6ceeb478e31b4aea0133713edf9b778ceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9hYnVzZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e320f60ade73c680fe43c99902876f153e3fb717969197887d8712982b5b9a78JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f1fe5548020cfecce0bd73151c28076898142f38f2d581bcf3ab98b66a05f0bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cec16ae-9f68-6105-0297-014f9e36606f&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNlZA&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3d05079ee41d510d9ba0c1e696afdf69348cb0cb077b578d7395199952821f34JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV29tYW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1639be8811e019393b8802f2d4a5a3198dbd339631a0ab9d83fe942724b1e43eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL1dvbWFu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=65cf02ace8b9ab5d1a029b51d3bf0031861eb813d3d4d5eda741aa5ae501f63bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3dvbWFu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5eac0086ff67c7e61ca9c3ebb72216a03b90ead6c2ccbd3952114bd208332f17JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmVtYWxl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e5cdf4e5a3342169af033bb576b77461d760a2230cc519517c9c65e8a245093aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly93d3cud29tZW4uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f4a3657e164a21b3fb769e7dd1af3cbf72be9fadb35d41631078a362f69e05a2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly93d3cuYmlvZ3JhcGh5LmNvbS9oaXN0b3J5LWN1bHR1cmUvZzQzMzM2MjUyL2ZhbW91cy13b21lbi1pbi1oaXN0b3J5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e5a0ae33908522ba9922000a99bbd62e35f85926db8eac5a37575c292d06b541JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvd29tZW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b9de5f88a33e6321793c46da077d66e93f42c27698198b8f4ea32fe93d89476JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly93d3cuZ2V0dHlpbWFnZXMuY29tL3Bob3Rvcy93b21lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8abf634394bd58ddea2db3431a8b496787646ebf93745e64c2c663b77d85e25eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly93d3cud29tZW5zaGlzdG9yeS5vcmcvd29tZW5zLWhpc3Rvcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ada04507b397f9290f250576289727766a8ae59cff778d4d8f7217b9ccdec8cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL2xpZmVhbmRzdHlsZS93b21lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f4ec368eff4221a8277e564977df0d7bb73a694ec8612aa9fd2590b0ab4fc495JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvR2VuZGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e5ebcbc63c98db435af45f5c1f57fc8cc3e9ef57b209c9badfb7193a992d3d3cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2dlbmRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=862deeb73d4c9687534f2ef6715ddc46427ecc3acf5cc24a411fedb7af500a5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly93d3cuc2ltcGx5cHN5Y2hvbG9neS5vcmcvc2V4LWdlbmRlci5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8c9ed369899cccb508d9e202bfca3514d29a02fc8df5ace962a22cdbdb79dca2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9oZWFsdGgtdG9waWNzL2dlbmRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=baffb3a0e6a4fccd7dab2bd5a0811fffc524c94c12bf9edd5cf361a10dbece0eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9iYXNpY3MvZ2VuZGVyP21zb2NraWQ9MWQ3MmU2MDU2Nzg0NjEyNDNhODBmMWU0NjY2NTYwZmE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f9f57ae089f003131b554e2d43ac4036afd99a136fb47049a565a5c5c61bece3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNpbmVuZXQuY29tL3doYXRfYXJlX3RoZV83Ml9vdGhlcl9nZW5kZXJzL2FydGljbGUuaHRt&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba48ff8b587dee11e883dee86b400cb5f8af4495daa364bb2390f81080b7cbf9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMjMyMzYz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d633682501ce0160479c737c3784f779c6269418ad40015cb5b39374ecaedc7eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGlzdF9vZl9nZW5kZXJfaWRlbnRpdGllcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=04454439b95feaa8d65cf071637e1e35c63de62c67ccb07988a72d4be75a41a1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly9sZ2J0cWlhLndpa2kvd2lraS9HZW5kZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ecd600187becffd38fc0847e8722fd48a9e82c605d6373afbd2fc58d431b3bd2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL0dlbmRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=41254791fc6d955bd8e8996be73e975c0dd98e6b003ca995315467d35ed9d8d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GYW1pbHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b092b0132189f48858108d43e4c1e70fdb7de60e2ebb27781c4fcf308b4ef60bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly9mYW1saS5jb2xvcmFkby5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1e635b79eb3a9efb22d6601b2b889cd00c24374c015c16f6b3630cc8574474d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvZmFtaWx5LWtpbnNoaXA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=673781226fa17b99507a39a7dfa33797aabe8cd26f57c5ba32ce002f9133df26JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly93d3cuZmFtaWx5c2VhcmNoLm9yZy9lbi91bml0ZWQtc3RhdGVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=03626dfba36dfa48fb30e8307717cf5620d2c731671641d77d662a0a4ac896caJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vVHlwZXMtb2YtRmFtaWx5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=126df58473345568885eb7788ea6d05277d74f79bc021a29865b22006860e9e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZhbWlseQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e6c0a4aa2d91d77c1c0a246bc4c264d6cbd07ce4b02cf25dc80081bd6222232JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvRmFtaWx5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a504667f9748b7c3a99bab97b3cd442f86ce06881d33b11fee1de4db83b31d0aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly9zaW1wbGljYWJsZS5jb20vc29jaWV0eS93aGF0LWlzLWZhbWlseQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=167dede33cee30f80285939b3c180acdbe39f0b550131365f6c04832b417ae61JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly92b2NhYmVycnkuY29tL3ZvY2FidWxhcnkvZmFtaWx5LW1lbWJlcnMtaW4tZW5nbGlzaC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9a966254bdab5f253acbba3937fa2cb8e92425f1a7066fd0e61a6c2c2e95b954JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GYW1pbHlfaW5fdGhlX1VuaXRlZF9TdGF0ZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7a4e22502c4642f453f05f1a1bb5731ede0aed146d54050bd08d49875b0dbc58JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly93d3cub2VkLmNvbS9kaWN0aW9uYXJ5L3NpbmdsZV9hZGo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a9d33c4abf8901d8b389ae7fdda81986897a4907b88c09f5731cda2876928f66JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7f5632a00903979c8bac13e202f85ec80785ae37e72967a5d131278b22edca8eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly93d3cud29yZHdlYm9ubGluZS5jb20vZW4vU0lOR0xF&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2fcceb61f541c86fa1c8762a77b0cae4edb4eaa7213c3538c7c79d508ef347e5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9zZW50ZW5jZXMvc2luZ2xl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7391c7130413a28d5058b3307c79a4e2b3735d219b702bc7bc361c8d79970c5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=25efbf762d7a77a58d9dd0c128fd103e68b00a2378472ea416b3b432e9d98a88JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d4d0093f8ebdca4f06b1e5bb8f99b1e8ab3d0d099b1f395298e7023e4865f24JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bed0a77b819f5560e03c2a0680cbba3d679eed3526a9d00bd18435d09421078aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly93d3cuYWJicmV2aWF0aW9ucy5jb20vYWJicmV2aWF0aW9uL1NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=88989e8de733187d1d728862c0a0fb75e1b512a5cd114d4154d3a94a38abf112JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL3VzL2RpY3Rpb25hcnkvZW5nbGlzaC9zaW5nbGU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8111883b509ad8926b9952aca888fe35815e7a07363084cafcf28470492d9b21JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzNTY5NDU2NS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=929fb7eb2d7005c33717962157cc0f30a3c07a609e89f99918ad434b296b7d43JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FidXNlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=469bb6be6f9ecd7ae7c534ff2243c8e2793871b1bb4939a7e2e117e95013fc05JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b90e36fc78fb5b67122d2aacdf1251aae39775bd4750b01e45b67f6395d6368bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvYWJ1c2Vk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6038b8c2a932fef3ddd1384db5851129c5e537478cc2779af6b1f7caa97d1e56JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNjk2ODUwMC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ea302d38d6130be58f800c04f61ef4b71e52b89703757a02a2816ed89b16e511JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=583e5aae7f222e3e35c18bc83d0f8a69fe8bcb01b3a257fba88363a2f45d3c04JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=551b4f1f531693e2c6e027cec5afd544091a68dd5011105095ee00c73f683192JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2FidXNlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd011390447714a3b19ea26bb0948839851ba0049954af0ab2cd0190f291283cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9hYnVzZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=25110f9b2fb254f56e24bacbbcd6f2718e933a80e9a1527fd0dba31cb8c0d503JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2FidXNlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2ebef50ad5cfa9c511ca0365832c260b6831b591eaaf71056be74b3217dcc574JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d77575f6e74ad76cb100e6e7030e611e4793fc3d8fa2d4c1a85adeaedbff81d3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly93ZWF0aGVyLmNvbS91cy93YXNoaW5ndG9uL2NpdHkvc2VhdHRsZS90ZW5kYXk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e8e2b491313bf1be32b4024a18d7048b642681a53172502f04208ea4ce27e81bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly93d3cuYWNjdXdlYXRoZXIuY29tL2VuL3VzL3NlYXR0bGUvOTgxMDQvd2VhdGhlci1mb3JlY2FzdC8zNTE0MDk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89801e500eaac146deb016a343c182c67ad345021f275db396719cf3879d12aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly93d3cud2VhdGhlci5nb3YvOTgxODg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6da1ee9f8bcf693ca97b86774a14a4706d1d29cf5351abf45108c255b0acb72bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly93d3cuYWNjdXdlYXRoZXIuY29tL2VuL3VzL3NlYXR0bGUvOTgxMDQvaG91cmx5LXdlYXRoZXItZm9yZWNhc3QvMzUxNDA5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=61f3db5d941c5734c0f34cdb679aa1c145060d3de192ec1874b366d91ecf839eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly93d3cua2luZzUuY29tL3dlYXRoZXIv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=112bbb5d75885ba5b5db6814997ddafcc0ef276e423d0fe67325e4884b4bfb7fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly93d3cud3VuZGVyZ3JvdW5kLmNvbS9mb3JlY2FzdC91cy93YS9zZWF0dGxl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7c1574b166cc32b6be18d298526ffe244e37302c2543da4fd00ee744efaaa75eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvbS93ZWF0aGVyLzU4MDk4NDQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2697b2164f62ef072f9336795d545a73b2500985121446a28140e1d4a5f64a43JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly93d3cud2VhdGhlci5nb3Yvc2V3Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45d73c8272631706db33db9f1e2367eb6155e737ba8c7de26f656f166378773eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly9rb21vbmV3cy5jb20vd2VhdGhlci8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fa03bd2851dd1086082e26e643dab8eaf31f91172463568cde7ca498cc0d81cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly9mb3JlY2FzdC53ZWF0aGVyLmdvdi96aXBjaXR5LnBocD9pbnB1dHN0cmluZz1TZWF0dGxlJTJDV0E&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
+  </si>
+  <si>
+    <t>Observatory</t>
   </si>
   <si>
     <t>Bing</t>
@@ -694,7 +757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -728,19 +791,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H2" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -748,19 +811,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="G3" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H3" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -768,19 +831,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="G4" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H4" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -788,19 +851,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H5" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -808,19 +871,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G6" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H6" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -828,19 +891,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G7" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H7" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -848,19 +911,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H8" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -868,19 +931,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H9" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -888,19 +951,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H10" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -908,19 +971,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H11" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -928,19 +991,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H12" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -948,19 +1011,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="G13" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H13" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -968,19 +1031,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="G14" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H14" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -988,19 +1051,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G15" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H15" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1008,19 +1071,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G16" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H16" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1028,19 +1091,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G17" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H17" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1048,19 +1111,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G18" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H18" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1068,19 +1131,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G19" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H19" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1088,19 +1151,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H20" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1108,19 +1171,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G21" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H21" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1128,19 +1191,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H22" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1148,19 +1211,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G23" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H23" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1168,19 +1231,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G24" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H24" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1188,19 +1251,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="G25" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H25" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1208,19 +1271,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G26" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H26" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1228,19 +1291,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="G27" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H27" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1248,19 +1311,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G28" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H28" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1268,19 +1331,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G29" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H29" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1288,19 +1351,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G30" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H30" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1308,19 +1371,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G31" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H31" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1328,19 +1391,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G32" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H32" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1348,19 +1411,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G33" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H33" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1368,19 +1431,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C34" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="G34" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H34" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1388,19 +1451,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G35" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H35" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1408,19 +1471,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G36" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H36" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1428,19 +1491,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C37" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G37" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H37" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1448,19 +1511,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C38" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="G38" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H38" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1468,19 +1531,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="G39" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H39" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1488,19 +1551,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C40" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="G40" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H40" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1508,19 +1571,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C41" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="G41" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H41" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1528,19 +1591,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C42" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G42" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H42" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1548,19 +1611,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C43" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G43" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H43" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1568,19 +1631,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C44" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="G44" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H44" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1588,19 +1651,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G45" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H45" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1608,19 +1671,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C46" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G46" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H46" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1628,19 +1691,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="G47" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H47" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1648,19 +1711,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C48" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="G48" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H48" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1668,19 +1731,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G49" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H49" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1688,19 +1751,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="G50" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H50" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1708,19 +1771,219 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C51" t="s">
+        <v>69</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G51" t="s">
+        <v>130</v>
+      </c>
+      <c r="H51" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
         <v>58</v>
       </c>
-      <c r="C51" t="s">
+      <c r="B52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52" t="s">
+        <v>69</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G52" t="s">
+        <v>131</v>
+      </c>
+      <c r="H52" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
         <v>59</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G51" t="s">
-        <v>110</v>
-      </c>
-      <c r="H51" t="s">
-        <v>111</v>
+      <c r="B53" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53" t="s">
+        <v>69</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G53" t="s">
+        <v>131</v>
+      </c>
+      <c r="H53" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" t="s">
+        <v>69</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G54" t="s">
+        <v>131</v>
+      </c>
+      <c r="H54" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55" t="s">
+        <v>69</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G55" t="s">
+        <v>131</v>
+      </c>
+      <c r="H55" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" t="s">
+        <v>69</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G56" t="s">
+        <v>131</v>
+      </c>
+      <c r="H56" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" t="s">
+        <v>68</v>
+      </c>
+      <c r="C57" t="s">
+        <v>69</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G57" t="s">
+        <v>131</v>
+      </c>
+      <c r="H57" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" t="s">
+        <v>69</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G58" t="s">
+        <v>131</v>
+      </c>
+      <c r="H58" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59" t="s">
+        <v>69</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G59" t="s">
+        <v>131</v>
+      </c>
+      <c r="H59" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" t="s">
+        <v>69</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G60" t="s">
+        <v>131</v>
+      </c>
+      <c r="H60" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61" t="s">
+        <v>69</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G61" t="s">
+        <v>131</v>
+      </c>
+      <c r="H61" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1775,6 +2038,16 @@
     <hyperlink ref="F49" r:id="rId48"/>
     <hyperlink ref="F50" r:id="rId49"/>
     <hyperlink ref="F51" r:id="rId50"/>
+    <hyperlink ref="F52" r:id="rId51"/>
+    <hyperlink ref="F53" r:id="rId52"/>
+    <hyperlink ref="F54" r:id="rId53"/>
+    <hyperlink ref="F55" r:id="rId54"/>
+    <hyperlink ref="F56" r:id="rId55"/>
+    <hyperlink ref="F57" r:id="rId56"/>
+    <hyperlink ref="F58" r:id="rId57"/>
+    <hyperlink ref="F59" r:id="rId58"/>
+    <hyperlink ref="F60" r:id="rId59"/>
+    <hyperlink ref="F61" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Women_and_Family_Support.xlsx
+++ b/results/scraped_Cape_Town_Women_and_Family_Support.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="112">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -43,25 +43,25 @@
     <t>Woman-Wikipedia</t>
   </si>
   <si>
+    <t>WOMANDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
+    <t>Female-Wikipedia</t>
+  </si>
+  <si>
     <t>Woman- Simple EnglishWikipedia, the free encyclopedia</t>
   </si>
   <si>
-    <t>WOMANDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>Female-Wikipedia</t>
+    <t>51 FamousWomenin History Who Have Changed the World</t>
   </si>
   <si>
     <t>Women| News, Celebrity, Lifestyle, and Expert Opinions</t>
   </si>
   <si>
-    <t>51 FamousWomenin History Who Have Changed the World</t>
-  </si>
-  <si>
     <t>Women| Britannica</t>
   </si>
   <si>
-    <t>28,394,802WomenImages and Stock Photos - Getty Images</t>
+    <t>Welcome |UN Women– Headquarters</t>
   </si>
   <si>
     <t>Women's History| NationalWomen's HistoryMuseum</t>
@@ -79,12 +79,12 @@
     <t>What Is The Difference Between Sex andGender-Simply Psychology</t>
   </si>
   <si>
+    <t>Gender-Psychology Today</t>
+  </si>
+  <si>
     <t>Gender-World Health Organization(WHO)</t>
   </si>
   <si>
-    <t>Gender-Psychology Today</t>
-  </si>
-  <si>
     <t>How Many Genders Are There? All 72 Genders List -MedicineNet</t>
   </si>
   <si>
@@ -103,313 +103,250 @@
     <t>Family- Wikipedia</t>
   </si>
   <si>
-    <t>Home |Familyand Medical Leave Insurance (FAMLI)</t>
-  </si>
-  <si>
     <t>Family| Definition, Meaning, Members, Types, &amp; Facts | Britannica</t>
   </si>
   <si>
+    <t>FAMILYDefinition &amp; Meaning - Merriam-Webster</t>
+  </si>
+  <si>
+    <t>12 Types ofFamilyStructures &amp; Their Characteristics - wikiHow</t>
+  </si>
+  <si>
     <t>Find yourfamily. Free Genealogy Archives - FamilySearch</t>
   </si>
   <si>
-    <t>12 Types ofFamilyStructures &amp; Their Characteristics - wikiHow</t>
-  </si>
-  <si>
-    <t>FAMILYDefinition &amp; Meaning - Merriam-Webster</t>
-  </si>
-  <si>
     <t>Family- Simple English Wikipedia, the free encyclopedia</t>
   </si>
   <si>
+    <t>FamilyMembers in English: Complete List with Examples</t>
+  </si>
+  <si>
+    <t>Familyin the United States - Wikipedia</t>
+  </si>
+  <si>
     <t>What IsFamily? (14 Key Points) - Simplicable</t>
   </si>
   <si>
-    <t>FamilyMembers in English: Complete List with Examples</t>
-  </si>
-  <si>
-    <t>Familyin the United States - Wikipedia</t>
-  </si>
-  <si>
-    <t>single, adj. meanings, etymology and more | Oxford English Dictionary</t>
-  </si>
-  <si>
-    <t>SINGLEDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>single, singling, singled, singles- WordWeb dictionary definition</t>
-  </si>
-  <si>
-    <t>Examples of 'SINGLE' in a Sentence |Merriam-Webster</t>
+    <t>What IsFamily? A Closer Look AtFamilyStructure ... -FamilyOriented</t>
+  </si>
+  <si>
+    <t>SINGLEDefinition &amp; Meaning - Merriam-Webster</t>
+  </si>
+  <si>
+    <t>Match® | The leading dating app for singles. Find better matches.</t>
+  </si>
+  <si>
+    <t>Single- Wikipedia</t>
+  </si>
+  <si>
+    <t>Single(music) - Wikipedia</t>
+  </si>
+  <si>
+    <t>SINGLE| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
     <t>SINGLEDefinition &amp; Meaning |Dictionary.com</t>
   </si>
   <si>
-    <t>SINGLE| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
-    <t>SINGLE| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>What is the abbreviation for Single?</t>
-  </si>
-  <si>
-    <t>SINGLE definitionin American English | Collins English Dictionary</t>
-  </si>
-  <si>
-    <t>#Single(2025) - IMDb</t>
+    <t>Single- definition ofsingleby The Free Dictionary</t>
+  </si>
+  <si>
+    <t>Single- YouTube</t>
+  </si>
+  <si>
+    <t>Single- Apps on Google Play</t>
+  </si>
+  <si>
+    <t>Welcome toSinglePoint- U.S. Bank Commercial Internet Banking</t>
   </si>
   <si>
     <t>ABUSEDDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>ABUSEDSynonyms: 157 Similar and Opposite Words -Merriam-Webster</t>
+  </si>
+  <si>
     <t>ABUSED| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
-    <t>ABUSEDSynonyms: 157 Similar and Opposite Words -Merriam-Webster</t>
+    <t>ABUSE| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
     <t>Abused- IMDb</t>
   </si>
   <si>
-    <t>ABUSE| English meaning - Cambridge Dictionary</t>
+    <t>Abused- definition ofabusedby The Free Dictionary</t>
+  </si>
+  <si>
+    <t>Abused - Definition, Meaning &amp; Synonyms| Vocabulary.com</t>
+  </si>
+  <si>
+    <t>What doesabusedmean? -Definitions.net</t>
   </si>
   <si>
     <t>ABUSEDefinition &amp; Meaning |Dictionary.com</t>
   </si>
   <si>
-    <t>abused- Wiktionary, the free dictionary</t>
-  </si>
-  <si>
-    <t>Abused - Definition, Meaning &amp; Synonyms| Vocabulary.com</t>
-  </si>
-  <si>
-    <t>Abused- definition ofabusedby The Free Dictionary</t>
-  </si>
-  <si>
     <t>ABUSEDDefinition &amp; Meaning | Dictionary.com</t>
   </si>
   <si>
-    <t>10-DayWeatherForecast forSeattle, Washington -The Weather Channel...</t>
-  </si>
-  <si>
-    <t>Seattle, WAWeatherForecast |AccuWeather</t>
-  </si>
-  <si>
-    <t>7-Day Forecast 47.44N 122.27W -National Weather Service</t>
-  </si>
-  <si>
-    <t>Seattle, WAHourly Weather|AccuWeather</t>
-  </si>
-  <si>
-    <t>Weather|Seattle, Washington -king5.com</t>
-  </si>
-  <si>
-    <t>Seattle, WA 10-DayWeatherForecast |Weather Underground</t>
-  </si>
-  <si>
-    <t>Seattle-BBC Weather</t>
-  </si>
-  <si>
-    <t>Seattle/Tacoma, WA -National Weather Service</t>
-  </si>
-  <si>
-    <t>Weather-KOMO</t>
-  </si>
-  <si>
-    <t>National Weather Service</t>
-  </si>
-  <si>
     <t>Women &amp; Family Support</t>
   </si>
   <si>
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3d05079ee41d510d9ba0c1e696afdf69348cb0cb077b578d7395199952821f34JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV29tYW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1639be8811e019393b8802f2d4a5a3198dbd339631a0ab9d83fe942724b1e43eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL1dvbWFu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=65cf02ace8b9ab5d1a029b51d3bf0031861eb813d3d4d5eda741aa5ae501f63bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3dvbWFu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5eac0086ff67c7e61ca9c3ebb72216a03b90ead6c2ccbd3952114bd208332f17JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmVtYWxl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e5cdf4e5a3342169af033bb576b77461d760a2230cc519517c9c65e8a245093aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly93d3cud29tZW4uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f4a3657e164a21b3fb769e7dd1af3cbf72be9fadb35d41631078a362f69e05a2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly93d3cuYmlvZ3JhcGh5LmNvbS9oaXN0b3J5LWN1bHR1cmUvZzQzMzM2MjUyL2ZhbW91cy13b21lbi1pbi1oaXN0b3J5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e5a0ae33908522ba9922000a99bbd62e35f85926db8eac5a37575c292d06b541JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvd29tZW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b9de5f88a33e6321793c46da077d66e93f42c27698198b8f4ea32fe93d89476JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly93d3cuZ2V0dHlpbWFnZXMuY29tL3Bob3Rvcy93b21lbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8abf634394bd58ddea2db3431a8b496787646ebf93745e64c2c663b77d85e25eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly93d3cud29tZW5zaGlzdG9yeS5vcmcvd29tZW5zLWhpc3Rvcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ada04507b397f9290f250576289727766a8ae59cff778d4d8f7217b9ccdec8cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136cb0a6-6891-61af-100c-a7476919606c&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL2xpZmVhbmRzdHlsZS93b21lbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f4ec368eff4221a8277e564977df0d7bb73a694ec8612aa9fd2590b0ab4fc495JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvR2VuZGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e5ebcbc63c98db435af45f5c1f57fc8cc3e9ef57b209c9badfb7193a992d3d3cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2dlbmRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=862deeb73d4c9687534f2ef6715ddc46427ecc3acf5cc24a411fedb7af500a5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly93d3cuc2ltcGx5cHN5Y2hvbG9neS5vcmcvc2V4LWdlbmRlci5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8c9ed369899cccb508d9e202bfca3514d29a02fc8df5ace962a22cdbdb79dca2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9oZWFsdGgtdG9waWNzL2dlbmRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=baffb3a0e6a4fccd7dab2bd5a0811fffc524c94c12bf9edd5cf361a10dbece0eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9iYXNpY3MvZ2VuZGVyP21zb2NraWQ9MWQ3MmU2MDU2Nzg0NjEyNDNhODBmMWU0NjY2NTYwZmE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f9f57ae089f003131b554e2d43ac4036afd99a136fb47049a565a5c5c61bece3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNpbmVuZXQuY29tL3doYXRfYXJlX3RoZV83Ml9vdGhlcl9nZW5kZXJzL2FydGljbGUuaHRt&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba48ff8b587dee11e883dee86b400cb5f8af4495daa364bb2390f81080b7cbf9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMjMyMzYz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d633682501ce0160479c737c3784f779c6269418ad40015cb5b39374ecaedc7eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGlzdF9vZl9nZW5kZXJfaWRlbnRpdGllcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=04454439b95feaa8d65cf071637e1e35c63de62c67ccb07988a72d4be75a41a1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly9sZ2J0cWlhLndpa2kvd2lraS9HZW5kZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ecd600187becffd38fc0847e8722fd48a9e82c605d6373afbd2fc58d431b3bd2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d72e605-6784-6124-3a80-f1e4666560fa&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL0dlbmRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=41254791fc6d955bd8e8996be73e975c0dd98e6b003ca995315467d35ed9d8d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GYW1pbHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b092b0132189f48858108d43e4c1e70fdb7de60e2ebb27781c4fcf308b4ef60bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly9mYW1saS5jb2xvcmFkby5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1e635b79eb3a9efb22d6601b2b889cd00c24374c015c16f6b3630cc8574474d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvZmFtaWx5LWtpbnNoaXA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=673781226fa17b99507a39a7dfa33797aabe8cd26f57c5ba32ce002f9133df26JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly93d3cuZmFtaWx5c2VhcmNoLm9yZy9lbi91bml0ZWQtc3RhdGVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=03626dfba36dfa48fb30e8307717cf5620d2c731671641d77d662a0a4ac896caJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vVHlwZXMtb2YtRmFtaWx5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=126df58473345568885eb7788ea6d05277d74f79bc021a29865b22006860e9e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZhbWlseQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e6c0a4aa2d91d77c1c0a246bc4c264d6cbd07ce4b02cf25dc80081bd6222232JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvRmFtaWx5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a504667f9748b7c3a99bab97b3cd442f86ce06881d33b11fee1de4db83b31d0aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly9zaW1wbGljYWJsZS5jb20vc29jaWV0eS93aGF0LWlzLWZhbWlseQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=167dede33cee30f80285939b3c180acdbe39f0b550131365f6c04832b417ae61JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly92b2NhYmVycnkuY29tL3ZvY2FidWxhcnkvZmFtaWx5LW1lbWJlcnMtaW4tZW5nbGlzaC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9a966254bdab5f253acbba3937fa2cb8e92425f1a7066fd0e61a6c2c2e95b954JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dead0b4-3776-6a8c-0b19-c75536aa6bc1&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GYW1pbHlfaW5fdGhlX1VuaXRlZF9TdGF0ZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7a4e22502c4642f453f05f1a1bb5731ede0aed146d54050bd08d49875b0dbc58JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly93d3cub2VkLmNvbS9kaWN0aW9uYXJ5L3NpbmdsZV9hZGo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a9d33c4abf8901d8b389ae7fdda81986897a4907b88c09f5731cda2876928f66JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7f5632a00903979c8bac13e202f85ec80785ae37e72967a5d131278b22edca8eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly93d3cud29yZHdlYm9ubGluZS5jb20vZW4vU0lOR0xF&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2fcceb61f541c86fa1c8762a77b0cae4edb4eaa7213c3538c7c79d508ef347e5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9zZW50ZW5jZXMvc2luZ2xl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7391c7130413a28d5058b3307c79a4e2b3735d219b702bc7bc361c8d79970c5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=25efbf762d7a77a58d9dd0c128fd103e68b00a2378472ea416b3b432e9d98a88JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d4d0093f8ebdca4f06b1e5bb8f99b1e8ab3d0d099b1f395298e7023e4865f24JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bed0a77b819f5560e03c2a0680cbba3d679eed3526a9d00bd18435d09421078aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly93d3cuYWJicmV2aWF0aW9ucy5jb20vYWJicmV2aWF0aW9uL1NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=88989e8de733187d1d728862c0a0fb75e1b512a5cd114d4154d3a94a38abf112JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL3VzL2RpY3Rpb25hcnkvZW5nbGlzaC9zaW5nbGU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8111883b509ad8926b9952aca888fe35815e7a07363084cafcf28470492d9b21JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05b03c72-dcb9-6585-183e-2b93ddd26477&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzNTY5NDU2NS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=929fb7eb2d7005c33717962157cc0f30a3c07a609e89f99918ad434b296b7d43JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=469bb6be6f9ecd7ae7c534ff2243c8e2793871b1bb4939a7e2e117e95013fc05JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b90e36fc78fb5b67122d2aacdf1251aae39775bd4750b01e45b67f6395d6368bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvYWJ1c2Vk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6038b8c2a932fef3ddd1384db5851129c5e537478cc2779af6b1f7caa97d1e56JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNjk2ODUwMC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ea302d38d6130be58f800c04f61ef4b71e52b89703757a02a2816ed89b16e511JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=583e5aae7f222e3e35c18bc83d0f8a69fe8bcb01b3a257fba88363a2f45d3c04JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=551b4f1f531693e2c6e027cec5afd544091a68dd5011105095ee00c73f683192JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd011390447714a3b19ea26bb0948839851ba0049954af0ab2cd0190f291283cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9hYnVzZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=25110f9b2fb254f56e24bacbbcd6f2718e933a80e9a1527fd0dba31cb8c0d503JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2ebef50ad5cfa9c511ca0365832c260b6831b591eaaf71056be74b3217dcc574JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3da5fc94-0cd8-6e74-1cfd-eb750dcc6fcb&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d77575f6e74ad76cb100e6e7030e611e4793fc3d8fa2d4c1a85adeaedbff81d3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly93ZWF0aGVyLmNvbS91cy93YXNoaW5ndG9uL2NpdHkvc2VhdHRsZS90ZW5kYXk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e8e2b491313bf1be32b4024a18d7048b642681a53172502f04208ea4ce27e81bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly93d3cuYWNjdXdlYXRoZXIuY29tL2VuL3VzL3NlYXR0bGUvOTgxMDQvd2VhdGhlci1mb3JlY2FzdC8zNTE0MDk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89801e500eaac146deb016a343c182c67ad345021f275db396719cf3879d12aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly93d3cud2VhdGhlci5nb3YvOTgxODg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6da1ee9f8bcf693ca97b86774a14a4706d1d29cf5351abf45108c255b0acb72bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly93d3cuYWNjdXdlYXRoZXIuY29tL2VuL3VzL3NlYXR0bGUvOTgxMDQvaG91cmx5LXdlYXRoZXItZm9yZWNhc3QvMzUxNDA5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=61f3db5d941c5734c0f34cdb679aa1c145060d3de192ec1874b366d91ecf839eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly93d3cua2luZzUuY29tL3dlYXRoZXIv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=112bbb5d75885ba5b5db6814997ddafcc0ef276e423d0fe67325e4884b4bfb7fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly93d3cud3VuZGVyZ3JvdW5kLmNvbS9mb3JlY2FzdC91cy93YS9zZWF0dGxl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7c1574b166cc32b6be18d298526ffe244e37302c2543da4fd00ee744efaaa75eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvbS93ZWF0aGVyLzU4MDk4NDQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2697b2164f62ef072f9336795d545a73b2500985121446a28140e1d4a5f64a43JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly93d3cud2VhdGhlci5nb3Yvc2V3Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45d73c8272631706db33db9f1e2367eb6155e737ba8c7de26f656f166378773eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly9rb21vbmV3cy5jb20vd2VhdGhlci8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fa03bd2851dd1086082e26e643dab8eaf31f91172463568cde7ca498cc0d81cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c5be6ea-4a0c-6b91-048b-f10b4bdf6abf&amp;u=a1aHR0cHM6Ly9mb3JlY2FzdC53ZWF0aGVyLmdvdi96aXBjaXR5LnBocD9pbnB1dHN0cmluZz1TZWF0dGxlJTJDV0E&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b313cc6de9cd06870b1825f56ac13750351e30f3ea7b7b326e76ef4a9db71046JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV29tYW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4b9c4a2e084ee0f7219f06e94c15bd57b2898ba758bdbc2a0de83a800e05507cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3dvbWFu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=73f18f2471b874c8381c34c48ba5e5fb07ef2a4d2c6bb7cff3de5d1424930ee7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmVtYWxl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d554c001dd878c9c579f8d6a7be1a1f54d5541f2655a1fddf6c8a6d4b5aa68bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL1dvbWFu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e64312b7dee0f892dec3315a0cf295b2e821664fac3cb71a500c3e0e0f8ec92JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly93d3cuYmlvZ3JhcGh5LmNvbS9oaXN0b3J5LWN1bHR1cmUvZzQzMzM2MjUyL2ZhbW91cy13b21lbi1pbi1oaXN0b3J5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5f201897b250b28740d62e1ab81cbcc44d4567cdef6730911089f1d624dd56eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly93d3cud29tZW4uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7764148619e278897435ea2408446d83dc06fe58b21caae4d81a1a87ed24509JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvd29tZW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d2feb9b3cc602ea09b496a0af70c79d6be6ac6be09e6f08dab2d3f09f76263dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly93d3cudW53b21lbi5vcmcvZW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=874959f383bc6a0270e673204b3ac17a2f78511d94d8d84e22ef2eb9a79ad303JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly93d3cud29tZW5zaGlzdG9yeS5vcmcvd29tZW5zLWhpc3Rvcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba028a638bed2ca1ac72e2f5054892fc7687df4704b49b07357b5f0a0b8ff48dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL2xpZmVhbmRzdHlsZS93b21lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8bf3c115ea94fa2c771fefbd239963441a6b577f412841f2ac8a5d86320c9e91JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9HZW5kZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=38153be2651f6ea2dd23ddc490f34fee2dddf880411b7a81d7305934f1eb407bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2dlbmRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=78fbcccbc1c7704d9cf1542dcdd4f3fb8dfe782186434537a0803a7b9d04ffcaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly93d3cuc2ltcGx5cHN5Y2hvbG9neS5vcmcvc2V4LWdlbmRlci5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6f1965f09e77805cab8848af58391e4e2737a76e3bd642f5aff66be9e307435aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9iYXNpY3MvZ2VuZGVyP21zb2NraWQ9MWJkOGNkODVmM2EzNjEyYTI0N2RkYTY0ZjI3MjYwM2Y&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4037cfd7d6f38c9f0a44550e363243375a53b29a2163f986dc4bed5de41d340aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9oZWFsdGgtdG9waWNzL2dlbmRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1b1275dcfd88ff4567aa36e51f17fc5fef1866228ccb99b881713ab8d015aff9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNpbmVuZXQuY29tL3doYXRfYXJlX3RoZV83Ml9vdGhlcl9nZW5kZXJzL2FydGljbGUuaHRt&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=788b4d7e82057a737d3e58abeca5bec0fa6f78b9f8439ce530a7b43ca3b81096JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMjMyMzYz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bf39cbc6babdfc3b5cab43f1c6cc2b938e745da49bd6e42f4cb203120a452710JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9MaXN0X29mX2dlbmRlcl9pZGVudGl0aWVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2eeeba883830db787433dd57ae31076ac78e50cbad19f6eb4451af25f4e6af9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly9sZ2J0cWlhLndpa2kvd2lraS9HZW5kZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=02c21fa1b7a89d8b2a885793d62aafd19cec022404408e5874943803173bb3d3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvR2VuZGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a9f064b85d9f913e491fd0bf82e200369be156cd39118a530d5f88078b24a94dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmFtaWx5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bbf9711f5a153fd94fd4e949fa5cb90c32558fef61ae16684d485d0af184cd4aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvZmFtaWx5LWtpbnNoaXA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=efcfd236db5952351d6f257a8f8b6b55122027281729986b1d8c3a1e24730704JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZhbWlseQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=77c147fee14505e8c87057e5284dce221839acd866af810c25f53548c78b6108JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vVHlwZXMtb2YtRmFtaWx5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9fe02c0f847ca4bfb558208ade64869b565e3b1e5e74b0bbc9f89503288aac4eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly93d3cuZmFtaWx5c2VhcmNoLm9yZy9lbi91bml0ZWQtc3RhdGVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8374a1a0416d855c08a392ab03e339921aa5be7ada66500dbbc2e648ca9b2738JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL0ZhbWlseQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebe8a91512bfb3d1aa479e55d6651e543696e886de077f9d7441cc2cbb60918aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly92b2NhYmVycnkuY29tL3ZvY2FidWxhcnkvZmFtaWx5LW1lbWJlcnMtaW4tZW5nbGlzaC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bfefa15e077ace3da0f08c48af55e90a53bc48fe67fa1e257465310a8d33c13bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmFtaWx5X2luX3RoZV9Vbml0ZWRfU3RhdGVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4c9a0d648fee048f12a05b9218b5d596838949ae19ce79a951d8efa4caadeb02JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly9zaW1wbGljYWJsZS5jb20vc29jaWV0eS93aGF0LWlzLWZhbWlseQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=27fcb671aba5301841a3f2d18d5b74049bd7809a7c443e8c1e6c33ca95cee8d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly9mYW1pbHlvcmllbnRlZC5uZXQvd2hhdC1pcy1mYW1pbHkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3bbb6687c1066ad8fe43700a4af5eae5cc9235a0fa7a4c0eaf76e7bfe858fd9bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c295bf068cd382768e2ba2c239382ed6fe37f3eba59d688582c6318b9208b72cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly93d3cubWF0Y2guY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96ababe7fb87235dc928f925d08e0de7fe74e2affb3e4b83c33e6f1fadd223f7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2luZ2xl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=025fdfe7e6da5337afb8292e45ae39235946ade4852fc4c416d47b707046c5e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2luZ2xlXyhtdXNpYyk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7113e89b92e0a86c8ac2208612a5b88c4152fe182f906313ea9035de5c443c6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=84811aaf5963eb7e7ca0de3994c12e65e4d81b085a183f14430961e6e55897b5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bef6ff5b8645f281309425886fe1eedbf7d7dc97a3ba9068de52a72527bb367bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0d99e3ecda1dc6657f38e45d2ee12f974ab67ab59db60abaf0afe5c06f235b61JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1keFI5dEN1OEhfVQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ac008b7dfd4dcf66525728473b7fc1d13ce967f82e7144c835ffb03a16362d0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly9wbGF5Lmdvb2dsZS5jb20vc3RvcmUvYXBwcy9kZXRhaWxzP2lkPWNvbS5zaW5nbGUuZGF0aW5nJmhsPWVuLVVT&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=50ac81580c96509ce2b251d604ab52f416d97f57f37dcfd7ce12db61a34843cfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly9zaW5nbGVwb2ludC51c2JhbmsuY29tL2NzNzBfYmFua2luZy9sb2dvbi9zYnVzZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=820110b6b41fdb7d5f100b7a5cf563781f0e8cca8a8e3f7b48eeb27f9d43b056JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FidXNlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=af042277f131aac962a9a6e32b5e1e981537cb88c242755d8969af029b79eaabJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvYWJ1c2Vk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24d05db5d55b2c3eed3063dd07966834da81720f07314f7fae07343cc7f627d0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dbecb4e42431a91204fa09155dcfa7eeca38b22634e5c5a8029cbfeae3cbe51eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be0eaee926cdf1ac653dfc23a79a1b7f8397fa90aac2e5b4fd278fe798963b80JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNjk2ODUwMC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bfb2175763a52bca5e87bd72407f408792810a7f2fd8403094e339843447709fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2FidXNlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d72ca832dbbed23140cbde918de6b820532017e8370fcf866e65a08d1dbd58fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9hYnVzZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4270627e80e8f6d8ea1a6e0471e18dfc49dd3fe5b5474d9403ecb2e8342a88f9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly93d3cuZGVmaW5pdGlvbnMubmV0L2RlZmluaXRpb24vYWJ1c2Vk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1640fa93b3551a9feca00a97666e72a7f919f54364dbca00474ec528d7dd416JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a8262bc94ef3a09ee05c6ecfdae32a30d7325f84f208f83f9b158bd70f3b9f4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNlZA&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
-  </si>
-  <si>
-    <t>Observatory</t>
   </si>
   <si>
     <t>Bing</t>
@@ -757,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -791,19 +728,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G2" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -811,19 +748,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="G3" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H3" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -831,19 +768,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H4" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -851,19 +788,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H5" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -871,19 +808,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H6" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -891,19 +828,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G7" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H7" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -911,19 +848,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="G8" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H8" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -931,19 +868,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="G9" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H9" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -951,19 +888,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C10" t="s">
-        <v>69</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="G10" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H10" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -971,19 +908,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="G11" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H11" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -991,19 +928,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G12" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H12" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1011,19 +948,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G13" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H13" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1031,19 +968,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="G14" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H14" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1051,19 +988,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G15" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H15" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1071,19 +1008,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H16" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1091,19 +1028,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G17" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H17" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1111,19 +1048,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G18" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H18" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1131,19 +1068,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H19" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1151,19 +1088,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H20" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1171,19 +1108,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H21" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1191,19 +1128,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H22" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1211,19 +1148,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H23" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1231,19 +1168,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G24" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H24" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1251,19 +1188,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H25" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1271,19 +1208,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="G26" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H26" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1291,19 +1228,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="G27" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H27" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1311,19 +1248,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="G28" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H28" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1331,19 +1268,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H29" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1351,19 +1288,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="G30" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H30" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1371,19 +1308,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G31" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H31" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1391,19 +1328,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G32" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H32" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1411,19 +1348,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C33" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="G33" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H33" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1431,19 +1368,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="G34" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H34" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1451,19 +1388,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H35" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1471,19 +1408,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="G36" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H36" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1491,19 +1428,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C37" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="G37" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H37" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1511,19 +1448,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="G38" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H38" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1531,19 +1468,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C39" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="G39" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H39" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1551,19 +1488,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="G40" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H40" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1571,19 +1508,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C41" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="G41" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H41" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1591,19 +1528,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C42" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G42" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H42" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1611,19 +1548,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C43" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="G43" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H43" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1631,19 +1568,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C44" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="G44" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H44" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1651,19 +1588,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C45" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="G45" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H45" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1671,19 +1608,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C46" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="G46" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H46" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1691,19 +1628,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C47" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="G47" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H47" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1711,19 +1648,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="G48" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H48" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1731,19 +1668,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C49" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="G49" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H49" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1751,19 +1688,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C50" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="G50" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H50" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1771,219 +1708,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C51" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="G51" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H51" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" t="s">
-        <v>68</v>
-      </c>
-      <c r="C52" t="s">
-        <v>69</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G52" t="s">
-        <v>131</v>
-      </c>
-      <c r="H52" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" t="s">
-        <v>68</v>
-      </c>
-      <c r="C53" t="s">
-        <v>69</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G53" t="s">
-        <v>131</v>
-      </c>
-      <c r="H53" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" t="s">
-        <v>68</v>
-      </c>
-      <c r="C54" t="s">
-        <v>69</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="G54" t="s">
-        <v>131</v>
-      </c>
-      <c r="H54" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" t="s">
-        <v>68</v>
-      </c>
-      <c r="C55" t="s">
-        <v>69</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G55" t="s">
-        <v>131</v>
-      </c>
-      <c r="H55" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C56" t="s">
-        <v>69</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G56" t="s">
-        <v>131</v>
-      </c>
-      <c r="H56" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" t="s">
-        <v>68</v>
-      </c>
-      <c r="C57" t="s">
-        <v>69</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G57" t="s">
-        <v>131</v>
-      </c>
-      <c r="H57" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" t="s">
-        <v>68</v>
-      </c>
-      <c r="C58" t="s">
-        <v>69</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G58" t="s">
-        <v>131</v>
-      </c>
-      <c r="H58" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" t="s">
-        <v>65</v>
-      </c>
-      <c r="B59" t="s">
-        <v>68</v>
-      </c>
-      <c r="C59" t="s">
-        <v>69</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G59" t="s">
-        <v>131</v>
-      </c>
-      <c r="H59" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" t="s">
-        <v>66</v>
-      </c>
-      <c r="B60" t="s">
-        <v>68</v>
-      </c>
-      <c r="C60" t="s">
-        <v>69</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G60" t="s">
-        <v>131</v>
-      </c>
-      <c r="H60" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" t="s">
-        <v>67</v>
-      </c>
-      <c r="B61" t="s">
-        <v>68</v>
-      </c>
-      <c r="C61" t="s">
-        <v>69</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G61" t="s">
-        <v>131</v>
-      </c>
-      <c r="H61" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2038,16 +1775,6 @@
     <hyperlink ref="F49" r:id="rId48"/>
     <hyperlink ref="F50" r:id="rId49"/>
     <hyperlink ref="F51" r:id="rId50"/>
-    <hyperlink ref="F52" r:id="rId51"/>
-    <hyperlink ref="F53" r:id="rId52"/>
-    <hyperlink ref="F54" r:id="rId53"/>
-    <hyperlink ref="F55" r:id="rId54"/>
-    <hyperlink ref="F56" r:id="rId55"/>
-    <hyperlink ref="F57" r:id="rId56"/>
-    <hyperlink ref="F58" r:id="rId57"/>
-    <hyperlink ref="F59" r:id="rId58"/>
-    <hyperlink ref="F60" r:id="rId59"/>
-    <hyperlink ref="F61" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Women_and_Family_Support.xlsx
+++ b/results/scraped_Cape_Town_Women_and_Family_Support.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="213">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -46,25 +46,25 @@
     <t>WOMANDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>Woman- Simple EnglishWikipedia, the free encyclopedia</t>
+  </si>
+  <si>
     <t>Female-Wikipedia</t>
   </si>
   <si>
-    <t>Woman- Simple EnglishWikipedia, the free encyclopedia</t>
+    <t>Women's Clothing &amp; Apparel |Dillard's</t>
+  </si>
+  <si>
+    <t>Women| News, Celebrity, Lifestyle, and Expert Opinions</t>
+  </si>
+  <si>
+    <t>Women| Britannica</t>
   </si>
   <si>
     <t>51 FamousWomenin History Who Have Changed the World</t>
   </si>
   <si>
-    <t>Women| News, Celebrity, Lifestyle, and Expert Opinions</t>
-  </si>
-  <si>
-    <t>Women| Britannica</t>
-  </si>
-  <si>
-    <t>Welcome |UN Women– Headquarters</t>
-  </si>
-  <si>
-    <t>Women's History| NationalWomen's HistoryMuseum</t>
+    <t>28,394,802WomenImages and Stock Photos - Getty Images</t>
   </si>
   <si>
     <t>Women|The Guardian</t>
@@ -79,12 +79,12 @@
     <t>What Is The Difference Between Sex andGender-Simply Psychology</t>
   </si>
   <si>
+    <t>Gender-World Health Organization(WHO)</t>
+  </si>
+  <si>
     <t>Gender-Psychology Today</t>
   </si>
   <si>
-    <t>Gender-World Health Organization(WHO)</t>
-  </si>
-  <si>
     <t>How Many Genders Are There? All 72 Genders List -MedicineNet</t>
   </si>
   <si>
@@ -97,7 +97,7 @@
     <t>Gender- LGBTQIA+ Wiki</t>
   </si>
   <si>
-    <t>Gender- Simple EnglishWikipedia, the free encyclopedia</t>
+    <t>GENDER| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
     <t>Family- Wikipedia</t>
@@ -109,27 +109,27 @@
     <t>FAMILYDefinition &amp; Meaning - Merriam-Webster</t>
   </si>
   <si>
+    <t>Find yourfamily. Free Genealogy Archives - FamilySearch</t>
+  </si>
+  <si>
     <t>12 Types ofFamilyStructures &amp; Their Characteristics - wikiHow</t>
   </si>
   <si>
-    <t>Find yourfamily. Free Genealogy Archives - FamilySearch</t>
+    <t>What IsFamily? (14 Key Points) - Simplicable</t>
   </si>
   <si>
     <t>Family- Simple English Wikipedia, the free encyclopedia</t>
   </si>
   <si>
-    <t>FamilyMembers in English: Complete List with Examples</t>
-  </si>
-  <si>
     <t>Familyin the United States - Wikipedia</t>
   </si>
   <si>
-    <t>What IsFamily? (14 Key Points) - Simplicable</t>
-  </si>
-  <si>
     <t>What IsFamily? A Closer Look AtFamilyStructure ... -FamilyOriented</t>
   </si>
   <si>
+    <t>FAMILY| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
     <t>SINGLEDefinition &amp; Meaning - Merriam-Webster</t>
   </si>
   <si>
@@ -139,55 +139,199 @@
     <t>Single- Wikipedia</t>
   </si>
   <si>
-    <t>Single(music) - Wikipedia</t>
-  </si>
-  <si>
     <t>SINGLE| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
     <t>SINGLEDefinition &amp; Meaning |Dictionary.com</t>
   </si>
   <si>
+    <t>Single person- Wikipedia</t>
+  </si>
+  <si>
     <t>Single- definition ofsingleby The Free Dictionary</t>
   </si>
   <si>
+    <t>SINGLESynonyms: 179 Similar and Opposite Words - Merriam-Webster</t>
+  </si>
+  <si>
+    <t>Why Some People Really Love BeingSingle- Psychology Today</t>
+  </si>
+  <si>
     <t>Single- YouTube</t>
   </si>
   <si>
-    <t>Single- Apps on Google Play</t>
-  </si>
-  <si>
-    <t>Welcome toSinglePoint- U.S. Bank Commercial Internet Banking</t>
-  </si>
-  <si>
-    <t>ABUSEDDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>ABUSEDSynonyms: 157 Similar and Opposite Words -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>ABUSED| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>ABUSE| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>Abused- IMDb</t>
-  </si>
-  <si>
-    <t>Abused- definition ofabusedby The Free Dictionary</t>
-  </si>
-  <si>
-    <t>Abused - Definition, Meaning &amp; Synonyms| Vocabulary.com</t>
-  </si>
-  <si>
-    <t>What doesabusedmean? -Definitions.net</t>
-  </si>
-  <si>
-    <t>ABUSEDefinition &amp; Meaning |Dictionary.com</t>
-  </si>
-  <si>
-    <t>ABUSEDDefinition &amp; Meaning | Dictionary.com</t>
+    <t>Luke 24:31-35 KJV - Andtheir eyes were opened, and they -Bible Gateway</t>
+  </si>
+  <si>
+    <t>Luke 24:31 Thentheir eyes were openedand they recognized Jesus</t>
+  </si>
+  <si>
+    <t>Luke 24:28-43,John 20:19-31 NKJV - The Disciples’Eyes Opened</t>
+  </si>
+  <si>
+    <t>Whywerethe disciples'eyes openedin Luke 24:31? - Bible Hub</t>
+  </si>
+  <si>
+    <t>When the Lord Opened My Eyes</t>
+  </si>
+  <si>
+    <t>LUKE 24:31 KJV "Andtheir eyes were opened, and they knew him; …</t>
+  </si>
+  <si>
+    <t>Luke 24:31-45 - Thentheir eyes were openedand they recognized hi...</t>
+  </si>
+  <si>
+    <t>Their Eyes were Opened- GoServ Global</t>
+  </si>
+  <si>
+    <t>Their Eyes Were Opened- peterdehaan.com</t>
+  </si>
+  <si>
+    <t>Luke 24:31-32 They came to the edge of the village where theywere...</t>
+  </si>
+  <si>
+    <t>GitHub - 0xk1h0/ChatGPT_DAN: ChatGPT DAN, Jailbreaks prompt</t>
+  </si>
+  <si>
+    <t>AITAH - Reddit</t>
+  </si>
+  <si>
+    <t>Download GitHub Desktop</t>
+  </si>
+  <si>
+    <t>为什么近期gpt出现大规模的路由降智？ - 知乎</t>
+  </si>
+  <si>
+    <t>chatgpt-api · GitHub Topics · GitHub</t>
+  </si>
+  <si>
+    <t>Guild Wars 3 - Reddit</t>
+  </si>
+  <si>
+    <t>ChatGPT Plus 正式恢复五小时使用上限，Codex 长任务体验会受影响 …</t>
+  </si>
+  <si>
+    <t>GitHub - rasbt/LLMs-from-scratch: Implement a ChatGPT-like LLM in ...</t>
+  </si>
+  <si>
+    <t>GitHub - miuuyy/codex-chatgpt-web: Use ChatGPT Web (including …</t>
+  </si>
+  <si>
+    <t>GitHub - f/prompts.chat: f.k.a. Awesome ChatGPT Prompts. Share ...</t>
+  </si>
+  <si>
+    <t>Giants Home | New York Giants – Giants.com</t>
+  </si>
+  <si>
+    <t>NEW YORK GIANTS NEWS</t>
+  </si>
+  <si>
+    <t>NEW YORK GIANTS SCHEDULE</t>
+  </si>
+  <si>
+    <t>Giants Team Depth Chart | New York Giants – Giants.com</t>
+  </si>
+  <si>
+    <t>Giants Tickets | New York Giants - Giants.com</t>
+  </si>
+  <si>
+    <t>Giants Team | New York Giants – Giants.com</t>
+  </si>
+  <si>
+    <t>New York Giants release official 2026 schedule</t>
+  </si>
+  <si>
+    <t>New York Giants Radio | Listen on Radio and Podcasts - Giants.com</t>
+  </si>
+  <si>
+    <t>New York Giants Apparel, NY Giants Gear, NY Giants Pro Shop</t>
+  </si>
+  <si>
+    <t>NEW YORK GIANTS: IN THE COMMUNITY</t>
+  </si>
+  <si>
+    <t>Passport to Darkness-Harvard Film Archive</t>
+  </si>
+  <si>
+    <t>A Tale of Sorrow and Sadness -Harvard Film Archive</t>
+  </si>
+  <si>
+    <t>Passport to Darkness(1959) - IMDb</t>
+  </si>
+  <si>
+    <t>Seijun Suzuki-Wikipedia</t>
+  </si>
+  <si>
+    <t>‎Passport to Darkness(1959) directed bySeijun Suzuki• Reviews,film...</t>
+  </si>
+  <si>
+    <t>Seijun Suzuki filmography-Wikipedia</t>
+  </si>
+  <si>
+    <t>Passport to Darkness- filmlinc.org</t>
+  </si>
+  <si>
+    <t>Japanese noir | I See A Dark Theater</t>
+  </si>
+  <si>
+    <t>Passport to Darkness(1959) - User reviews - IMDb</t>
+  </si>
+  <si>
+    <t>Leader SFriedChickenInc inBurnside, LA - The RealYellow Pages</t>
+  </si>
+  <si>
+    <t>Home [www.leadersfriedchicken.com]</t>
+  </si>
+  <si>
+    <t>LEADER’S FRIEDCHICKEN- Updated September 2026 -Yelp</t>
+  </si>
+  <si>
+    <t>Leader SFriedChickeninBurnside, LA with Reviews</t>
+  </si>
+  <si>
+    <t>Leader'sFriedChicken- Restaurantji</t>
+  </si>
+  <si>
+    <t>Leader'sFriedChicken| Gonzales LA -Facebook</t>
+  </si>
+  <si>
+    <t>LEADER'SFRIEDCHICKEN- Reviews, Photos &amp; Phone Number …</t>
+  </si>
+  <si>
+    <t>Leader'sFriedChickenDonaldsonville | Maurepas LA - Facebook</t>
+  </si>
+  <si>
+    <t>Leader's Fried Chicken, Gonzales -MenuPix</t>
+  </si>
+  <si>
+    <t>Leader's Fried Chickenmenu - Gonzales LA 70737 - (877) 585-1085 -Allmenus</t>
+  </si>
+  <si>
+    <t>Store locator: Find an At Home Store Near You</t>
+  </si>
+  <si>
+    <t>Wall Art &amp; Mirrors for Home Decor |At Home</t>
+  </si>
+  <si>
+    <t>At Home</t>
+  </si>
+  <si>
+    <t>How do I find the nearest At Home location? – At Home</t>
+  </si>
+  <si>
+    <t>Affordable Rugs For Every Space | At Home</t>
+  </si>
+  <si>
+    <t>Affordable Home Furniture for Every Room | At Home</t>
+  </si>
+  <si>
+    <t>Home Decor Store in Phoenix, AZ 85028 | At Home</t>
+  </si>
+  <si>
+    <t>Home Decor Store in Longmont, CO 80501 | At Home</t>
+  </si>
+  <si>
+    <t>What are your store hours? - At Home</t>
   </si>
   <si>
     <t>Women &amp; Family Support</t>
@@ -196,157 +340,316 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b313cc6de9cd06870b1825f56ac13750351e30f3ea7b7b326e76ef4a9db71046JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV29tYW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4b9c4a2e084ee0f7219f06e94c15bd57b2898ba758bdbc2a0de83a800e05507cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3dvbWFu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=73f18f2471b874c8381c34c48ba5e5fb07ef2a4d2c6bb7cff3de5d1424930ee7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmVtYWxl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d554c001dd878c9c579f8d6a7be1a1f54d5541f2655a1fddf6c8a6d4b5aa68bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL1dvbWFu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e64312b7dee0f892dec3315a0cf295b2e821664fac3cb71a500c3e0e0f8ec92JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly93d3cuYmlvZ3JhcGh5LmNvbS9oaXN0b3J5LWN1bHR1cmUvZzQzMzM2MjUyL2ZhbW91cy13b21lbi1pbi1oaXN0b3J5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5f201897b250b28740d62e1ab81cbcc44d4567cdef6730911089f1d624dd56eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly93d3cud29tZW4uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7764148619e278897435ea2408446d83dc06fe58b21caae4d81a1a87ed24509JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvd29tZW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d2feb9b3cc602ea09b496a0af70c79d6be6ac6be09e6f08dab2d3f09f76263dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly93d3cudW53b21lbi5vcmcvZW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=874959f383bc6a0270e673204b3ac17a2f78511d94d8d84e22ef2eb9a79ad303JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly93d3cud29tZW5zaGlzdG9yeS5vcmcvd29tZW5zLWhpc3Rvcnk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba028a638bed2ca1ac72e2f5054892fc7687df4704b49b07357b5f0a0b8ff48dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dd8f707-87a1-6561-2298-e0e686776471&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL2xpZmVhbmRzdHlsZS93b21lbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8bf3c115ea94fa2c771fefbd239963441a6b577f412841f2ac8a5d86320c9e91JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9HZW5kZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=38153be2651f6ea2dd23ddc490f34fee2dddf880411b7a81d7305934f1eb407bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2dlbmRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=78fbcccbc1c7704d9cf1542dcdd4f3fb8dfe782186434537a0803a7b9d04ffcaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly93d3cuc2ltcGx5cHN5Y2hvbG9neS5vcmcvc2V4LWdlbmRlci5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6f1965f09e77805cab8848af58391e4e2737a76e3bd642f5aff66be9e307435aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9iYXNpY3MvZ2VuZGVyP21zb2NraWQ9MWJkOGNkODVmM2EzNjEyYTI0N2RkYTY0ZjI3MjYwM2Y&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4037cfd7d6f38c9f0a44550e363243375a53b29a2163f986dc4bed5de41d340aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9oZWFsdGgtdG9waWNzL2dlbmRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1b1275dcfd88ff4567aa36e51f17fc5fef1866228ccb99b881713ab8d015aff9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNpbmVuZXQuY29tL3doYXRfYXJlX3RoZV83Ml9vdGhlcl9nZW5kZXJzL2FydGljbGUuaHRt&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=788b4d7e82057a737d3e58abeca5bec0fa6f78b9f8439ce530a7b43ca3b81096JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMjMyMzYz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bf39cbc6babdfc3b5cab43f1c6cc2b938e745da49bd6e42f4cb203120a452710JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9MaXN0X29mX2dlbmRlcl9pZGVudGl0aWVz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2eeeba883830db787433dd57ae31076ac78e50cbad19f6eb4451af25f4e6af9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly9sZ2J0cWlhLndpa2kvd2lraS9HZW5kZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=02c21fa1b7a89d8b2a885793d62aafd19cec022404408e5874943803173bb3d3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1bd8cd85-f3a3-612a-247d-da64f272603f&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvR2VuZGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a9f064b85d9f913e491fd0bf82e200369be156cd39118a530d5f88078b24a94dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmFtaWx5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bbf9711f5a153fd94fd4e949fa5cb90c32558fef61ae16684d485d0af184cd4aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvZmFtaWx5LWtpbnNoaXA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=efcfd236db5952351d6f257a8f8b6b55122027281729986b1d8c3a1e24730704JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZhbWlseQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=77c147fee14505e8c87057e5284dce221839acd866af810c25f53548c78b6108JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vVHlwZXMtb2YtRmFtaWx5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9fe02c0f847ca4bfb558208ade64869b565e3b1e5e74b0bbc9f89503288aac4eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly93d3cuZmFtaWx5c2VhcmNoLm9yZy9lbi91bml0ZWQtc3RhdGVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8374a1a0416d855c08a392ab03e339921aa5be7ada66500dbbc2e648ca9b2738JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL0ZhbWlseQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebe8a91512bfb3d1aa479e55d6651e543696e886de077f9d7441cc2cbb60918aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly92b2NhYmVycnkuY29tL3ZvY2FidWxhcnkvZmFtaWx5LW1lbWJlcnMtaW4tZW5nbGlzaC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bfefa15e077ace3da0f08c48af55e90a53bc48fe67fa1e257465310a8d33c13bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmFtaWx5X2luX3RoZV9Vbml0ZWRfU3RhdGVz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4c9a0d648fee048f12a05b9218b5d596838949ae19ce79a951d8efa4caadeb02JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly9zaW1wbGljYWJsZS5jb20vc29jaWV0eS93aGF0LWlzLWZhbWlseQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=27fcb671aba5301841a3f2d18d5b74049bd7809a7c443e8c1e6c33ca95cee8d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ad07533-3830-6202-0c09-62d23955638e&amp;u=a1aHR0cHM6Ly9mYW1pbHlvcmllbnRlZC5uZXQvd2hhdC1pcy1mYW1pbHkv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3bbb6687c1066ad8fe43700a4af5eae5cc9235a0fa7a4c0eaf76e7bfe858fd9bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c295bf068cd382768e2ba2c239382ed6fe37f3eba59d688582c6318b9208b72cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly93d3cubWF0Y2guY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96ababe7fb87235dc928f925d08e0de7fe74e2affb3e4b83c33e6f1fadd223f7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2luZ2xl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=025fdfe7e6da5337afb8292e45ae39235946ade4852fc4c416d47b707046c5e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2luZ2xlXyhtdXNpYyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7113e89b92e0a86c8ac2208612a5b88c4152fe182f906313ea9035de5c443c6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=84811aaf5963eb7e7ca0de3994c12e65e4d81b085a183f14430961e6e55897b5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bef6ff5b8645f281309425886fe1eedbf7d7dc97a3ba9068de52a72527bb367bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0d99e3ecda1dc6657f38e45d2ee12f974ab67ab59db60abaf0afe5c06f235b61JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1keFI5dEN1OEhfVQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ac008b7dfd4dcf66525728473b7fc1d13ce967f82e7144c835ffb03a16362d0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly9wbGF5Lmdvb2dsZS5jb20vc3RvcmUvYXBwcy9kZXRhaWxzP2lkPWNvbS5zaW5nbGUuZGF0aW5nJmhsPWVuLVVT&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=50ac81580c96509ce2b251d604ab52f416d97f57f37dcfd7ce12db61a34843cfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=267c6757-491e-6a42-00a4-70b648eb6b22&amp;u=a1aHR0cHM6Ly9zaW5nbGVwb2ludC51c2JhbmsuY29tL2NzNzBfYmFua2luZy9sb2dvbi9zYnVzZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=820110b6b41fdb7d5f100b7a5cf563781f0e8cca8a8e3f7b48eeb27f9d43b056JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=af042277f131aac962a9a6e32b5e1e981537cb88c242755d8969af029b79eaabJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvYWJ1c2Vk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24d05db5d55b2c3eed3063dd07966834da81720f07314f7fae07343cc7f627d0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dbecb4e42431a91204fa09155dcfa7eeca38b22634e5c5a8029cbfeae3cbe51eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be0eaee926cdf1ac653dfc23a79a1b7f8397fa90aac2e5b4fd278fe798963b80JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNjk2ODUwMC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bfb2175763a52bca5e87bd72407f408792810a7f2fd8403094e339843447709fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d72ca832dbbed23140cbde918de6b820532017e8370fcf866e65a08d1dbd58fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9hYnVzZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4270627e80e8f6d8ea1a6e0471e18dfc49dd3fe5b5474d9403ecb2e8342a88f9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly93d3cuZGVmaW5pdGlvbnMubmV0L2RlZmluaXRpb24vYWJ1c2Vk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1640fa93b3551a9feca00a97666e72a7f919f54364dbca00474ec528d7dd416JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a8262bc94ef3a09ee05c6ecfdae32a30d7325f84f208f83f9b158bd70f3b9f4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa8e771-e193-60fc-1e5e-f090e0876108&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNlZA&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=63aa9353a106a114855f2bb640fa8689ec3dc6fdcb387a02970b1801f8651219JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29970461-d5b5-6404-3952-1380d4e1653e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV29tYW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f6a1349917d913b050c2d35ada4aa2a3487da3ca11fbb6883536a7868caf8dbfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29970461-d5b5-6404-3952-1380d4e1653e&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3dvbWFu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c8f667f897039da2153b53ffbcfd94d2b9ff610ffce988c8ef1f024c98ac90dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29970461-d5b5-6404-3952-1380d4e1653e&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL1dvbWFu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87d65a0bb1521de1bbf4da7ab8683896811de9309fc1c7212059075adc0c6920JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29970461-d5b5-6404-3952-1380d4e1653e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmVtYWxl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8eabbc41bc61fa43fab547bc74dc13527d6b1b04776baacf9491572c0394f216JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29970461-d5b5-6404-3952-1380d4e1653e&amp;u=a1aHR0cHM6Ly93d3cuZGlsbGFyZHMuY29tL2Mvd29tZW4_bXNvY2tpZD0yOTk3MDQ2MWQ1YjU2NDA0Mzk1MjEzODBkNGUxNjUzZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e76358d488c476c0a486cfac6599b2b610fb6296883f1dbfe2c7852e5c12cedbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29970461-d5b5-6404-3952-1380d4e1653e&amp;u=a1aHR0cHM6Ly93d3cud29tZW4uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9dfea67c7c24b8599b4a618a60f3f9b4781fa7fc0dafffbba806a004465f1822JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29970461-d5b5-6404-3952-1380d4e1653e&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvd29tZW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0b1aee29d1bbaa1387f8fb0ec5fa8261c364c9d105b12f85c813c276b2bd76e6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29970461-d5b5-6404-3952-1380d4e1653e&amp;u=a1aHR0cHM6Ly93d3cuYmlvZ3JhcGh5LmNvbS9oaXN0b3J5LWN1bHR1cmUvZzQzMzM2MjUyL2ZhbW91cy13b21lbi1pbi1oaXN0b3J5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=33cd528a8ac0ec693351daabd72b757367093e16f3c2df2210709d45fa5a0fefJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29970461-d5b5-6404-3952-1380d4e1653e&amp;u=a1aHR0cHM6Ly93d3cuZ2V0dHlpbWFnZXMuY29tL3Bob3Rvcy93b21lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8790b1ed209338e261aa1494d94c85f543b5a6bee62d2aec3314ead5482f091fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29970461-d5b5-6404-3952-1380d4e1653e&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL2xpZmVhbmRzdHlsZS93b21lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d8dc1ee8249e40c2c9eacdc6e9f8919f344937d75654d84e5cc0694b866d95bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0afd659b-eb4a-6357-136b-727aea9d6221&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvR2VuZGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3f1f154ae25ed4129fe9f09239f974ae53c997632d684336c3ab2b155558aacdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0afd659b-eb4a-6357-136b-727aea9d6221&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2dlbmRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f9e3b612377a527ab5e9ddeac321d3bf83875d53f85f80f37b3b0c7c86dc96fdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0afd659b-eb4a-6357-136b-727aea9d6221&amp;u=a1aHR0cHM6Ly93d3cuc2ltcGx5cHN5Y2hvbG9neS5vcmcvc2V4LWdlbmRlci5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=376044d24485ead05debb32bc726f2514ab6fb8e3aeeaead98c702e31ed32ab5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0afd659b-eb4a-6357-136b-727aea9d6221&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9oZWFsdGgtdG9waWNzL2dlbmRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80f96e44e44393bef2bbc29991a0a1e5d64b7060fc03113281bc19e6ad165fb1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0afd659b-eb4a-6357-136b-727aea9d6221&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9iYXNpY3MvZ2VuZGVyP21zb2NraWQ9MGFmZDY1OWJlYjRhNjM1NzEzNmI3MjdhZWE5ZDYyMjE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2e766060867d554f6415f4473799584cec2b66dc26f10fdacdaceb7b8977d20JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0afd659b-eb4a-6357-136b-727aea9d6221&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNpbmVuZXQuY29tL3doYXRfYXJlX3RoZV83Ml9vdGhlcl9nZW5kZXJzL2FydGljbGUuaHRt&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=68079998b11db225310a34bb407f7988dca42dda41f21693543aa5863fa3058fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0afd659b-eb4a-6357-136b-727aea9d6221&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMjMyMzYz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4bacd8b3f0cf5143f04ce85481e09d151669f3d18e35922bc1176600583f3816JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0afd659b-eb4a-6357-136b-727aea9d6221&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGlzdF9vZl9nZW5kZXJfaWRlbnRpdGllcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e819b817660ded6c37469d206e4e0eda03329c576e0df82b371c8c8a7e7c76edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0afd659b-eb4a-6357-136b-727aea9d6221&amp;u=a1aHR0cHM6Ly9sZ2J0cWlhLndpa2kvd2lraS9HZW5kZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de1692930a7b7c1295f601a1ce169efea53bba704068bfe9b4332b3c2ac0fb1fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0afd659b-eb4a-6357-136b-727aea9d6221&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2dlbmRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bef03ce1bab67928341bda9afbd451cf183203f81fec54f6ba2ff1924efb8194JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35be0826-9207-6fb6-1887-1fc793de6eae&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmFtaWx5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=725a9b882862cf6e1341c1961cf846b5dd585398d168b97fe11e0a8bbb0a5fefJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35be0826-9207-6fb6-1887-1fc793de6eae&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvZmFtaWx5LWtpbnNoaXA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=25e005d5810a7fe7b27c8b128e80b70276b447546241e4cc585c11c0125be68cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35be0826-9207-6fb6-1887-1fc793de6eae&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZhbWlseQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a140f54de7a3f7a0f08d3a6da49ef24370ab726c2c705be519872d29a81dfe6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35be0826-9207-6fb6-1887-1fc793de6eae&amp;u=a1aHR0cHM6Ly93d3cuZmFtaWx5c2VhcmNoLm9yZy9lbi91bml0ZWQtc3RhdGVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=84e4a1bdb696b650fba2258b8e6a524a75dd4426970d74a31c9cc8570c26ce3eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35be0826-9207-6fb6-1887-1fc793de6eae&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vVHlwZXMtb2YtRmFtaWx5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=26848b071416b94afac0a006a703cc178d53a1192a2dd81bed9be31ba82eb84dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35be0826-9207-6fb6-1887-1fc793de6eae&amp;u=a1aHR0cHM6Ly9zaW1wbGljYWJsZS5jb20vc29jaWV0eS93aGF0LWlzLWZhbWlseQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=970a6965d26c6c039e8b710cfd31301019f55e41f733a4571f864894a4fbe98aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35be0826-9207-6fb6-1887-1fc793de6eae&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL0ZhbWlseQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e58887023f837c232105a08bb6bd89a2c07df873c2c83210e4f140637f90f79aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35be0826-9207-6fb6-1887-1fc793de6eae&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmFtaWx5X2luX3RoZV9Vbml0ZWRfU3RhdGVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b0c0ff44eebf0666e241e00c984be76d8a47677bd037cb2316d56b3ae50826eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35be0826-9207-6fb6-1887-1fc793de6eae&amp;u=a1aHR0cHM6Ly9mYW1pbHlvcmllbnRlZC5uZXQvd2hhdC1pcy1mYW1pbHkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a68777b2041b70468edd8934c49286176c07191a0b283466f7916a0af6a7c97eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35be0826-9207-6fb6-1887-1fc793de6eae&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZhbWlseQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=25959ab7a6d63edac12b22762219dd0b016de7722fc2c359987356e84c46e31cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=178a78b6-4368-60a6-1380-6f5742b161c7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=230a15330de68da40ab56be5268a81b38d68a5ce36c3699bbe57a41b0994f9f2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=178a78b6-4368-60a6-1380-6f5742b161c7&amp;u=a1aHR0cHM6Ly93d3cubWF0Y2guY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6898b585812195d0defcda6a0528781571ae4d9f1c7234957722de9f35250f33JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=178a78b6-4368-60a6-1380-6f5742b161c7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2luZ2xl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=926d7482b48e220f6858c0c00added724e53e4e122ba930dde880104148887aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=178a78b6-4368-60a6-1380-6f5742b161c7&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=625a937a42c4acfeeec3de256e3ecef65946574118a6b44bfc4afabc072a86d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=178a78b6-4368-60a6-1380-6f5742b161c7&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7fd63be5bcbc377073fb672239eec37c9898b82d9cbd80f73089c0cbe6ef53d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=178a78b6-4368-60a6-1380-6f5742b161c7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2luZ2xlX3BlcnNvbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a51095cd31c3e7ab1cfc02e599cc78c3b8a5b69c79615de79abdf999aa8ae38aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=178a78b6-4368-60a6-1380-6f5742b161c7&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL3NpbmdsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7e3d5a40f626c7a86719df31553b8e2945f80ba70ea79cf5bdc0e45a7f63dd02JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=178a78b6-4368-60a6-1380-6f5742b161c7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvc2luZ2xl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4f7420db4915fbe77b079924824d6a226169e67350349040a880ad603e6af126JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=178a78b6-4368-60a6-1380-6f5742b161c7&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9ibG9nL2xpdmluZy1zaW5nbGUvMjAyMTA5L3doeS1zb21lLXBlb3BsZS1yZWFsbHktbG92ZS1iZWluZy1zaW5nbGU_bXNvY2tpZD0xNzhhNzhiNjQzNjg2MGE2MTM4MDZmNTc0MmIxNjFjNw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=75a461bbdb8fceaa45d1580fdf3f9c08ed1ddfb415a26f59e9ada77d02779b50JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=178a78b6-4368-60a6-1380-6f5742b161c7&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1keFI5dEN1OEhfVQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dee71a007a4dd6ae38f03b010e4d86a4b1b1f6bd29effafef2b9c137caee118dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16762ec3-1f1f-6053-09a6-39221ec66163&amp;u=a1aHR0cHM6Ly93d3cuYmlibGVnYXRld2F5LmNvbS9wYXNzYWdlLz9zZWFyY2g9THVrZSUyMDI0JTNBMzEtMzUmdmVyc2lvbj1LSlY&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=552c9b2ff3b3270ac6a95ad3229c8d8fb85a8757d408b1c5bb377863f4a9cb04JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16762ec3-1f1f-6053-09a6-39221ec66163&amp;u=a1aHR0cHM6Ly9iaWJsZWh1Yi5jb20vbHVrZS8yNC0zMS5odG0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=95685393068967971389a644176d9e41d901333f949d93bdb4ca18bfd5c52297JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16762ec3-1f1f-6053-09a6-39221ec66163&amp;u=a1aHR0cHM6Ly93d3cuYmlibGVnYXRld2F5LmNvbS9wYXNzYWdlLz9zZWFyY2g9THVrZSUyMDI0JTNBMjgtNDMlMkNKb2huJTIwMjAlM0ExOS0zMSZ2ZXJzaW9uPU5LSlY&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dec4d5e83fea23a058049f5dc49c5a87d6f886ea18081ab63b85b45f33eb961cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16762ec3-1f1f-6053-09a6-39221ec66163&amp;u=a1aHR0cHM6Ly9iaWJsZWh1Yi5jb20vcS9XaGF0X29wZW5lZF90aGVfZGlzY2lwbGVzX2V5ZXNfaW5fTHVrZV8yNF8zMS5odG0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1f6c9fd5f5b8d87d9d79f42a634e555fdb0a5361ebefa9a18f74f0169ffb4389JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16762ec3-1f1f-6053-09a6-39221ec66163&amp;u=a1aHR0cHM6Ly93d3cuY2h1cmNob2ZqZXN1c2NocmlzdC5vcmcvc3R1ZHkvbGlhaG9uYS8yMDAwLzA2L2xhdHRlci1kYXktc2FpbnQtdm9pY2VzLWEtbGFib3Itb2YtbG92ZS93aGVuLXRoZS1sb3JkLW9wZW5lZC1teS1leWVzP2xhbmc9ZW5n&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef2bf21d95d533a170976b6560e96f6dbafd78b07cb4b426d5512aff3e8697b7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16762ec3-1f1f-6053-09a6-39221ec66163&amp;u=a1aHR0cHM6Ly93d3cua2luZ2phbWVzYmlibGVvbmxpbmUub3JnL0x1a2UtMjQtMzEv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3f47d9e85bcbdffd622aa38557bead052501628bbfa27e7d62f266a55a88667eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16762ec3-1f1f-6053-09a6-39221ec66163&amp;u=a1aHR0cHM6Ly93d3cuYmlibGVzdHVkeXRvb2xzLmNvbS9sdWtlL3Bhc3NhZ2UvP3E9bHVrZSsyNDozMS00NQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=36356e623f4ec9a27bbcc0e6eab147fc3bc324be987c3280eaeafb8870461fc0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16762ec3-1f1f-6053-09a6-39221ec66163&amp;u=a1aHR0cHM6Ly9nb3NlcnZnbG9iYWwub3JnLzIwMjUvMDkvMTgvdGhlaXItZXllcy13ZXJlLW9wZW5lZC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7b9b9c3145ec9aa5965b980234d34b29ed2f01529023adf6bbf0093fe982818eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16762ec3-1f1f-6053-09a6-39221ec66163&amp;u=a1aHR0cHM6Ly93d3cucGV0ZXJkZWhhYW4uY29tL2JpYmxlL3RoZWlyLWV5ZXMtd2VyZS1vcGVuZWQv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=902653f43b9d3a3cfa6a192529eccf01f24eb3852915da1c0ed2392e07cd0c50JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=16762ec3-1f1f-6053-09a6-39221ec66163&amp;u=a1aHR0cHM6Ly93d3cuYmlibGUuY29tL2JpYmxlL2NvbXBhcmUvTFVLLjI0LjMxLTMy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=48a8b370a5cbd8ae69771bae4da12029e6b6681703de09bccda6ba7ff38d8da7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172d0c55-318b-66c9-0fd6-1bb430ec67cd&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tLzB4azFoMC9DaGF0R1BUX0RBTg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b6b63dc476ca3828814b1e05fc805434f9946b855f44fe6e2d91d18dca3ac4f1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172d0c55-318b-66c9-0fd6-1bb430ec67cd&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0FJVEFILw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a1ddf933aec9a64914b06e0e941badb7bf1c673dda13d066b1fc5b415c910c57JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172d0c55-318b-66c9-0fd6-1bb430ec67cd&amp;u=a1aHR0cHM6Ly9kZXNrdG9wLmdpdGh1Yi5jb20vZG93bmxvYWQv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7900e039c49e7de6aaf559bd738eb1ff1dff92c79c8009a949486c4146033773JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172d0c55-318b-66c9-0fd6-1bb430ec67cd&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzIwNzAwMzQzNDYwMjM2MzgxOTE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c4cd6215981d3757db6fd13a9926ff0531da8daed74dfc576baa1c06402eb8cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172d0c55-318b-66c9-0fd6-1bb430ec67cd&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL3RvcGljcy9jaGF0Z3B0LWFwaQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9d6c2215094e079ba2daba2c04b0f0fca0c7d1b05d27cf27a0142c78a75a47b3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172d0c55-318b-66c9-0fd6-1bb430ec67cd&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0d1aWxkV2FyczMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3ccb9b62dc1f31391fb871cd3fafa1f906965bee289620bdc645e119d477596JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172d0c55-318b-66c9-0fd6-1bb430ec67cd&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzIwNzU5MDMwNDQ2NzYzMTUwNTg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=437cdf01962040bab06b1161fc32f4f38ee30ccd7aa61b988091347883e263ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172d0c55-318b-66c9-0fd6-1bb430ec67cd&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL3Jhc2J0L0xMTXMtZnJvbS1zY3JhdGNo&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8de2a079448989394e71f19f8ebaa8b5e4e26b50db9afd0e0296d41728b40d8bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172d0c55-318b-66c9-0fd6-1bb430ec67cd&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL21pdXV5eS9jb2RleC1jaGF0Z3B0LXdlYg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8004490bdc5f151091809314db2e8a2f6d26dea1f0146f165720e3f35546e395JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=172d0c55-318b-66c9-0fd6-1bb430ec67cd&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL2YvcHJvbXB0cy5jaGF0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4f4565c4715d1466859a1411b4a12601254e96145b3f323ce6aa373a2c17baa1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=214d6fa4-16a7-6c16-1338-784517246df2&amp;u=a1aHR0cHM6Ly93d3cuZ2lhbnRzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f150f722aa58f344ca9cd0893c4998f2a80ab422dd430e4ec0cea4a00f4462c0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=214d6fa4-16a7-6c16-1338-784517246df2&amp;u=a1aHR0cHM6Ly93d3cuZ2lhbnRzLmNvbS9uZXdzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d65f6a195ce3e89dc5279c3bf002e4c08a56a90d239f0dd8308b8ac0d5e1ef24JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=214d6fa4-16a7-6c16-1338-784517246df2&amp;u=a1aHR0cHM6Ly93d3cuZ2lhbnRzLmNvbS9zY2hlZHVsZS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=65fb954da237c9988e4d096bf1f51f42267c62bca009ef551d3b5c3bb413dd16JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=214d6fa4-16a7-6c16-1338-784517246df2&amp;u=a1aHR0cHM6Ly93d3cuZ2lhbnRzLmNvbS90ZWFtL2RlcHRoLWNoYXJ0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=059bbf3ca7e1c234fcb74c5f47dc894c931bf5c1bef98a4241b156b953d65cd3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=214d6fa4-16a7-6c16-1338-784517246df2&amp;u=a1aHR0cHM6Ly93d3cuZ2lhbnRzLmNvbS90aWNrZXRzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d7c7d46c0c8f94a06a8b4f460ee7e1c8f8adc48410f8120beb34f67c7f437efJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=214d6fa4-16a7-6c16-1338-784517246df2&amp;u=a1aHR0cHM6Ly93d3cuZ2lhbnRzLmNvbS90ZWFtL2Zyb250LW9mZmljZS1yb3N0ZXIv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=920f89d93c82758a517338b3786c6d4ec9bf8aa036f84c9bcfcc9e4c3fda681eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=214d6fa4-16a7-6c16-1338-784517246df2&amp;u=a1aHR0cHM6Ly93d3cuZ2lhbnRzLmNvbS9uZXdzL25mbC1zY2hlZHVsZS0yMDI2LW5ldy15b3JrLWdpYW50cy10aWNrZXRzLWluZm9ybWF0aW9uLWNvd2JveXMtZWFnbGVzLWNvbW1hbmRlcnM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a1297a32c08d9a9211d4aa7bb8338b74c38fd1077c5ff7c0a3927fb8f07ba152JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=214d6fa4-16a7-6c16-1338-784517246df2&amp;u=a1aHR0cHM6Ly93d3cuZ2lhbnRzLmNvbS9wb2RjYXN0cy9yYWRpbw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1edd221887f03684227593058e13fa098121ba8989b92ca4447edc5ddf6e6132JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=214d6fa4-16a7-6c16-1338-784517246df2&amp;u=a1aHR0cHM6Ly9zaG9wLmdpYW50cy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6367ba31b465968c279407cb131f1a16d04c23084b9b35e3a214afccdf2ca682JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=214d6fa4-16a7-6c16-1338-784517246df2&amp;u=a1aHR0cHM6Ly93d3cuZ2lhbnRzLmNvbS9jb21tdW5pdHkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5e3771704b6a9e00b9160c2834d3032e0bdc33a1573b3db59e4720b8a693f956JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23fef714-ca68-6bda-2776-e0f5cb036a4e&amp;u=a1aHR0cHM6Ly9oYXJ2YXJkZmlsbWFyY2hpdmUub3JnL2NhbGVuZGFyL3Bhc3Nwb3J0LXRvLWRhcmtuZXNzLTIwMTYtMDUvMQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c1f11acd6d236a814571a9715b6a55201f50fd6af00294f8cb5da51802e37420JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23fef714-ca68-6bda-2776-e0f5cb036a4e&amp;u=a1aHR0cHM6Ly9oYXJ2YXJkZmlsbWFyY2hpdmUub3JnL2NhbGVuZGFyL2EtdGFsZS1vZi1zb3Jyb3ctYW5kLXNhZG5lc3MtMjAxNi0wNS8x&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0405c08240c2453c1d936c7850c517ffb585b536abb3b047bb58808e8535640fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23fef714-ca68-6bda-2776-e0f5cb036a4e&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDUyNTY2Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f8cdd54d1944888bb61128a0c40034da504861e40a1f1109607a8896283a1065JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23fef714-ca68-6bda-2776-e0f5cb036a4e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2VpanVuX1N1enVraQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=697d16a0def8d326e34db01795502c74cf530abd587cd3c4c2c22b3a8d0436a0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23fef714-ca68-6bda-2776-e0f5cb036a4e&amp;u=a1aHR0cHM6Ly9sZXR0ZXJib3hkLmNvbS9maWxtL3Bhc3Nwb3J0LXRvLWRhcmtuZXNzL2RldGFpbHMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=596300441939e60e31dbd3604aa3dbb05abd0f3a7a4b431b860fada2453300adJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23fef714-ca68-6bda-2776-e0f5cb036a4e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2VpanVuX1N1enVraV9maWxtb2dyYXBoeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e62d2c13396bba3a8476910de0934400c1967e23763dc614d7c479b6e3ee498aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23fef714-ca68-6bda-2776-e0f5cb036a4e&amp;u=a1aHR0cHM6Ly93d3cuZmlsbWxpbmMub3JnL2ZpbG1zL3Bhc3Nwb3J0LXRvLWRhcmtuZXNzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c4884e2b6238b041ebd657162af152a26f4cf03bfdf074b8511c0c126a3c5d1bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23fef714-ca68-6bda-2776-e0f5cb036a4e&amp;u=a1aHR0cHM6Ly93d3cuaXNlZWFkYXJrdGhlYXRlci5jb20vamFwYW5lc2Utbm9pcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=55b193a6bdc0c115e48df4323d4b1f15913042fbd95f1c5915bb74bee0b77d16JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23fef714-ca68-6bda-2776-e0f5cb036a4e&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDUyNTY2L3Jldmlld3MvP2ZlYXR1cmVkPXJ3MzM1MzYyMw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=524a223a531dd2817a9ec9ed0e748a1cf72a071488f781c5c9973327e8924f8bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0accd58b-6d9f-651a-0221-c26a6c5b646e&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL2J1cm5zaWRlLWxhL2xlYWRlci1zLWZyaWVkLWNoaWNrZW4taW5j&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b4cee03e9a0d8be30b07fc6d9397d0f4dd3da4f58c89d3513f32f5cb2632cd03JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0accd58b-6d9f-651a-0221-c26a6c5b646e&amp;u=a1aHR0cHM6Ly93d3cubGVhZGVyc2ZyaWVkY2hpY2tlbi5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=363a20866519de927017e06558d223bbba45a922e8368e4c4f71a927750381b1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0accd58b-6d9f-651a-0221-c26a6c5b646e&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vYml6L2xlYWRlcnMtZnJpZWQtY2hpY2tlbi1nb256YWxlcz9tc29ja2lkPTBhY2NkNThiNmQ5ZjY1MWEwMjIxYzI2YTZjNWI2NDZl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef8e82ccfdcd5687e2f52e70c8e1c88a3c8c86fabe44f1a78f5553c9da0c2efeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0accd58b-6d9f-651a-0221-c26a6c5b646e&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL2J1cm5zaWRlLWxhL2xlYWRlci1zLWZyaWVkLWNoaWNrZW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aec3e733812a9470fd44c3ae45107063c1dac97456c3b4d665c2364e4cc0fb34JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0accd58b-6d9f-651a-0221-c26a6c5b646e&amp;u=a1aHR0cHM6Ly93d3cucmVzdGF1cmFudGppLmNvbS9sYS9nb256YWxlcy9sZWFkZXJzLWZyaWVkLWNoaWNrZW4taW5jLS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=533b02a9472ee1aca7db718b3d0e0acb16ded4df200ae7367d450857fdb62777JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0accd58b-6d9f-651a-0221-c26a6c5b646e&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2xlYWRlcnNmcmllZGNoaWNrZW4v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd4b94612911c93f32b3b7d812ff03ec72f5edc27e4217ad7d8b670761656ecdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0accd58b-6d9f-651a-0221-c26a6c5b646e&amp;u=a1aHR0cHM6Ly9sZWFkZXJzLWZyaWVkLWNoaWNrZW4ud2hlcmVlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ad1a5ca92e828a9c7e3a876d125e5c83d61869e40e4a32c5a56933939a10fe22JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0accd58b-6d9f-651a-0221-c26a6c5b646e&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL3Blb3BsZS9MZWFkZXJzLUZyaWVkLUNoaWNrZW4tTWF1cmVwYXMvNjE1NTA1MTc2Mzg5NzYv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6decc66a2b0f86f30ccce598b87c308f64cf81d57e22355efa59e744a3d7e40aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0accd58b-6d9f-651a-0221-c26a6c5b646e&amp;u=a1aHR0cHM6Ly93d3cubWVudXBpeC5jb20vbG91aXNpYW5hL3Jlc3RhdXJhbnRzLzE4MDQ1NzcvTGVhZGVycy1GcmllZC1DaGlja2VuLUdvbnphbGVzLUxB&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5a6b6a23fa97bfe040b6d966b717e284d1f74693a9d6f8709754b28c3e3e81f3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0accd58b-6d9f-651a-0221-c26a6c5b646e&amp;u=a1aHR0cHM6Ly93d3cuYWxsbWVudXMuY29tL2xhL2dvbnphbGVzLzc0OTM2NC1sZWFkZXJzLWZyaWVkLWNoaWNrZW4vbWVudS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b0410bb07c706ea257dfbf9c9e2099820204a98afb53aa1bb0ded72324ff68ffJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01563581-5872-659c-3f24-226059a464c4&amp;u=a1aHR0cHM6Ly93d3cuYXRob21lLmNvbS9zdG9yZS1maW5kLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3ccc93c754befd5e63cfb50810dc758f595336625e0487e4a3b11531650b7b1bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01563581-5872-659c-3f24-226059a464c4&amp;u=a1aHR0cHM6Ly93d3cuYXRob21lLmNvbS93YWxsLWRlY29yLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4dc98022a361cb3ac787ea9cb038deaf9ecec01edda1c5e469b4ace0baf83d5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01563581-5872-659c-3f24-226059a464c4&amp;u=a1aHR0cHM6Ly9oZWxwLmF0aG9tZS5jb20vaGMvZW4tdXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8ab8893993d4764022d47e0768f1c671475d204d49ba6e9e6617d839f73e4b4aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01563581-5872-659c-3f24-226059a464c4&amp;u=a1aHR0cHM6Ly9oZWxwLmF0aG9tZS5jb20vaGMvZW4tdXMvYXJ0aWNsZXMvMzYwMDEyMTcwMTUyLUhvdy1kby1JLWZpbmQtdGhlLW5lYXJlc3QtQXQtSG9tZS1sb2NhdGlvbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4839ee8cde9713b74f252a033d2147c9ee7c4ac06b0cdbf481ecf2e5a350191cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01563581-5872-659c-3f24-226059a464c4&amp;u=a1aHR0cHM6Ly93d3cuYXRob21lLmNvbS9ydWdzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7bf0916a3d95ebed6d0dbd90ec392468bfe8044d471e0a9f5b34ea61567cf41JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01563581-5872-659c-3f24-226059a464c4&amp;u=a1aHR0cHM6Ly93d3cuYXRob21lLmNvbS9mdXJuaXR1cmUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=252ede3ae7cff75cd57d35c2a71371f935334080a3b554e1b59a19bdffde242fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01563581-5872-659c-3f24-226059a464c4&amp;u=a1aHR0cHM6Ly93d3cuYXRob21lLmNvbS9zdG9yZS9hcml6b25hLXBob2VuaXgv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e7ba0f148fb042318d7aa11a85833037129be8285da618f9a07bd89d7a896c64JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01563581-5872-659c-3f24-226059a464c4&amp;u=a1aHR0cHM6Ly93d3cuYXRob21lLmNvbS9zdG9yZS9jb2xvcmFkby1sb25nbW9udC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c252242aa92e83b7845c254e0a2ca4b7f45e34970e3ed7847eca37a916aa25e1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01563581-5872-659c-3f24-226059a464c4&amp;u=a1aHR0cHM6Ly9oZWxwLmF0aG9tZS5jb20vaGMvZW4tdXMvYXJ0aWNsZXMvMjAzMDQ0NjY5LVdoYXQtYXJlLXlvdXItc3RvcmUtaG91cnM&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
+  </si>
+  <si>
+    <t>Sea Point</t>
+  </si>
+  <si>
+    <t>Green Point</t>
+  </si>
+  <si>
+    <t>Woodstock</t>
+  </si>
+  <si>
+    <t>Observatory</t>
+  </si>
+  <si>
+    <t>Salt River</t>
   </si>
   <si>
     <t>Bing</t>
@@ -694,7 +997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -728,19 +1031,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="G2" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H2" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -748,19 +1051,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="G3" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H3" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -768,19 +1071,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="G4" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H4" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -788,19 +1091,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="G5" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H5" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -808,19 +1111,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="G6" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H6" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -828,19 +1131,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="G7" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H7" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -848,19 +1151,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="G8" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H8" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -868,19 +1171,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="G9" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H9" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -888,19 +1191,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="G10" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H10" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -908,19 +1211,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="G11" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H11" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -928,19 +1231,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="G12" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H12" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -948,19 +1251,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="G13" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H13" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -968,19 +1271,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="G14" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H14" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -988,19 +1291,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="G15" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H15" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1008,19 +1311,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="G16" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H16" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1028,19 +1331,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="G17" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H17" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1048,19 +1351,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="G18" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H18" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1068,19 +1371,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="G19" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H19" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1088,19 +1391,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="G20" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H20" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1108,19 +1411,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="G21" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H21" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1128,19 +1431,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="G22" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H22" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1148,19 +1451,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="G23" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H23" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1168,19 +1471,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="G24" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H24" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1188,19 +1491,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="G25" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H25" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1208,19 +1511,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="G26" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H26" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1228,19 +1531,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="G27" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H27" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1248,19 +1551,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="G28" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H28" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1268,19 +1571,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="G29" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H29" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1288,19 +1591,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="G30" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H30" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1308,19 +1611,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="G31" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H31" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1328,19 +1631,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="G32" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H32" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1348,19 +1651,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="G33" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H33" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1368,19 +1671,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C34" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="G34" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H34" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1388,19 +1691,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="G35" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H35" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1408,19 +1711,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="G36" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H36" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1428,19 +1731,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C37" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="G37" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H37" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1448,19 +1751,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="G38" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H38" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1468,19 +1771,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="G39" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H39" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1488,19 +1791,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C40" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="G40" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H40" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1508,19 +1811,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C41" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="G41" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H41" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1528,19 +1831,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C42" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="G42" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H42" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1548,19 +1851,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C43" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="G43" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H43" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1568,19 +1871,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C44" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="G44" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H44" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1588,19 +1891,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C45" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="G45" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H45" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1608,19 +1911,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C46" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="G46" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H46" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1628,19 +1931,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C47" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="G47" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H47" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1648,19 +1951,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C48" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="G48" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H48" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1668,19 +1971,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C49" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="G49" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H49" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1688,19 +1991,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C50" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="G50" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="H50" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1708,19 +2011,979 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
+        <v>106</v>
+      </c>
+      <c r="C51" t="s">
+        <v>107</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G51" t="s">
+        <v>206</v>
+      </c>
+      <c r="H51" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
         <v>58</v>
       </c>
-      <c r="C51" t="s">
+      <c r="B52" t="s">
+        <v>106</v>
+      </c>
+      <c r="C52" t="s">
+        <v>107</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G52" t="s">
+        <v>207</v>
+      </c>
+      <c r="H52" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
         <v>59</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G51" t="s">
-        <v>110</v>
-      </c>
-      <c r="H51" t="s">
-        <v>111</v>
+      <c r="B53" t="s">
+        <v>106</v>
+      </c>
+      <c r="C53" t="s">
+        <v>107</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G53" t="s">
+        <v>207</v>
+      </c>
+      <c r="H53" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" t="s">
+        <v>107</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G54" t="s">
+        <v>207</v>
+      </c>
+      <c r="H54" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" t="s">
+        <v>106</v>
+      </c>
+      <c r="C55" t="s">
+        <v>107</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G55" t="s">
+        <v>207</v>
+      </c>
+      <c r="H55" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" t="s">
+        <v>107</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G56" t="s">
+        <v>207</v>
+      </c>
+      <c r="H56" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" t="s">
+        <v>106</v>
+      </c>
+      <c r="C57" t="s">
+        <v>107</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G57" t="s">
+        <v>207</v>
+      </c>
+      <c r="H57" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58" t="s">
+        <v>107</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G58" t="s">
+        <v>207</v>
+      </c>
+      <c r="H58" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" t="s">
+        <v>106</v>
+      </c>
+      <c r="C59" t="s">
+        <v>107</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G59" t="s">
+        <v>207</v>
+      </c>
+      <c r="H59" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" t="s">
+        <v>106</v>
+      </c>
+      <c r="C60" t="s">
+        <v>107</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G60" t="s">
+        <v>207</v>
+      </c>
+      <c r="H60" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" t="s">
+        <v>106</v>
+      </c>
+      <c r="C61" t="s">
+        <v>107</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G61" t="s">
+        <v>207</v>
+      </c>
+      <c r="H61" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" t="s">
+        <v>106</v>
+      </c>
+      <c r="C62" t="s">
+        <v>107</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G62" t="s">
+        <v>208</v>
+      </c>
+      <c r="H62" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" t="s">
+        <v>106</v>
+      </c>
+      <c r="C63" t="s">
+        <v>107</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G63" t="s">
+        <v>208</v>
+      </c>
+      <c r="H63" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" t="s">
+        <v>106</v>
+      </c>
+      <c r="C64" t="s">
+        <v>107</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G64" t="s">
+        <v>208</v>
+      </c>
+      <c r="H64" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" t="s">
+        <v>106</v>
+      </c>
+      <c r="C65" t="s">
+        <v>107</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G65" t="s">
+        <v>208</v>
+      </c>
+      <c r="H65" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" t="s">
+        <v>106</v>
+      </c>
+      <c r="C66" t="s">
+        <v>107</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G66" t="s">
+        <v>208</v>
+      </c>
+      <c r="H66" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" t="s">
+        <v>106</v>
+      </c>
+      <c r="C67" t="s">
+        <v>107</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G67" t="s">
+        <v>208</v>
+      </c>
+      <c r="H67" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" t="s">
+        <v>106</v>
+      </c>
+      <c r="C68" t="s">
+        <v>107</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G68" t="s">
+        <v>208</v>
+      </c>
+      <c r="H68" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" t="s">
+        <v>106</v>
+      </c>
+      <c r="C69" t="s">
+        <v>107</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G69" t="s">
+        <v>208</v>
+      </c>
+      <c r="H69" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" t="s">
+        <v>106</v>
+      </c>
+      <c r="C70" t="s">
+        <v>107</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G70" t="s">
+        <v>208</v>
+      </c>
+      <c r="H70" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" t="s">
+        <v>106</v>
+      </c>
+      <c r="C71" t="s">
+        <v>107</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G71" t="s">
+        <v>208</v>
+      </c>
+      <c r="H71" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" t="s">
+        <v>106</v>
+      </c>
+      <c r="C72" t="s">
+        <v>107</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G72" t="s">
+        <v>209</v>
+      </c>
+      <c r="H72" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" t="s">
+        <v>106</v>
+      </c>
+      <c r="C73" t="s">
+        <v>107</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G73" t="s">
+        <v>209</v>
+      </c>
+      <c r="H73" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" t="s">
+        <v>106</v>
+      </c>
+      <c r="C74" t="s">
+        <v>107</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G74" t="s">
+        <v>209</v>
+      </c>
+      <c r="H74" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" t="s">
+        <v>106</v>
+      </c>
+      <c r="C75" t="s">
+        <v>107</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G75" t="s">
+        <v>209</v>
+      </c>
+      <c r="H75" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" t="s">
+        <v>106</v>
+      </c>
+      <c r="C76" t="s">
+        <v>107</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H76" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" t="s">
+        <v>106</v>
+      </c>
+      <c r="C77" t="s">
+        <v>107</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G77" t="s">
+        <v>209</v>
+      </c>
+      <c r="H77" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" t="s">
+        <v>106</v>
+      </c>
+      <c r="C78" t="s">
+        <v>107</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G78" t="s">
+        <v>209</v>
+      </c>
+      <c r="H78" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" t="s">
+        <v>106</v>
+      </c>
+      <c r="C79" t="s">
+        <v>107</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G79" t="s">
+        <v>209</v>
+      </c>
+      <c r="H79" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" t="s">
+        <v>106</v>
+      </c>
+      <c r="C80" t="s">
+        <v>107</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G80" t="s">
+        <v>209</v>
+      </c>
+      <c r="H80" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" t="s">
+        <v>106</v>
+      </c>
+      <c r="C81" t="s">
+        <v>107</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G81" t="s">
+        <v>210</v>
+      </c>
+      <c r="H81" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" t="s">
+        <v>106</v>
+      </c>
+      <c r="C82" t="s">
+        <v>107</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G82" t="s">
+        <v>210</v>
+      </c>
+      <c r="H82" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" t="s">
+        <v>106</v>
+      </c>
+      <c r="C83" t="s">
+        <v>107</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G83" t="s">
+        <v>210</v>
+      </c>
+      <c r="H83" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" t="s">
+        <v>106</v>
+      </c>
+      <c r="C84" t="s">
+        <v>107</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G84" t="s">
+        <v>210</v>
+      </c>
+      <c r="H84" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" t="s">
+        <v>106</v>
+      </c>
+      <c r="C85" t="s">
+        <v>107</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G85" t="s">
+        <v>210</v>
+      </c>
+      <c r="H85" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" t="s">
+        <v>92</v>
+      </c>
+      <c r="B86" t="s">
+        <v>106</v>
+      </c>
+      <c r="C86" t="s">
+        <v>107</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G86" t="s">
+        <v>210</v>
+      </c>
+      <c r="H86" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" t="s">
+        <v>106</v>
+      </c>
+      <c r="C87" t="s">
+        <v>107</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G87" t="s">
+        <v>210</v>
+      </c>
+      <c r="H87" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" t="s">
+        <v>106</v>
+      </c>
+      <c r="C88" t="s">
+        <v>107</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G88" t="s">
+        <v>210</v>
+      </c>
+      <c r="H88" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89" t="s">
+        <v>106</v>
+      </c>
+      <c r="C89" t="s">
+        <v>107</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G89" t="s">
+        <v>210</v>
+      </c>
+      <c r="H89" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" t="s">
+        <v>106</v>
+      </c>
+      <c r="C90" t="s">
+        <v>107</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G90" t="s">
+        <v>210</v>
+      </c>
+      <c r="H90" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>97</v>
+      </c>
+      <c r="B91" t="s">
+        <v>106</v>
+      </c>
+      <c r="C91" t="s">
+        <v>107</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G91" t="s">
+        <v>211</v>
+      </c>
+      <c r="H91" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" t="s">
+        <v>106</v>
+      </c>
+      <c r="C92" t="s">
+        <v>107</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G92" t="s">
+        <v>211</v>
+      </c>
+      <c r="H92" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
+        <v>99</v>
+      </c>
+      <c r="B93" t="s">
+        <v>106</v>
+      </c>
+      <c r="C93" t="s">
+        <v>107</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G93" t="s">
+        <v>211</v>
+      </c>
+      <c r="H93" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" t="s">
+        <v>106</v>
+      </c>
+      <c r="C94" t="s">
+        <v>107</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G94" t="s">
+        <v>211</v>
+      </c>
+      <c r="H94" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" t="s">
+        <v>106</v>
+      </c>
+      <c r="C95" t="s">
+        <v>107</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G95" t="s">
+        <v>211</v>
+      </c>
+      <c r="H95" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" t="s">
+        <v>106</v>
+      </c>
+      <c r="C96" t="s">
+        <v>107</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G96" t="s">
+        <v>211</v>
+      </c>
+      <c r="H96" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" t="s">
+        <v>106</v>
+      </c>
+      <c r="C97" t="s">
+        <v>107</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G97" t="s">
+        <v>211</v>
+      </c>
+      <c r="H97" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" t="s">
+        <v>106</v>
+      </c>
+      <c r="C98" t="s">
+        <v>107</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G98" t="s">
+        <v>211</v>
+      </c>
+      <c r="H98" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" t="s">
+        <v>106</v>
+      </c>
+      <c r="C99" t="s">
+        <v>107</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G99" t="s">
+        <v>211</v>
+      </c>
+      <c r="H99" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -1775,6 +3038,54 @@
     <hyperlink ref="F49" r:id="rId48"/>
     <hyperlink ref="F50" r:id="rId49"/>
     <hyperlink ref="F51" r:id="rId50"/>
+    <hyperlink ref="F52" r:id="rId51"/>
+    <hyperlink ref="F53" r:id="rId52"/>
+    <hyperlink ref="F54" r:id="rId53"/>
+    <hyperlink ref="F55" r:id="rId54"/>
+    <hyperlink ref="F56" r:id="rId55"/>
+    <hyperlink ref="F57" r:id="rId56"/>
+    <hyperlink ref="F58" r:id="rId57"/>
+    <hyperlink ref="F59" r:id="rId58"/>
+    <hyperlink ref="F60" r:id="rId59"/>
+    <hyperlink ref="F61" r:id="rId60"/>
+    <hyperlink ref="F62" r:id="rId61"/>
+    <hyperlink ref="F63" r:id="rId62"/>
+    <hyperlink ref="F64" r:id="rId63"/>
+    <hyperlink ref="F65" r:id="rId64"/>
+    <hyperlink ref="F66" r:id="rId65"/>
+    <hyperlink ref="F67" r:id="rId66"/>
+    <hyperlink ref="F68" r:id="rId67"/>
+    <hyperlink ref="F69" r:id="rId68"/>
+    <hyperlink ref="F70" r:id="rId69"/>
+    <hyperlink ref="F71" r:id="rId70"/>
+    <hyperlink ref="F72" r:id="rId71"/>
+    <hyperlink ref="F73" r:id="rId72"/>
+    <hyperlink ref="F74" r:id="rId73"/>
+    <hyperlink ref="F75" r:id="rId74"/>
+    <hyperlink ref="F76" r:id="rId75"/>
+    <hyperlink ref="F77" r:id="rId76"/>
+    <hyperlink ref="F78" r:id="rId77"/>
+    <hyperlink ref="F79" r:id="rId78"/>
+    <hyperlink ref="F80" r:id="rId79"/>
+    <hyperlink ref="F81" r:id="rId80"/>
+    <hyperlink ref="F82" r:id="rId81"/>
+    <hyperlink ref="F83" r:id="rId82"/>
+    <hyperlink ref="F84" r:id="rId83"/>
+    <hyperlink ref="F85" r:id="rId84"/>
+    <hyperlink ref="F86" r:id="rId85"/>
+    <hyperlink ref="F87" r:id="rId86"/>
+    <hyperlink ref="F88" r:id="rId87"/>
+    <hyperlink ref="F89" r:id="rId88"/>
+    <hyperlink ref="F90" r:id="rId89"/>
+    <hyperlink ref="F91" r:id="rId90"/>
+    <hyperlink ref="F92" r:id="rId91"/>
+    <hyperlink ref="F93" r:id="rId92"/>
+    <hyperlink ref="F94" r:id="rId93"/>
+    <hyperlink ref="F95" r:id="rId94"/>
+    <hyperlink ref="F96" r:id="rId95"/>
+    <hyperlink ref="F97" r:id="rId96"/>
+    <hyperlink ref="F98" r:id="rId97"/>
+    <hyperlink ref="F99" r:id="rId98"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Women_and_Family_Support.xlsx
+++ b/results/scraped_Cape_Town_Women_and_Family_Support.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="94">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -58,27 +58,27 @@
     <t>Women| Britannica</t>
   </si>
   <si>
+    <t>51 FamousWomenin History Who Have Changed the World</t>
+  </si>
+  <si>
+    <t>28,394,802WomenImages and Stock Photos - Getty Images</t>
+  </si>
+  <si>
     <t>Women|The Guardian</t>
   </si>
   <si>
-    <t>51 FamousWomenin History Who Have Changed the World</t>
-  </si>
-  <si>
-    <t>28,394,802WomenImages and Stock Photos - Getty Images</t>
-  </si>
-  <si>
-    <t>Women’s History:Women's Rights &amp; FamousWomen|HISTORY</t>
+    <t>Women's History| NationalWomen's HistoryMuseum</t>
   </si>
   <si>
     <t>Gender-Wikipedia</t>
   </si>
   <si>
+    <t>What Is The Difference Between Sex andGender-Simply Psychology</t>
+  </si>
+  <si>
     <t>GENDERDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>What Is The Difference Between Sex andGender-Simply Psychology</t>
-  </si>
-  <si>
     <t>Gender-World Health Organization(WHO)</t>
   </si>
   <si>
@@ -88,108 +88,78 @@
     <t>How Many Genders Are There? All 72 Genders List -MedicineNet</t>
   </si>
   <si>
+    <t>List ofgenderidentities -Wikipedia</t>
+  </si>
+  <si>
     <t>Sex and gender: Meanings, definition, identity, and expression</t>
   </si>
   <si>
-    <t>List ofgenderidentities -Wikipedia</t>
-  </si>
-  <si>
     <t>Gender- LGBTQIA+ Wiki</t>
   </si>
   <si>
     <t>Gender- Simple EnglishWikipedia, the free encyclopedia</t>
   </si>
   <si>
-    <t>MicrosoftFamilySafety | Microsoft 365</t>
-  </si>
-  <si>
-    <t>Buy Microsoft 365Family(formerly Office 365) - Subscription Price ...</t>
-  </si>
-  <si>
-    <t>Disabling thefamilysecurity - Microsoft Q&amp;A</t>
-  </si>
-  <si>
-    <t>Listening to families. Improving MicrosoftFamily.</t>
-  </si>
-  <si>
-    <t>Microsoft OneDrive</t>
-  </si>
-  <si>
-    <t>How do I combine two individual Microsoft 365 plans into myfamily…</t>
-  </si>
-  <si>
-    <t>XBOX Family Settings app</t>
-  </si>
-  <si>
-    <t>Dynamics 365 Customer Voice</t>
-  </si>
-  <si>
-    <t>Manage web filtering for members in yourXBOX familygroup</t>
-  </si>
-  <si>
-    <t>Helping families and educators support safer experiences and …</t>
-  </si>
-  <si>
-    <t>FamilyConnect - Free download and install on Windows | Microsoft Store</t>
-  </si>
-  <si>
-    <t>single, adj. meanings, etymology and more | Oxford English Dictionary</t>
-  </si>
-  <si>
-    <t>SINGLEDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>single, singling, singled, singles- WordWeb dictionary definition</t>
-  </si>
-  <si>
-    <t>Examples of 'SINGLE' in a Sentence |Merriam-Webster</t>
-  </si>
-  <si>
-    <t>SINGLEDefinition &amp; Meaning |Dictionary.com</t>
-  </si>
-  <si>
-    <t>SINGLE| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
-    <t>SINGLE| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>What is the abbreviation for Single?</t>
-  </si>
-  <si>
-    <t>SINGLE definitionin American English | Collins English Dictionary</t>
-  </si>
-  <si>
-    <t>#Single(2025) - IMDb</t>
+    <t>Family- Wikipedia</t>
+  </si>
+  <si>
+    <t>Family| Definition, Meaning, Members, Types, &amp; Facts | Britannica</t>
+  </si>
+  <si>
+    <t>12 Types ofFamilyStructures &amp; Their Characteristics - wikiHow</t>
+  </si>
+  <si>
+    <t>FAMILYDefinition &amp; Meaning - Merriam-Webster</t>
+  </si>
+  <si>
+    <t>Family- Simple English Wikipedia, the free encyclopedia</t>
+  </si>
+  <si>
+    <t>Familyin the United States - Wikipedia</t>
+  </si>
+  <si>
+    <t>FamilyMembers in English: Complete List with Examples</t>
+  </si>
+  <si>
+    <t>What IsFamily? (14 Key Points) - Simplicable</t>
+  </si>
+  <si>
+    <t>What IsFamily? A Closer Look AtFamilyStructure ... -FamilyOriented</t>
+  </si>
+  <si>
+    <t>FAMILY| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>Fenton Toggle Switchplate | Rejuvenation</t>
   </si>
   <si>
     <t>ABUSEDDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>ABUSEDSynonyms: 157 Similar and Opposite Words -Merriam-Webster</t>
+  </si>
+  <si>
     <t>ABUSED| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
-    <t>ABUSEDSynonyms: 157 Similar and Opposite Words -Merriam-Webster</t>
+    <t>ABUSE| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
     <t>Abused- IMDb</t>
   </si>
   <si>
-    <t>ABUSE| English meaning - Cambridge Dictionary</t>
+    <t>Abused- definition ofabusedby The Free Dictionary</t>
+  </si>
+  <si>
+    <t>Abused - Definition, Meaning &amp; Synonyms| Vocabulary.com</t>
+  </si>
+  <si>
+    <t>What doesabusedmean? -Definitions.net</t>
   </si>
   <si>
     <t>ABUSEDefinition &amp; Meaning |Dictionary.com</t>
   </si>
   <si>
-    <t>abused- Wiktionary, the free dictionary</t>
-  </si>
-  <si>
-    <t>Abused - Definition, Meaning &amp; Synonyms| Vocabulary.com</t>
-  </si>
-  <si>
-    <t>Abused- definition ofabusedby The Free Dictionary</t>
-  </si>
-  <si>
     <t>ABUSEDDefinition &amp; Meaning | Dictionary.com</t>
   </si>
   <si>
@@ -199,157 +169,127 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3c0a692d3c0a84d46959b3496554a0bb4daaebcdffc3aa77969d418ae424c745JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2530ec71-2a3a-6359-3903-fb902bd6625e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV29tYW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=54baa4404051b5756ea2c725553d764704e08397d33db4343bda09a0cd3bd385JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2530ec71-2a3a-6359-3903-fb902bd6625e&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3dvbWFu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a8516609c65d860a4adb58831d8124113a8980ba1526f94fd4a1c9a9de753893JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2530ec71-2a3a-6359-3903-fb902bd6625e&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL1dvbWFu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a0a53c131d84aabe4abea98188b849db573b040f9c53578211184590679f70d9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2530ec71-2a3a-6359-3903-fb902bd6625e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmVtYWxl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4f50ee095ac331f711d10c9435fa0e4829ebb402e214122772d785ed9a4cebf1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2530ec71-2a3a-6359-3903-fb902bd6625e&amp;u=a1aHR0cHM6Ly93d3cud29tZW4uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9678ba939398e46015d1a5a55137c594eba89470063af97e858a2c05b52a990fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2530ec71-2a3a-6359-3903-fb902bd6625e&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvd29tZW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=55b88039be53aca52579459483a0ddcf84b24a6277ddab47da3222a906c1d27aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2530ec71-2a3a-6359-3903-fb902bd6625e&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL2xpZmVhbmRzdHlsZS93b21lbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7747fb1fa0e050477e36f02047dbc6a2b1363883a8db7e1c897ef7066f95c82cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2530ec71-2a3a-6359-3903-fb902bd6625e&amp;u=a1aHR0cHM6Ly93d3cuYmlvZ3JhcGh5LmNvbS9oaXN0b3J5LWN1bHR1cmUvZzQzMzM2MjUyL2ZhbW91cy13b21lbi1pbi1oaXN0b3J5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6f02f86e5abc71b5e96f77477dfd92a10138c161c95e5b9c945cdded3b344330JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2530ec71-2a3a-6359-3903-fb902bd6625e&amp;u=a1aHR0cHM6Ly93d3cuZ2V0dHlpbWFnZXMuY29tL3Bob3Rvcy93b21lbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=817944ae51073bea2be78703cc438ea6b2739c14faf3fab34f787af6b9350abaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2530ec71-2a3a-6359-3903-fb902bd6625e&amp;u=a1aHR0cHM6Ly93d3cuaGlzdG9yeS5jb20vdG9waWNzL3dvbWVucy1oaXN0b3J5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=53551ba5038c7df4b41c30bd86bc5b5559516c747c65a831a0717cbefa337499JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d08a82a-3782-6f51-393f-bfcb36306e26&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvR2VuZGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1c4571ecfe5ff6c03fb8ae75a81cbfff7c03deb9c966dadf7fef42a77c12d76JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d08a82a-3782-6f51-393f-bfcb36306e26&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2dlbmRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e47a3a1f7166dafdd5b240056086d69ab7aaed72ac52ec97b586af00f94f3d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d08a82a-3782-6f51-393f-bfcb36306e26&amp;u=a1aHR0cHM6Ly93d3cuc2ltcGx5cHN5Y2hvbG9neS5vcmcvc2V4LWdlbmRlci5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=807cc62b581341b29c5593070ea31cac6dd9cf0a4c19ee3cd03a51d0b1740c47JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d08a82a-3782-6f51-393f-bfcb36306e26&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9oZWFsdGgtdG9waWNzL2dlbmRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b16e7cedfbbd1365035a7c21acd2e09ea45647fc4bf80860c162862777474761JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d08a82a-3782-6f51-393f-bfcb36306e26&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9iYXNpY3MvZ2VuZGVyP21zb2NraWQ9MmQwOGE4MmEzNzgyNmY1MTM5M2ZiZmNiMzYzMDZlMjY&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8505fc073f4c699da08a8630ae90008326d922f8deeba21fc79c88660d61dd54JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d08a82a-3782-6f51-393f-bfcb36306e26&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNpbmVuZXQuY29tL3doYXRfYXJlX3RoZV83Ml9vdGhlcl9nZW5kZXJzL2FydGljbGUuaHRt&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ee1a93805e8c2be14ea93a197d222793f7f4e48ac04114c0f7d32282bb7d3fbbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d08a82a-3782-6f51-393f-bfcb36306e26&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMjMyMzYz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ded2080559523bfb5e959c189a6807f6cea3971f4bd331c193ecfdd1ef48b0d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d08a82a-3782-6f51-393f-bfcb36306e26&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGlzdF9vZl9nZW5kZXJfaWRlbnRpdGllcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=56370d6685c1c8aa01d1a709dd0cd858e3a4d2c3f7a86b00490bb8d9012d78dbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d08a82a-3782-6f51-393f-bfcb36306e26&amp;u=a1aHR0cHM6Ly9sZ2J0cWlhLndpa2kvd2lraS9HZW5kZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=414d693e3cdcd8061b859fbb6350f3b168688cde160737d2bb29c091fb024358JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2d08a82a-3782-6f51-393f-bfcb36306e26&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL0dlbmRlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=849dd1176632627f130c182e01d8486f6279fa59f6f67ab74b8078aed646e041JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32aca372-ead2-6706-3591-b493eb5066da&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cy9taWNyb3NvZnQtMzY1L2ZhbWlseS1zYWZldHk_bXNvY2tpZD0zMmFjYTM3MmVhZDI2NzA2MzU5MWI0OTNlYjUwNjZkYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11482ca5d883eba26f1a1b0aaedb56716fae08df4c95c482763cf62acd045b46JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32aca372-ead2-6706-3591-b493eb5066da&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cy9taWNyb3NvZnQtMzY1L3AvbWljcm9zb2Z0LTM2NS1mYW1pbHkvY2ZxN3R0YzBrNWRtP21zb2NraWQ9MzJhY2EzNzJlYWQyNjcwNjM1OTFiNDkzZWI1MDY2ZGE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f0bacca4d189a29b65c360006b3ce518eb7a0478e0189f8968e59fba9c28dd30JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32aca372-ead2-6706-3591-b493eb5066da&amp;u=a1aHR0cHM6Ly9sZWFybi5taWNyb3NvZnQuY29tL2VuLXVzL2Fuc3dlcnMvcXVlc3Rpb25zLzU5MTA0MTEvZGlzYWJsaW5nLXRoZS1mYW1pbHktc2VjdXJpdHk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3e62dbd81b180c9ced9fd4e3e984856ccb36d3eea037b58eb3311b63f2e8a659JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32aca372-ead2-6706-3591-b493eb5066da&amp;u=a1aHR0cHM6Ly9ibG9ncy53aW5kb3dzLmNvbS93aW5kb3dzZXhwZXJpZW5jZS8yMDI2LzA5LzA4L2xpc3RlbmluZy10by1mYW1pbGllcy1pbXByb3ZpbmctbWljcm9zb2Z0LWZhbWlseS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=707cc29eec93decf9fe32496ac9f9f06981cd49cc9f86f770ea6fffcb97541aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32aca372-ead2-6706-3591-b493eb5066da&amp;u=a1aHR0cHM6Ly9vbmVkcml2ZWx0aS5taWNyb3NvZnQuY29tL3Rvb2w&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7a09054f35c6fc5a323e39d2e5cd488bedc34bbd51cafbcfb728442df09a411dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32aca372-ead2-6706-3591-b493eb5066da&amp;u=a1aHR0cHM6Ly9sZWFybi5taWNyb3NvZnQuY29tL2VuLXVzL2Fuc3dlcnMvcXVlc3Rpb25zLzYwMTE0NTQvaG93LWRvLWktY29tYmluZS10d28taW5kaXZpZHVhbC1taWNyb3NvZnQtMzY1LXBsYW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e0e1ec72c42b0dc8d84e7ba47022f5cec6c3e47915eaedbcd62f1b16caf1dca2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32aca372-ead2-6706-3591-b493eb5066da&amp;u=a1aHR0cHM6Ly93d3cueGJveC5jb20vZW4tR0IvYXBwcy9mYW1pbHktc2V0dGluZ3MtYXBwP21zb2NraWQ9MzJhY2EzNzJlYWQyNjcwNjM1OTFiNDkzZWI1MDY2ZGE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7a29c472edf526048a520fd122e9c6ef84d1112bf47ed8be811edc1bdf703c24JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32aca372-ead2-6706-3591-b493eb5066da&amp;u=a1aHR0cHM6Ly9jdXN0b21lcnZvaWNlLm1pY3Jvc29mdC5jb20vUGFnZXMvUmVzcG9uc2VQYWdlLmFzcHg_aWQ9TmdqQU9STHQya2libDFsTmdJOEQ1UXRzWHFPWjNmWkZqNFZGN1V0QW8tMVVOMVJPVVRORlVETldXVU5VVXpGRlJEbFNSMGN4UkVOUVRpUWxRQ04wUFdjdQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3a0349cb19f05661c6f2dbda7b91fa22f83e99f23b164bb59652126cf56de78eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32aca372-ead2-6706-3591-b493eb5066da&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lnhib3guY29tL2VuLVVTL2hlbHAvZmFtaWx5LW9ubGluZS1zYWZldHkvb25saW5lLXNhZmV0eS9ibG9jay1pbmFwcHJvcHJpYXRlLWNvbnRlbnQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7344f564daef3a524f3bccabfcfd8edd0972148696c7312e4f76f4ff5b0c768aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32aca372-ead2-6706-3591-b493eb5066da&amp;u=a1aHR0cHM6Ly9ibG9ncy53aW5kb3dzLmNvbS93aW5kb3dzZXhwZXJpZW5jZS8yMDI2LzA5LzA4L2hlbHBpbmctZmFtaWxpZXMtYW5kLWVkdWNhdG9ycy1zdXBwb3J0LXNhZmVyLWV4cGVyaWVuY2VzLWFuZC1oZWFsdGhpZXItaGFiaXRzLW9uLXdpbmRvd3Mv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=231550e255b72d19088e8d2d99cbeaacabea3d521c29e0c2c6644afc000a1ff5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32aca372-ead2-6706-3591-b493eb5066da&amp;u=a1aHR0cHM6Ly9hcHBzLm1pY3Jvc29mdC5jb20vZGV0YWlsLzlubXptYmhiOGR4Zg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9ca144de0d0d52f2a9c11872cf20642ca39e35cf0e5af9f5bc546eaa39a86faJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bad424f-644f-634e-3950-55ae65e86233&amp;u=a1aHR0cHM6Ly93d3cub2VkLmNvbS9kaWN0aW9uYXJ5L3NpbmdsZV9hZGo&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aca500d8d36b723fc61e058171b406b0b5ad86e7e8edb1d691861d6f70dabafcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bad424f-644f-634e-3950-55ae65e86233&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=521bef6bae88c87234fb2a7819d9a7369ee934bb4756a332d72dd253166bdfc0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bad424f-644f-634e-3950-55ae65e86233&amp;u=a1aHR0cHM6Ly93d3cud29yZHdlYm9ubGluZS5jb20vZW4vU0lOR0xF&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=039f3d3de6f3da345601a5ae2f50a539b44fd6eaf30ffffced4c09d861092054JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bad424f-644f-634e-3950-55ae65e86233&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9zZW50ZW5jZXMvc2luZ2xl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7ac3dbabbb3a38c6e985ebf06503cd1898ca06296c10b67558c3c210d7d6d372JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bad424f-644f-634e-3950-55ae65e86233&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=27386597254080c39c785da93979e2148004cee408f7d260086e0b045a42dd27JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bad424f-644f-634e-3950-55ae65e86233&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7946f0d7b23210f5b155c5f56e19261aa9348b3741d9f041b903609babf5ed0eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bad424f-644f-634e-3950-55ae65e86233&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b6a469f3dd059d545dbb4b8b516f1b0425d23b910f3e60a6cb80ede48f87ce6dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bad424f-644f-634e-3950-55ae65e86233&amp;u=a1aHR0cHM6Ly93d3cuYWJicmV2aWF0aW9ucy5jb20vYWJicmV2aWF0aW9uL1NpbmdsZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a4931425ef0c6d597152659b59462ac2df91c06ae16e8f4803e6f621c07867eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bad424f-644f-634e-3950-55ae65e86233&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL3VzL2RpY3Rpb25hcnkvZW5nbGlzaC9zaW5nbGU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c5d99cd00465af2014317478cd5a97744a17d3e69c01144ad51127ba9a5f3c2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2bad424f-644f-634e-3950-55ae65e86233&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQzNTY5NDU2NS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7b9fb467eda6c112c9735a140e6a7a24ce70b2b234e665f2b519646cbda4b922JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12bb3ae2-874b-6fd8-1f87-2d0386ae6ef2&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=85c97abd510e762446bda8064488dd39d9d53c6e6f6270a2b643c6cdc27f167eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12bb3ae2-874b-6fd8-1f87-2d0386ae6ef2&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0271531642f12eefeb7fbd902ad29dcace3f1a7ac6bd71ed5040d427a277c231JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12bb3ae2-874b-6fd8-1f87-2d0386ae6ef2&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvYWJ1c2Vk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f61f47d6b67d3e7ce2c5fad646e814f430510c54e1bd7ac34cc74b467c8563dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12bb3ae2-874b-6fd8-1f87-2d0386ae6ef2&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNjk2ODUwMC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6b770aff8233ba8c7726d11d07620296b2d8495d73a706e5a3575a80507c293bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12bb3ae2-874b-6fd8-1f87-2d0386ae6ef2&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9203f612334bd46c90161d2a696f29adf891a86e60a9e019cd9cc226346195f9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12bb3ae2-874b-6fd8-1f87-2d0386ae6ef2&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4602a01375ede21a0845772df7e8d235ea54755f443a6b1040b5e093f134b2e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12bb3ae2-874b-6fd8-1f87-2d0386ae6ef2&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72a1fe10b40c995c54c6f226b4a46bcdcb70b24007afe5b9a519eb511f70e045JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12bb3ae2-874b-6fd8-1f87-2d0386ae6ef2&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9hYnVzZWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f057ad4e8f5a00825aa50d2315ec2e1734c5738dc206a7de8c50161eb91fdf06JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12bb3ae2-874b-6fd8-1f87-2d0386ae6ef2&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2FidXNlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=35f058b82ab6f79029f260769be9a60b42d59a24dea1761e93cfca2c2df1a8aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12bb3ae2-874b-6fd8-1f87-2d0386ae6ef2&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNlZA&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3401788bbd828128a9ea079b7e5b76b5eb79bcf5ba1b3c772ccc4a461061e989JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dcae5c7-aab4-63ea-0c10-f226abcd6256&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Xb21hbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a07c048ffc448432fbce13cbe25863588c4265bd934e755ddf29dae281f8beccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dcae5c7-aab4-63ea-0c10-f226abcd6256&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3dvbWFu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=13f0fb1fd3afb9d44fe44a117def6fc16f9bbc3daaefc0cf31be73b5c508ec57JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dcae5c7-aab4-63ea-0c10-f226abcd6256&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvV29tYW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=864f1b1b1998780dea5808615c9a492ad9cb38d5d63df4cb29d5266eb5e11485JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dcae5c7-aab4-63ea-0c10-f226abcd6256&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GZW1hbGU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=251c7a09004c9674d5dfdbb694d1b074c5bfdb048ac8b61c6d83248a91a009a1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dcae5c7-aab4-63ea-0c10-f226abcd6256&amp;u=a1aHR0cHM6Ly93d3cud29tZW4uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8af92e08b2e5715a0e03215c992f12cdfb4d6aa21aa40b89d195f46b2eb1c68cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dcae5c7-aab4-63ea-0c10-f226abcd6256&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvd29tZW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f76c7783224aee54161967ec91bb59f0cb3870d0ecfcea27cdb3514ec45883bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dcae5c7-aab4-63ea-0c10-f226abcd6256&amp;u=a1aHR0cHM6Ly93d3cuYmlvZ3JhcGh5LmNvbS9oaXN0b3J5LWN1bHR1cmUvZzQzMzM2MjUyL2ZhbW91cy13b21lbi1pbi1oaXN0b3J5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=699b6f41e5d9b8598be279baca38280c98c45521f57e509f5ffe7146df10eed3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dcae5c7-aab4-63ea-0c10-f226abcd6256&amp;u=a1aHR0cHM6Ly93d3cuZ2V0dHlpbWFnZXMuY29tL3Bob3Rvcy93b21lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=533d0820f482eeffac6590e2e24662cbdbe6cd7f7976ce1b3b402a8fbb433c1dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dcae5c7-aab4-63ea-0c10-f226abcd6256&amp;u=a1aHR0cHM6Ly93d3cudGhlZ3VhcmRpYW4uY29tL2xpZmVhbmRzdHlsZS93b21lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=656ff9ce4fbe0003ccc490dea7fb7f90e316248ce754aded2c2364bb5fa2ec3fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2dcae5c7-aab4-63ea-0c10-f226abcd6256&amp;u=a1aHR0cHM6Ly93d3cud29tZW5zaGlzdG9yeS5vcmcvd29tZW5zLWhpc3Rvcnk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5979b1c5895bccd823cda9eea945873ca2e97002276308f6a221fe8afa16a4aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19ece652-baa8-6d63-212a-f1b3bb326c62&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9HZW5kZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d0d6acd120fb9588de0221c997e367f9ff90ed1a3e62a990994ccee236fe4d3aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19ece652-baa8-6d63-212a-f1b3bb326c62&amp;u=a1aHR0cHM6Ly93d3cuc2ltcGx5cHN5Y2hvbG9neS5vcmcvc2V4LWdlbmRlci5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e98e27b49bcadf24f526c19aae0206454ae0248ed2601fbb1695d55cfe8eeefJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19ece652-baa8-6d63-212a-f1b3bb326c62&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2dlbmRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7ad57dc2de35c9e459d914fbf62b7cb30f59079b16c12e6a36f4514a30c32dc7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19ece652-baa8-6d63-212a-f1b3bb326c62&amp;u=a1aHR0cHM6Ly93d3cud2hvLmludC9oZWFsdGgtdG9waWNzL2dlbmRlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a6823f9b680e5dbbf4575dcbeebcd30c5b35da62ddb7ad602f3ca5f6c8600cb5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19ece652-baa8-6d63-212a-f1b3bb326c62&amp;u=a1aHR0cHM6Ly93d3cucHN5Y2hvbG9neXRvZGF5LmNvbS91cy9iYXNpY3MvZ2VuZGVyP21zb2NraWQ9MTllY2U2NTJiYWE4NmQ2MzIxMmFmMWIzYmIzMjZjNjI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=66e665c1bdcbc1ccbd109b8d40b96f4b70da048e2c059532f370379b47ab2073JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19ece652-baa8-6d63-212a-f1b3bb326c62&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNpbmVuZXQuY29tL3doYXRfYXJlX3RoZV83Ml9vdGhlcl9nZW5kZXJzL2FydGljbGUuaHRt&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a570867d0cb7a235211ab1d155a5b5802eb17c14907d4e5f1fcb6d7ab6835ed1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19ece652-baa8-6d63-212a-f1b3bb326c62&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9MaXN0X29mX2dlbmRlcl9pZGVudGl0aWVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=99eb562a927bbf4ad9065d827e2826b39f2462c1c312f37c334eba561b9ba2b6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19ece652-baa8-6d63-212a-f1b3bb326c62&amp;u=a1aHR0cHM6Ly93d3cubWVkaWNhbG5ld3N0b2RheS5jb20vYXJ0aWNsZXMvMjMyMzYz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d1e23437de52843549114263fcfe6bac3e54016f4b95ee57884fc67f1645251JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19ece652-baa8-6d63-212a-f1b3bb326c62&amp;u=a1aHR0cHM6Ly9sZ2J0cWlhLndpa2kvd2lraS9HZW5kZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d60b6928406f3fe1dbf16aba0f61aad7ede56fee7b29cf960489284cd11c2226JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=19ece652-baa8-6d63-212a-f1b3bb326c62&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvR2VuZGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c89486270e403b742aaad854408dc312f51b6bc25d040f0354a790b826850fecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd73e95-13c8-670f-33dd-2974122c6621&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GYW1pbHk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=19140604393d820a5e980a01a3814acca5576b23ac788f33f55ab82da455a1a6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd73e95-13c8-670f-33dd-2974122c6621&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vdG9waWMvZmFtaWx5LWtpbnNoaXA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f64fe31db2488530cca962dd2bf09bd4f40adc6bd423ee11bb81839765ad672JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd73e95-13c8-670f-33dd-2974122c6621&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vVHlwZXMtb2YtRmFtaWx5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0701bfa0cdd2b998ae225bef7d46452e1ab5967b1dd5c1b0351e652cfeef7d43JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd73e95-13c8-670f-33dd-2974122c6621&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZhbWlseQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c56c3ac5cd229c318d145ed894a68668733b51ac675e33124c01d0e8a7409ddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd73e95-13c8-670f-33dd-2974122c6621&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvRmFtaWx5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47fad95679a91e7356db5cb15d0b27aa99e29950be036c54337752dced76c71dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd73e95-13c8-670f-33dd-2974122c6621&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GYW1pbHlfaW5fdGhlX1VuaXRlZF9TdGF0ZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=785091b7062926028897f3c46a071eb835b443d6753b5e7de6efb33370362642JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd73e95-13c8-670f-33dd-2974122c6621&amp;u=a1aHR0cHM6Ly92b2NhYmVycnkuY29tL3ZvY2FidWxhcnkvZmFtaWx5LW1lbWJlcnMtaW4tZW5nbGlzaC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1506a5586d2aed8730c7f24610eaf4386437eaf03bbc4240c68ad9aadc149afaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd73e95-13c8-670f-33dd-2974122c6621&amp;u=a1aHR0cHM6Ly9zaW1wbGljYWJsZS5jb20vc29jaWV0eS93aGF0LWlzLWZhbWlseQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=67e3443a43ad0e2b08708db0f8eb40237988648e9eed22aba620f0b83accdff2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd73e95-13c8-670f-33dd-2974122c6621&amp;u=a1aHR0cHM6Ly9mYW1pbHlvcmllbnRlZC5uZXQvd2hhdC1pcy1mYW1pbHkv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1e6146156c8f3a7ef88f19d6ff925c3c2a64b7e811f79b57e9a0d92b0fa20b95JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3dd73e95-13c8-670f-33dd-2974122c6621&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZhbWlseQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=78edb82690ebcd034ef86549f63373f41904ad303a524ed655fce81ef1fda3b7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1a729312-ac06-63ca-3a8e-84f3ad79626f&amp;u=a1aHR0cHM6Ly93d3cucmVqdXZlbmF0aW9uLmNvbS9wcm9kdWN0cy9mZW50b24tdG9nZ2xlLXN3aXRjaHBsYXRlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6698199efe7bbca2f4723972ab2b9e10598d24d89f522ada61e088b2d4b2ed65JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c148ef9-5ef1-6340-37f3-99185fa16245&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FidXNlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2249cd65699151526dfaf1012070358a31316649f18c2a88a5cd7d7f5d0e412JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c148ef9-5ef1-6340-37f3-99185fa16245&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS90aGVzYXVydXMvYWJ1c2Vk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=84478fd3678e9d4450da33ea0697a5886ef3b9b64bd56ad2848d9881aadd5e2fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c148ef9-5ef1-6340-37f3-99185fa16245&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8d232415b1ab0c5322043f7e79e5e834d5b81e1ec2f668832f8f20f867decc59JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c148ef9-5ef1-6340-37f3-99185fa16245&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2FidXNl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=20a500c53a376afab4f9fe30062bdf89d2c59a6080a9860461012b04b846bf6bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c148ef9-5ef1-6340-37f3-99185fa16245&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQxNjk2ODUwMC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=078467b7e1918b8fe306418bb57f619e6149eab4b4912f8117ba2434320df05dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c148ef9-5ef1-6340-37f3-99185fa16245&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2FidXNlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4cdc44ef65ef2fa64c3eb8797bb02438b61bed0370af32886c1258681874075bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c148ef9-5ef1-6340-37f3-99185fa16245&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9hYnVzZWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e22d036b15370cfc987fc9840b205f779ebd09a93f666face8d7e0bae7c8d2aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c148ef9-5ef1-6340-37f3-99185fa16245&amp;u=a1aHR0cHM6Ly93d3cuZGVmaW5pdGlvbnMubmV0L2RlZmluaXRpb24vYWJ1c2Vk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5375b3ea41129c8f611299b9fa591c98abdd1734453c75bdee3da035888c973JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c148ef9-5ef1-6340-37f3-99185fa16245&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=00bb98523a46066ece8d4640d531721cfd467403e9ae8cf7f7e7edd2b5cac9e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c148ef9-5ef1-6340-37f3-99185fa16245&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2FidXNlZA&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
@@ -700,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -734,19 +674,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="G2" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H2" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -754,19 +694,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="G3" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H3" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -774,19 +714,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G4" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H4" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -794,19 +734,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G5" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -814,19 +754,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G6" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -834,19 +774,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="G7" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -854,19 +794,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="G8" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H8" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -874,19 +814,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G9" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H9" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -894,19 +834,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="G10" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H10" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -914,19 +854,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="G11" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H11" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -934,19 +874,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H12" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -954,19 +894,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="G13" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H13" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -974,19 +914,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G14" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H14" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -994,19 +934,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="G15" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H15" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1014,19 +954,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G16" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H16" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1034,19 +974,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="G17" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H17" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1054,19 +994,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="G18" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H18" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1074,19 +1014,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="G19" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H19" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1094,19 +1034,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G20" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H20" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1114,19 +1054,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G21" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H21" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1134,19 +1074,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H22" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1154,19 +1094,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="G23" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H23" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1174,19 +1114,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G24" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H24" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1194,19 +1134,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G25" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H25" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1214,19 +1154,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H26" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1234,19 +1174,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H27" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1254,19 +1194,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H28" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1274,19 +1214,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H29" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1294,19 +1234,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H30" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1314,19 +1254,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H31" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1334,19 +1274,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H32" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1354,19 +1294,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G33" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1374,19 +1314,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="G34" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H34" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1394,19 +1334,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="G35" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H35" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1414,19 +1354,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="G36" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H36" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1434,19 +1374,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="G37" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H37" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1454,19 +1394,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="G38" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H38" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1474,19 +1414,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="G39" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H39" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1494,19 +1434,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G40" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H40" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1514,19 +1454,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H41" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1534,219 +1474,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="G42" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" t="s">
-        <v>59</v>
-      </c>
-      <c r="C43" t="s">
-        <v>60</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G43" t="s">
-        <v>112</v>
-      </c>
-      <c r="H43" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" t="s">
-        <v>59</v>
-      </c>
-      <c r="C44" t="s">
-        <v>60</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G44" t="s">
-        <v>112</v>
-      </c>
-      <c r="H44" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" t="s">
-        <v>59</v>
-      </c>
-      <c r="C45" t="s">
-        <v>60</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G45" t="s">
-        <v>112</v>
-      </c>
-      <c r="H45" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" t="s">
-        <v>59</v>
-      </c>
-      <c r="C46" t="s">
-        <v>60</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G46" t="s">
-        <v>112</v>
-      </c>
-      <c r="H46" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" t="s">
-        <v>59</v>
-      </c>
-      <c r="C47" t="s">
-        <v>60</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G47" t="s">
-        <v>112</v>
-      </c>
-      <c r="H47" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" t="s">
-        <v>59</v>
-      </c>
-      <c r="C48" t="s">
-        <v>60</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G48" t="s">
-        <v>112</v>
-      </c>
-      <c r="H48" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" t="s">
-        <v>59</v>
-      </c>
-      <c r="C49" t="s">
-        <v>60</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G49" t="s">
-        <v>112</v>
-      </c>
-      <c r="H49" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" t="s">
-        <v>59</v>
-      </c>
-      <c r="C50" t="s">
-        <v>60</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G50" t="s">
-        <v>112</v>
-      </c>
-      <c r="H50" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" t="s">
-        <v>59</v>
-      </c>
-      <c r="C51" t="s">
-        <v>60</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G51" t="s">
-        <v>112</v>
-      </c>
-      <c r="H51" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" t="s">
-        <v>59</v>
-      </c>
-      <c r="C52" t="s">
-        <v>60</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G52" t="s">
-        <v>112</v>
-      </c>
-      <c r="H52" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1792,16 +1532,6 @@
     <hyperlink ref="F40" r:id="rId39"/>
     <hyperlink ref="F41" r:id="rId40"/>
     <hyperlink ref="F42" r:id="rId41"/>
-    <hyperlink ref="F43" r:id="rId42"/>
-    <hyperlink ref="F44" r:id="rId43"/>
-    <hyperlink ref="F45" r:id="rId44"/>
-    <hyperlink ref="F46" r:id="rId45"/>
-    <hyperlink ref="F47" r:id="rId46"/>
-    <hyperlink ref="F48" r:id="rId47"/>
-    <hyperlink ref="F49" r:id="rId48"/>
-    <hyperlink ref="F50" r:id="rId49"/>
-    <hyperlink ref="F51" r:id="rId50"/>
-    <hyperlink ref="F52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
